--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B94D522-9BC6-42F3-B9A9-F50FB765A840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936CEFD3-7387-4E60-B74E-6CE72A6AFF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -990,18 +990,180 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_007</t>
   </si>
   <si>
@@ -1020,16 +1182,112 @@
     <t>connecting solar to buses in cluster 42</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
+    <t>distr_solelc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_002</t>
@@ -1044,270 +1302,93 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD22</t>
   </si>
   <si>
+    <t>e_Skawina_POL</t>
+  </si>
+  <si>
+    <t>e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Mielec_POL</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>e_Pila_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Lublin_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
     <t>e_Lukow_POL</t>
   </si>
   <si>
@@ -1320,10 +1401,58 @@
     <t>e_Lodz_POL</t>
   </si>
   <si>
-    <t>e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>e_Szczecin_POL</t>
+    <t>e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>e_Siedlce_POL</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>e_Belchatow_POL</t>
+  </si>
+  <si>
+    <t>e_Zabrze_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
   </si>
   <si>
     <t>e_Bialystok_POL</t>
@@ -1332,135 +1461,6 @@
     <t>e_Grajewo_POL</t>
   </si>
   <si>
-    <t>e_Lublin_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL</t>
-  </si>
-  <si>
-    <t>e_Siedlce_POL</t>
-  </si>
-  <si>
-    <t>e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>e_Belchatow_POL</t>
-  </si>
-  <si>
-    <t>e_Zabrze_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL</t>
-  </si>
-  <si>
-    <t>e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>e_Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>e_Skawina_POL</t>
-  </si>
-  <si>
-    <t>e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Mielec_POL</t>
-  </si>
-  <si>
-    <t>e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>e_Pila_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>e_Poznan_POL</t>
-  </si>
-  <si>
-    <t>e_Wroclaw_POL</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_003</t>
   </si>
   <si>
@@ -1473,6 +1473,240 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_015</t>
   </si>
   <si>
@@ -1521,246 +1755,129 @@
     <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
     <t>elc_won_POL_020</t>
   </si>
   <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_049</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
@@ -1785,121 +1902,40 @@
     <t>elc_won_POL_047</t>
   </si>
   <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>elc_won_POL_041</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>elc_won_POL_049</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>elc_won_POL_034</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>elc_won_POL_023</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>elc_won_POL_037</t>
-  </si>
-  <si>
-    <t>elc_won_POL_030</t>
-  </si>
-  <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>elc_won_POL_032</t>
-  </si>
-  <si>
-    <t>elc_won_POL_026</t>
-  </si>
-  <si>
-    <t>elc_won_POL_048</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
-  </si>
-  <si>
-    <t>elc_won_POL_042</t>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_001</t>
@@ -1908,10 +1944,16 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_008</t>
@@ -1920,76 +1962,34 @@
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
   </si>
   <si>
-    <t>elc_wof_POL_002</t>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -6534,7 +6534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81B3BD1-21BC-4AB0-8A01-A6CBC561BD1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A8D779-F3C1-4A6E-9D6D-0A6F6C3A3C72}">
   <dimension ref="B9:BD61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6772,16 +6772,16 @@
         <v>308</v>
       </c>
       <c r="Y11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="Z11" t="s">
         <v>414</v>
       </c>
       <c r="AA11">
-        <v>0.99814724525850784</v>
+        <v>0.99751836673919181</v>
       </c>
       <c r="AB11">
-        <v>47.820994144128512</v>
+        <v>50.515025114296037</v>
       </c>
       <c r="AD11" t="s">
         <v>307</v>
@@ -6811,7 +6811,7 @@
         <v>563</v>
       </c>
       <c r="AN11" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="AO11">
         <v>0.99790284855194045</v>
@@ -6847,13 +6847,13 @@
         <v>632</v>
       </c>
       <c r="BB11" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="BC11">
-        <v>0.99436455351944619</v>
+        <v>0.99478860441526007</v>
       </c>
       <c r="BD11">
-        <v>728.41730490967211</v>
+        <v>610.20976015093845</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6918,16 +6918,16 @@
         <v>312</v>
       </c>
       <c r="Y12" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="Z12" t="s">
         <v>415</v>
       </c>
       <c r="AA12">
-        <v>0.99848201234520018</v>
+        <v>0.99774808836727491</v>
       </c>
       <c r="AB12">
-        <v>72.463654284142635</v>
+        <v>41.186340097586395</v>
       </c>
       <c r="AD12" t="s">
         <v>307</v>
@@ -6957,7 +6957,7 @@
         <v>564</v>
       </c>
       <c r="AN12" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="AO12">
         <v>0.99856107979091546</v>
@@ -6993,13 +6993,13 @@
         <v>633</v>
       </c>
       <c r="BB12" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="BC12">
-        <v>0.99478860441526007</v>
+        <v>0.99378504174620896</v>
       </c>
       <c r="BD12">
-        <v>610.20976015093845</v>
+        <v>761.13276667340403</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7064,16 +7064,16 @@
         <v>314</v>
       </c>
       <c r="Y13" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="Z13" t="s">
         <v>416</v>
       </c>
       <c r="AA13">
-        <v>0.99886290297361824</v>
+        <v>0.99828790514523624</v>
       </c>
       <c r="AB13">
-        <v>26.622770797002293</v>
+        <v>28.428965886446147</v>
       </c>
       <c r="AD13" t="s">
         <v>307</v>
@@ -7103,13 +7103,13 @@
         <v>565</v>
       </c>
       <c r="AN13" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO13">
-        <v>0.99632737337312927</v>
+        <v>0.99845480529905328</v>
       </c>
       <c r="AP13">
-        <v>48.031259731727893</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AR13" t="s">
         <v>307</v>
@@ -7139,13 +7139,13 @@
         <v>634</v>
       </c>
       <c r="BB13" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="BC13">
-        <v>0.99503061728845632</v>
+        <v>0.99671396210736585</v>
       </c>
       <c r="BD13">
-        <v>669.38461499965297</v>
+        <v>535.75153841730867</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7210,16 +7210,16 @@
         <v>316</v>
       </c>
       <c r="Y14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Z14" t="s">
         <v>417</v>
       </c>
       <c r="AA14">
-        <v>0.99779181951287421</v>
+        <v>0.9976031883518911</v>
       </c>
       <c r="AB14">
-        <v>61.086483632538339</v>
+        <v>58.963512461864056</v>
       </c>
       <c r="AD14" t="s">
         <v>307</v>
@@ -7249,13 +7249,13 @@
         <v>566</v>
       </c>
       <c r="AN14" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="AO14">
-        <v>0.99739127962445018</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AP14">
-        <v>39.831307398714806</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AR14" t="s">
         <v>307</v>
@@ -7285,13 +7285,13 @@
         <v>635</v>
       </c>
       <c r="BB14" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="BC14">
-        <v>0.99249606766869936</v>
+        <v>0.99498581429447941</v>
       </c>
       <c r="BD14">
-        <v>661.89204677750558</v>
+        <v>682.74537814765154</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7356,16 +7356,16 @@
         <v>318</v>
       </c>
       <c r="Y15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Z15" t="s">
         <v>418</v>
       </c>
       <c r="AA15">
-        <v>0.9976031883518911</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AB15">
-        <v>58.963512461864056</v>
+        <v>23.107973955380711</v>
       </c>
       <c r="AD15" t="s">
         <v>307</v>
@@ -7395,13 +7395,13 @@
         <v>567</v>
       </c>
       <c r="AN15" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="AO15">
-        <v>0.99818574894902312</v>
+        <v>0.99850473493624492</v>
       </c>
       <c r="AP15">
-        <v>33.253084498654445</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AR15" t="s">
         <v>307</v>
@@ -7431,13 +7431,13 @@
         <v>636</v>
       </c>
       <c r="BB15" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="BC15">
-        <v>0.99784666475123052</v>
+        <v>0.99705787611047647</v>
       </c>
       <c r="BD15">
-        <v>434.14794560012712</v>
+        <v>516.05305554711185</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7502,16 +7502,16 @@
         <v>320</v>
       </c>
       <c r="Y16" t="s">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="Z16" t="s">
         <v>419</v>
       </c>
       <c r="AA16">
-        <v>0.99870289970840342</v>
+        <v>0.99679205626668776</v>
       </c>
       <c r="AB16">
-        <v>23.107973955380711</v>
+        <v>28.983218493781202</v>
       </c>
       <c r="AD16" t="s">
         <v>307</v>
@@ -7541,13 +7541,13 @@
         <v>568</v>
       </c>
       <c r="AN16" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="AO16">
-        <v>0.99853353101054187</v>
+        <v>0.99837593922723478</v>
       </c>
       <c r="AP16">
-        <v>18.693183403514499</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AR16" t="s">
         <v>307</v>
@@ -7577,13 +7577,13 @@
         <v>637</v>
       </c>
       <c r="BB16" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="BC16">
-        <v>0.99378504174620896</v>
+        <v>0.99635015248973569</v>
       </c>
       <c r="BD16">
-        <v>761.13276667340403</v>
+        <v>366.10125775280716</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7648,16 +7648,16 @@
         <v>322</v>
       </c>
       <c r="Y17" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="Z17" t="s">
         <v>420</v>
       </c>
       <c r="AA17">
-        <v>0.99754569173664964</v>
+        <v>0.99713110094318969</v>
       </c>
       <c r="AB17">
-        <v>45.1502695224383</v>
+        <v>34.34566125862937</v>
       </c>
       <c r="AD17" t="s">
         <v>307</v>
@@ -7687,13 +7687,13 @@
         <v>569</v>
       </c>
       <c r="AN17" t="s">
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="AO17">
-        <v>0.99747843498043831</v>
+        <v>0.99757815671697558</v>
       </c>
       <c r="AP17">
-        <v>46.334800039670455</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AR17" t="s">
         <v>307</v>
@@ -7723,13 +7723,13 @@
         <v>638</v>
       </c>
       <c r="BB17" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="BC17">
-        <v>0.99635015248973569</v>
+        <v>0.99436455351944619</v>
       </c>
       <c r="BD17">
-        <v>366.10125775280716</v>
+        <v>728.41730490967211</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7794,16 +7794,16 @@
         <v>324</v>
       </c>
       <c r="Y18" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="Z18" t="s">
         <v>421</v>
       </c>
       <c r="AA18">
-        <v>0.99697644816659792</v>
+        <v>0.99749963479302273</v>
       </c>
       <c r="AB18">
-        <v>58.519281729791345</v>
+        <v>49.14481327115881</v>
       </c>
       <c r="AD18" t="s">
         <v>307</v>
@@ -7833,13 +7833,13 @@
         <v>570</v>
       </c>
       <c r="AN18" t="s">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="AO18">
-        <v>0.99466341005350978</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AP18">
-        <v>58.229467192272445</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AR18" t="s">
         <v>307</v>
@@ -7869,13 +7869,13 @@
         <v>639</v>
       </c>
       <c r="BB18" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="BC18">
-        <v>0.99671396210736585</v>
+        <v>0.99249606766869936</v>
       </c>
       <c r="BD18">
-        <v>535.75153841730867</v>
+        <v>661.89204677750558</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7940,16 +7940,16 @@
         <v>326</v>
       </c>
       <c r="Y19" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="Z19" t="s">
         <v>422</v>
       </c>
       <c r="AA19">
-        <v>0.99755900053893942</v>
+        <v>0.9985687661763365</v>
       </c>
       <c r="AB19">
-        <v>42.327567967950763</v>
+        <v>50.93040927578344</v>
       </c>
       <c r="AD19" t="s">
         <v>307</v>
@@ -7979,13 +7979,13 @@
         <v>571</v>
       </c>
       <c r="AN19" t="s">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="AO19">
-        <v>0.9977732948939011</v>
+        <v>0.99729296780855581</v>
       </c>
       <c r="AP19">
-        <v>51.165698000691506</v>
+        <v>49.14481327115881</v>
       </c>
       <c r="AR19" t="s">
         <v>307</v>
@@ -8015,13 +8015,13 @@
         <v>640</v>
       </c>
       <c r="BB19" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="BC19">
-        <v>0.99498581429447941</v>
+        <v>0.99784666475123052</v>
       </c>
       <c r="BD19">
-        <v>682.74537814765154</v>
+        <v>434.14794560012712</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8086,16 +8086,16 @@
         <v>328</v>
       </c>
       <c r="Y20" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="Z20" t="s">
         <v>423</v>
       </c>
       <c r="AA20">
-        <v>0.99776786767941794</v>
+        <v>0.99811506665856298</v>
       </c>
       <c r="AB20">
-        <v>27.059822883365296</v>
+        <v>35.874797800938026</v>
       </c>
       <c r="AD20" t="s">
         <v>307</v>
@@ -8125,13 +8125,13 @@
         <v>572</v>
       </c>
       <c r="AN20" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="AO20">
-        <v>0.99872758388674931</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AP20">
-        <v>23.31941562731657</v>
+        <v>12.729766626457181</v>
       </c>
       <c r="AR20" t="s">
         <v>307</v>
@@ -8161,13 +8161,13 @@
         <v>641</v>
       </c>
       <c r="BB20" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="BC20">
-        <v>0.99705787611047647</v>
+        <v>0.99503061728845632</v>
       </c>
       <c r="BD20">
-        <v>516.05305554711185</v>
+        <v>669.38461499965297</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8232,16 +8232,16 @@
         <v>330</v>
       </c>
       <c r="Y21" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="Z21" t="s">
         <v>424</v>
       </c>
       <c r="AA21">
-        <v>0.99789789449716026</v>
+        <v>0.99852418793335518</v>
       </c>
       <c r="AB21">
-        <v>39.831307398714806</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AD21" t="s">
         <v>307</v>
@@ -8271,13 +8271,13 @@
         <v>573</v>
       </c>
       <c r="AN21" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="AO21">
-        <v>0.9975765595050764</v>
+        <v>0.99863161241655762</v>
       </c>
       <c r="AP21">
-        <v>31.560996462068374</v>
+        <v>48.306707937232645</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8342,16 +8342,16 @@
         <v>332</v>
       </c>
       <c r="Y22" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="Z22" t="s">
         <v>425</v>
       </c>
       <c r="AA22">
-        <v>0.99864365615724771</v>
+        <v>0.99713671217394562</v>
       </c>
       <c r="AB22">
-        <v>45.737867404715672</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AD22" t="s">
         <v>307</v>
@@ -8381,13 +8381,13 @@
         <v>574</v>
       </c>
       <c r="AN22" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="AO22">
-        <v>0.9980121476893673</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AP22">
-        <v>30.863466083156009</v>
+        <v>24.883658184919245</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>334</v>
       </c>
       <c r="Y23" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="Z23" t="s">
         <v>426</v>
       </c>
       <c r="AA23">
-        <v>0.9991052659747558</v>
+        <v>0.99774884372261763</v>
       </c>
       <c r="AB23">
-        <v>12.019055461720432</v>
+        <v>84.621736519387298</v>
       </c>
       <c r="AD23" t="s">
         <v>307</v>
@@ -8491,13 +8491,13 @@
         <v>575</v>
       </c>
       <c r="AN23" t="s">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="AO23">
-        <v>0.99811519908104196</v>
+        <v>0.9967210177786987</v>
       </c>
       <c r="AP23">
-        <v>41.186340097586395</v>
+        <v>34.34566125862937</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8562,16 +8562,16 @@
         <v>336</v>
       </c>
       <c r="Y24" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="Z24" t="s">
         <v>427</v>
       </c>
       <c r="AA24">
-        <v>0.99761913939972058</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AB24">
-        <v>32.256845956342154</v>
+        <v>23.861203412894469</v>
       </c>
       <c r="AD24" t="s">
         <v>307</v>
@@ -8601,13 +8601,13 @@
         <v>576</v>
       </c>
       <c r="AN24" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="AO24">
-        <v>0.99845480529905328</v>
+        <v>0.99777922331243873</v>
       </c>
       <c r="AP24">
-        <v>47.820994144128512</v>
+        <v>61.086483632538339</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>338</v>
       </c>
       <c r="Y25" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="Z25" t="s">
         <v>428</v>
       </c>
       <c r="AA25">
-        <v>0.99916488913437129</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AB25">
-        <v>15.260625790927634</v>
+        <v>40.332510468654611</v>
       </c>
       <c r="AD25" t="s">
         <v>307</v>
@@ -8711,13 +8711,13 @@
         <v>577</v>
       </c>
       <c r="AN25" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="AO25">
-        <v>0.9991052659747558</v>
+        <v>0.99777988747037838</v>
       </c>
       <c r="AP25">
-        <v>12.019055461720432</v>
+        <v>36.605495131795273</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8782,16 +8782,16 @@
         <v>340</v>
       </c>
       <c r="Y26" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="Z26" t="s">
         <v>429</v>
       </c>
       <c r="AA26">
-        <v>0.99921633401208909</v>
+        <v>0.99871805281197423</v>
       </c>
       <c r="AB26">
-        <v>12.729766626457181</v>
+        <v>25.256759506353582</v>
       </c>
       <c r="AD26" t="s">
         <v>307</v>
@@ -8821,13 +8821,13 @@
         <v>578</v>
       </c>
       <c r="AN26" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AO26">
-        <v>0.99850473493624492</v>
+        <v>0.99828876210676587</v>
       </c>
       <c r="AP26">
-        <v>27.496123184453968</v>
+        <v>28.334088028040785</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8892,16 +8892,16 @@
         <v>342</v>
       </c>
       <c r="Y27" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="Z27" t="s">
         <v>430</v>
       </c>
       <c r="AA27">
-        <v>0.99984169097848852</v>
+        <v>0.99637763901827192</v>
       </c>
       <c r="AB27">
-        <v>2.9143415731308986</v>
+        <v>48.031259731727893</v>
       </c>
       <c r="AD27" t="s">
         <v>307</v>
@@ -8931,13 +8931,13 @@
         <v>579</v>
       </c>
       <c r="AN27" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="AO27">
-        <v>0.9967210177786987</v>
+        <v>0.99839049347738307</v>
       </c>
       <c r="AP27">
-        <v>34.34566125862937</v>
+        <v>75.277133913292474</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9002,16 +9002,16 @@
         <v>344</v>
       </c>
       <c r="Y28" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="Z28" t="s">
         <v>431</v>
       </c>
       <c r="AA28">
-        <v>0.99818574894902312</v>
+        <v>0.99873544632009026</v>
       </c>
       <c r="AB28">
-        <v>33.253084498654445</v>
+        <v>34.387878972174441</v>
       </c>
       <c r="AD28" t="s">
         <v>307</v>
@@ -9041,13 +9041,13 @@
         <v>580</v>
       </c>
       <c r="AN28" t="s">
-        <v>417</v>
+        <v>464</v>
       </c>
       <c r="AO28">
-        <v>0.99777922331243873</v>
+        <v>0.99697913305259955</v>
       </c>
       <c r="AP28">
-        <v>61.086483632538339</v>
+        <v>58.519281729791345</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9112,16 +9112,16 @@
         <v>346</v>
       </c>
       <c r="Y29" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="Z29" t="s">
         <v>432</v>
       </c>
       <c r="AA29">
-        <v>0.99815889366481214</v>
+        <v>0.99755900053893942</v>
       </c>
       <c r="AB29">
-        <v>34.892661212818595</v>
+        <v>42.327567967950763</v>
       </c>
       <c r="AD29" t="s">
         <v>307</v>
@@ -9151,13 +9151,13 @@
         <v>581</v>
       </c>
       <c r="AN29" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="AO29">
-        <v>0.99777988747037838</v>
+        <v>0.99757778563357669</v>
       </c>
       <c r="AP29">
-        <v>36.605495131795273</v>
+        <v>45.221154662357485</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9222,16 +9222,16 @@
         <v>348</v>
       </c>
       <c r="Y30" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="Z30" t="s">
         <v>433</v>
       </c>
       <c r="AA30">
-        <v>0.99811506665856298</v>
+        <v>0.99776786767941794</v>
       </c>
       <c r="AB30">
-        <v>35.874797800938026</v>
+        <v>27.059822883365296</v>
       </c>
       <c r="AD30" t="s">
         <v>307</v>
@@ -9261,13 +9261,13 @@
         <v>582</v>
       </c>
       <c r="AN30" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="AO30">
-        <v>0.99839049347738307</v>
+        <v>0.99896573022887158</v>
       </c>
       <c r="AP30">
-        <v>75.277133913292474</v>
+        <v>18.936001260254645</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9332,16 +9332,16 @@
         <v>350</v>
       </c>
       <c r="Y31" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="Z31" t="s">
         <v>434</v>
       </c>
       <c r="AA31">
-        <v>0.99852418793335518</v>
+        <v>0.99789789449716026</v>
       </c>
       <c r="AB31">
-        <v>25.205687076233477</v>
+        <v>39.831307398714806</v>
       </c>
       <c r="AD31" t="s">
         <v>307</v>
@@ -9371,13 +9371,13 @@
         <v>583</v>
       </c>
       <c r="AN31" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="AO31">
-        <v>0.99697913305259955</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AP31">
-        <v>58.519281729791345</v>
+        <v>40.332510468654611</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9442,16 +9442,16 @@
         <v>352</v>
       </c>
       <c r="Y32" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="Z32" t="s">
         <v>435</v>
       </c>
       <c r="AA32">
-        <v>0.99713671217394562</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AB32">
-        <v>51.990142494672078</v>
+        <v>45.737867404715672</v>
       </c>
       <c r="AD32" t="s">
         <v>307</v>
@@ -9481,13 +9481,13 @@
         <v>584</v>
       </c>
       <c r="AN32" t="s">
-        <v>459</v>
+        <v>416</v>
       </c>
       <c r="AO32">
-        <v>0.99757778563357669</v>
+        <v>0.99871472031655018</v>
       </c>
       <c r="AP32">
-        <v>45.221154662357485</v>
+        <v>28.428965886446147</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9552,16 +9552,16 @@
         <v>354</v>
       </c>
       <c r="Y33" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="Z33" t="s">
         <v>436</v>
       </c>
       <c r="AA33">
-        <v>0.99774884372261763</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AB33">
-        <v>84.621736519387298</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AD33" t="s">
         <v>307</v>
@@ -9591,13 +9591,13 @@
         <v>585</v>
       </c>
       <c r="AN33" t="s">
-        <v>461</v>
+        <v>427</v>
       </c>
       <c r="AO33">
-        <v>0.99896573022887158</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AP33">
-        <v>18.936001260254645</v>
+        <v>23.861203412894469</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9662,16 +9662,16 @@
         <v>356</v>
       </c>
       <c r="Y34" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="Z34" t="s">
         <v>437</v>
       </c>
       <c r="AA34">
-        <v>0.99782029353787438</v>
+        <v>0.99762279320259084</v>
       </c>
       <c r="AB34">
-        <v>23.861203412894469</v>
+        <v>50.682816539915542</v>
       </c>
       <c r="AD34" t="s">
         <v>307</v>
@@ -9701,13 +9701,13 @@
         <v>586</v>
       </c>
       <c r="AN34" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="AO34">
-        <v>0.99813022065694434</v>
+        <v>0.9980121476893673</v>
       </c>
       <c r="AP34">
-        <v>40.332510468654611</v>
+        <v>30.863466083156009</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9772,16 +9772,16 @@
         <v>358</v>
       </c>
       <c r="Y35" t="s">
-        <v>305</v>
+        <v>267</v>
       </c>
       <c r="Z35" t="s">
         <v>438</v>
       </c>
       <c r="AA35">
-        <v>0.99813022065694434</v>
+        <v>0.99782727135381688</v>
       </c>
       <c r="AB35">
-        <v>40.332510468654611</v>
+        <v>30.875049982999808</v>
       </c>
       <c r="AD35" t="s">
         <v>307</v>
@@ -9814,10 +9814,10 @@
         <v>415</v>
       </c>
       <c r="AO35">
-        <v>0.99863161241655762</v>
+        <v>0.99811519908104196</v>
       </c>
       <c r="AP35">
-        <v>48.306707937232645</v>
+        <v>41.186340097586395</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9882,16 +9882,16 @@
         <v>360</v>
       </c>
       <c r="Y36" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="Z36" t="s">
         <v>439</v>
       </c>
       <c r="AA36">
-        <v>0.99871805281197423</v>
+        <v>0.99795655945864681</v>
       </c>
       <c r="AB36">
-        <v>25.256759506353582</v>
+        <v>75.277133913292474</v>
       </c>
       <c r="AD36" t="s">
         <v>307</v>
@@ -9921,13 +9921,13 @@
         <v>588</v>
       </c>
       <c r="AN36" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="AO36">
-        <v>0.99864365615724771</v>
+        <v>0.99649252363612195</v>
       </c>
       <c r="AP36">
-        <v>24.883658184919245</v>
+        <v>28.983218493781202</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9992,16 +9992,16 @@
         <v>362</v>
       </c>
       <c r="Y37" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="Z37" t="s">
         <v>440</v>
       </c>
       <c r="AA37">
-        <v>0.99637763901827192</v>
+        <v>0.99874893763362849</v>
       </c>
       <c r="AB37">
-        <v>48.031259731727893</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AD37" t="s">
         <v>307</v>
@@ -10031,13 +10031,13 @@
         <v>589</v>
       </c>
       <c r="AN37" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AO37">
-        <v>0.99885698485202501</v>
+        <v>0.99767811393002859</v>
       </c>
       <c r="AP37">
-        <v>25.256759506353582</v>
+        <v>30.875049982999808</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10102,16 +10102,16 @@
         <v>364</v>
       </c>
       <c r="Y38" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="Z38" t="s">
         <v>441</v>
       </c>
       <c r="AA38">
-        <v>0.99873544632009026</v>
+        <v>0.99814724525850784</v>
       </c>
       <c r="AB38">
-        <v>34.387878972174441</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AD38" t="s">
         <v>307</v>
@@ -10141,13 +10141,13 @@
         <v>590</v>
       </c>
       <c r="AN38" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="AO38">
-        <v>0.99709581552680626</v>
+        <v>0.99764304373832691</v>
       </c>
       <c r="AP38">
-        <v>53.231766754458491</v>
+        <v>42.327567967950763</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10212,16 +10212,16 @@
         <v>366</v>
       </c>
       <c r="Y39" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Z39" t="s">
         <v>442</v>
       </c>
       <c r="AA39">
-        <v>0.99762279320259084</v>
+        <v>0.99848201234520018</v>
       </c>
       <c r="AB39">
-        <v>50.682816539915542</v>
+        <v>72.463654284142635</v>
       </c>
       <c r="AD39" t="s">
         <v>307</v>
@@ -10251,13 +10251,13 @@
         <v>591</v>
       </c>
       <c r="AN39" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="AO39">
-        <v>0.99863950725251116</v>
+        <v>0.99790384243262886</v>
       </c>
       <c r="AP39">
-        <v>34.387878972174441</v>
+        <v>72.461220387375079</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10322,16 +10322,16 @@
         <v>368</v>
       </c>
       <c r="Y40" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="Z40" t="s">
         <v>443</v>
       </c>
       <c r="AA40">
-        <v>0.99782727135381688</v>
+        <v>0.99886290297361824</v>
       </c>
       <c r="AB40">
-        <v>30.875049982999808</v>
+        <v>26.622770797002293</v>
       </c>
       <c r="AD40" t="s">
         <v>307</v>
@@ -10361,13 +10361,13 @@
         <v>592</v>
       </c>
       <c r="AN40" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AO40">
-        <v>0.99837520457423046</v>
+        <v>0.99797028609854399</v>
       </c>
       <c r="AP40">
-        <v>29.909469717927731</v>
+        <v>34.892661212818595</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10432,16 +10432,16 @@
         <v>370</v>
       </c>
       <c r="Y41" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="Z41" t="s">
         <v>444</v>
       </c>
       <c r="AA41">
-        <v>0.99795655945864681</v>
+        <v>0.99779181951287421</v>
       </c>
       <c r="AB41">
-        <v>75.277133913292474</v>
+        <v>61.086483632538339</v>
       </c>
       <c r="AD41" t="s">
         <v>307</v>
@@ -10471,13 +10471,13 @@
         <v>593</v>
       </c>
       <c r="AN41" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="AO41">
-        <v>0.99751816641322844</v>
+        <v>0.99777778253795524</v>
       </c>
       <c r="AP41">
-        <v>45.1502695224383</v>
+        <v>36.020821886415746</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10542,16 +10542,16 @@
         <v>372</v>
       </c>
       <c r="Y42" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="Z42" t="s">
         <v>445</v>
       </c>
       <c r="AA42">
-        <v>0.99874893763362849</v>
+        <v>0.9978643471647114</v>
       </c>
       <c r="AB42">
-        <v>27.496123184453968</v>
+        <v>31.560996462068374</v>
       </c>
       <c r="AD42" t="s">
         <v>307</v>
@@ -10581,13 +10581,13 @@
         <v>594</v>
       </c>
       <c r="AN42" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AO42">
-        <v>0.99754431624006568</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AP42">
-        <v>32.256845956342154</v>
+        <v>23.107973955380711</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10652,16 +10652,16 @@
         <v>374</v>
       </c>
       <c r="Y43" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="Z43" t="s">
         <v>446</v>
       </c>
       <c r="AA43">
-        <v>0.99834689519829145</v>
+        <v>0.99789011269484895</v>
       </c>
       <c r="AB43">
-        <v>32.749623583141812</v>
+        <v>36.605495131795273</v>
       </c>
       <c r="AD43" t="s">
         <v>307</v>
@@ -10691,13 +10691,13 @@
         <v>595</v>
       </c>
       <c r="AN43" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AO43">
-        <v>0.99755521694544447</v>
+        <v>0.9975765595050764</v>
       </c>
       <c r="AP43">
-        <v>50.682816539915542</v>
+        <v>31.560996462068374</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10762,16 +10762,16 @@
         <v>376</v>
       </c>
       <c r="Y44" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="Z44" t="s">
         <v>447</v>
       </c>
       <c r="AA44">
-        <v>0.99853303004525662</v>
+        <v>0.99783121031362565</v>
       </c>
       <c r="AB44">
-        <v>18.693183403514499</v>
+        <v>51.165698000691506</v>
       </c>
       <c r="AD44" t="s">
         <v>307</v>
@@ -10801,13 +10801,13 @@
         <v>596</v>
       </c>
       <c r="AN44" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="AO44">
-        <v>0.99984169097848852</v>
+        <v>0.99751816641322844</v>
       </c>
       <c r="AP44">
-        <v>2.9143415731308986</v>
+        <v>45.1502695224383</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10872,16 +10872,16 @@
         <v>378</v>
       </c>
       <c r="Y45" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Z45" t="s">
         <v>448</v>
       </c>
       <c r="AA45">
-        <v>0.99751836673919181</v>
+        <v>0.99818636444109388</v>
       </c>
       <c r="AB45">
-        <v>50.515025114296037</v>
+        <v>45.221154662357485</v>
       </c>
       <c r="AD45" t="s">
         <v>307</v>
@@ -10911,13 +10911,13 @@
         <v>597</v>
       </c>
       <c r="AN45" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="AO45">
-        <v>0.99828876210676587</v>
+        <v>0.99754431624006568</v>
       </c>
       <c r="AP45">
-        <v>28.334088028040785</v>
+        <v>32.256845956342154</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10982,16 +10982,16 @@
         <v>380</v>
       </c>
       <c r="Y46" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="Z46" t="s">
         <v>449</v>
       </c>
       <c r="AA46">
-        <v>0.99774808836727491</v>
+        <v>0.99843994478948561</v>
       </c>
       <c r="AB46">
-        <v>41.186340097586395</v>
+        <v>28.334088028040785</v>
       </c>
       <c r="AD46" t="s">
         <v>307</v>
@@ -11021,13 +11021,13 @@
         <v>598</v>
       </c>
       <c r="AN46" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="AO46">
-        <v>0.99777778253795524</v>
+        <v>0.99755521694544447</v>
       </c>
       <c r="AP46">
-        <v>36.020821886415746</v>
+        <v>50.682816539915542</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -11092,16 +11092,16 @@
         <v>382</v>
       </c>
       <c r="Y47" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Z47" t="s">
         <v>450</v>
       </c>
       <c r="AA47">
-        <v>0.99828790514523624</v>
+        <v>0.9983322364125492</v>
       </c>
       <c r="AB47">
-        <v>28.428965886446147</v>
+        <v>27.248239083262582</v>
       </c>
       <c r="AD47" t="s">
         <v>307</v>
@@ -11131,13 +11131,13 @@
         <v>599</v>
       </c>
       <c r="AN47" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AO47">
-        <v>0.99649252363612195</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AP47">
-        <v>28.983218493781202</v>
+        <v>2.9143415731308986</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -11202,16 +11202,16 @@
         <v>384</v>
       </c>
       <c r="Y48" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="Z48" t="s">
         <v>451</v>
       </c>
       <c r="AA48">
-        <v>0.99679205626668776</v>
+        <v>0.99795611274367535</v>
       </c>
       <c r="AB48">
-        <v>28.983218493781202</v>
+        <v>29.909469717927731</v>
       </c>
       <c r="AD48" t="s">
         <v>307</v>
@@ -11241,13 +11241,13 @@
         <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="AO48">
-        <v>0.99767811393002859</v>
+        <v>0.99885698485202501</v>
       </c>
       <c r="AP48">
-        <v>30.875049982999808</v>
+        <v>25.256759506353582</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -11312,16 +11312,16 @@
         <v>386</v>
       </c>
       <c r="Y49" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="Z49" t="s">
         <v>452</v>
       </c>
       <c r="AA49">
-        <v>0.99713110094318969</v>
+        <v>0.99756835894174822</v>
       </c>
       <c r="AB49">
-        <v>34.34566125862937</v>
+        <v>36.020821886415746</v>
       </c>
       <c r="AD49" t="s">
         <v>307</v>
@@ -11351,13 +11351,13 @@
         <v>601</v>
       </c>
       <c r="AN49" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="AO49">
-        <v>0.99764304373832691</v>
+        <v>0.99709581552680626</v>
       </c>
       <c r="AP49">
-        <v>42.327567967950763</v>
+        <v>53.231766754458491</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -11422,16 +11422,16 @@
         <v>388</v>
       </c>
       <c r="Y50" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="Z50" t="s">
         <v>453</v>
       </c>
       <c r="AA50">
-        <v>0.99749963479302273</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AB50">
-        <v>49.14481327115881</v>
+        <v>23.31941562731657</v>
       </c>
       <c r="AD50" t="s">
         <v>307</v>
@@ -11461,13 +11461,13 @@
         <v>602</v>
       </c>
       <c r="AN50" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AO50">
-        <v>0.99790384243262886</v>
+        <v>0.99863950725251116</v>
       </c>
       <c r="AP50">
-        <v>72.461220387375079</v>
+        <v>34.387878972174441</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -11532,16 +11532,16 @@
         <v>390</v>
       </c>
       <c r="Y51" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="Z51" t="s">
         <v>454</v>
       </c>
       <c r="AA51">
-        <v>0.9985687661763365</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AB51">
-        <v>50.93040927578344</v>
+        <v>33.253084498654445</v>
       </c>
       <c r="AD51" t="s">
         <v>307</v>
@@ -11571,13 +11571,13 @@
         <v>603</v>
       </c>
       <c r="AN51" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="AO51">
-        <v>0.99797028609854399</v>
+        <v>0.99837520457423046</v>
       </c>
       <c r="AP51">
-        <v>34.892661212818595</v>
+        <v>29.909469717927731</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -11642,16 +11642,16 @@
         <v>392</v>
       </c>
       <c r="Y52" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Z52" t="s">
         <v>455</v>
       </c>
       <c r="AA52">
-        <v>0.9978643471647114</v>
+        <v>0.99751567592854107</v>
       </c>
       <c r="AB52">
-        <v>31.560996462068374</v>
+        <v>46.334800039670455</v>
       </c>
       <c r="AD52" t="s">
         <v>307</v>
@@ -11681,13 +11681,13 @@
         <v>604</v>
       </c>
       <c r="AN52" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AO52">
-        <v>0.99871472031655018</v>
+        <v>0.99632737337312927</v>
       </c>
       <c r="AP52">
-        <v>28.428965886446147</v>
+        <v>48.031259731727893</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -11752,16 +11752,16 @@
         <v>394</v>
       </c>
       <c r="Y53" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
       <c r="Z53" t="s">
         <v>456</v>
       </c>
       <c r="AA53">
-        <v>0.99789011269484895</v>
+        <v>0.99761913939972058</v>
       </c>
       <c r="AB53">
-        <v>36.605495131795273</v>
+        <v>32.256845956342154</v>
       </c>
       <c r="AD53" t="s">
         <v>307</v>
@@ -11791,13 +11791,13 @@
         <v>605</v>
       </c>
       <c r="AN53" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AO53">
-        <v>0.99782029353787438</v>
+        <v>0.99739127962445018</v>
       </c>
       <c r="AP53">
-        <v>23.861203412894469</v>
+        <v>39.831307398714806</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -11862,16 +11862,16 @@
         <v>396</v>
       </c>
       <c r="Y54" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="Z54" t="s">
         <v>457</v>
       </c>
       <c r="AA54">
-        <v>0.99783121031362565</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AB54">
-        <v>51.165698000691506</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AD54" t="s">
         <v>307</v>
@@ -11901,13 +11901,13 @@
         <v>606</v>
       </c>
       <c r="AN54" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="AO54">
-        <v>0.99837593922723478</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AP54">
-        <v>25.205687076233477</v>
+        <v>33.253084498654445</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -11972,16 +11972,16 @@
         <v>398</v>
       </c>
       <c r="Y55" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Z55" t="s">
         <v>458</v>
       </c>
       <c r="AA55">
-        <v>0.99751567592854107</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AB55">
-        <v>46.334800039670455</v>
+        <v>12.729766626457181</v>
       </c>
       <c r="AD55" t="s">
         <v>307</v>
@@ -12011,13 +12011,13 @@
         <v>607</v>
       </c>
       <c r="AN55" t="s">
-        <v>435</v>
+        <v>462</v>
       </c>
       <c r="AO55">
-        <v>0.99757815671697558</v>
+        <v>0.99853353101054187</v>
       </c>
       <c r="AP55">
-        <v>51.990142494672078</v>
+        <v>18.693183403514499</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -12082,16 +12082,16 @@
         <v>400</v>
       </c>
       <c r="Y56" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="Z56" t="s">
         <v>459</v>
       </c>
       <c r="AA56">
-        <v>0.99818636444109388</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AB56">
-        <v>45.221154662357485</v>
+        <v>2.9143415731308986</v>
       </c>
       <c r="AD56" t="s">
         <v>307</v>
@@ -12121,13 +12121,13 @@
         <v>608</v>
       </c>
       <c r="AN56" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="AO56">
-        <v>0.99916488913437129</v>
+        <v>0.99747843498043831</v>
       </c>
       <c r="AP56">
-        <v>15.260625790927634</v>
+        <v>46.334800039670455</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -12192,16 +12192,16 @@
         <v>402</v>
       </c>
       <c r="Y57" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Z57" t="s">
         <v>460</v>
       </c>
       <c r="AA57">
-        <v>0.99843994478948561</v>
+        <v>0.99815889366481214</v>
       </c>
       <c r="AB57">
-        <v>28.334088028040785</v>
+        <v>34.892661212818595</v>
       </c>
       <c r="AD57" t="s">
         <v>307</v>
@@ -12231,13 +12231,13 @@
         <v>609</v>
       </c>
       <c r="AN57" t="s">
-        <v>453</v>
+        <v>417</v>
       </c>
       <c r="AO57">
-        <v>0.99729296780855581</v>
+        <v>0.99466341005350978</v>
       </c>
       <c r="AP57">
-        <v>49.14481327115881</v>
+        <v>58.229467192272445</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -12302,16 +12302,16 @@
         <v>404</v>
       </c>
       <c r="Y58" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="Z58" t="s">
         <v>461</v>
       </c>
       <c r="AA58">
-        <v>0.9983322364125492</v>
+        <v>0.99834689519829145</v>
       </c>
       <c r="AB58">
-        <v>27.248239083262582</v>
+        <v>32.749623583141812</v>
       </c>
       <c r="AD58" t="s">
         <v>307</v>
@@ -12341,13 +12341,13 @@
         <v>610</v>
       </c>
       <c r="AN58" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="AO58">
-        <v>0.99921633401208909</v>
+        <v>0.9977732948939011</v>
       </c>
       <c r="AP58">
-        <v>12.729766626457181</v>
+        <v>51.165698000691506</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -12412,16 +12412,16 @@
         <v>406</v>
       </c>
       <c r="Y59" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="Z59" t="s">
         <v>462</v>
       </c>
       <c r="AA59">
-        <v>0.99795611274367535</v>
+        <v>0.99853303004525662</v>
       </c>
       <c r="AB59">
-        <v>29.909469717927731</v>
+        <v>18.693183403514499</v>
       </c>
       <c r="AD59" t="s">
         <v>307</v>
@@ -12451,13 +12451,13 @@
         <v>611</v>
       </c>
       <c r="AN59" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="AO59">
-        <v>0.99870289970840342</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AP59">
-        <v>23.107973955380711</v>
+        <v>23.31941562731657</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -12522,16 +12522,16 @@
         <v>408</v>
       </c>
       <c r="Y60" t="s">
-        <v>294</v>
+        <v>256</v>
       </c>
       <c r="Z60" t="s">
         <v>463</v>
       </c>
       <c r="AA60">
-        <v>0.99756835894174822</v>
+        <v>0.99754569173664964</v>
       </c>
       <c r="AB60">
-        <v>36.020821886415746</v>
+        <v>45.1502695224383</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -12596,16 +12596,16 @@
         <v>410</v>
       </c>
       <c r="Y61" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="Z61" t="s">
         <v>464</v>
       </c>
       <c r="AA61">
-        <v>0.99872758388674931</v>
+        <v>0.99697644816659792</v>
       </c>
       <c r="AB61">
-        <v>23.31941562731657</v>
+        <v>58.519281729791345</v>
       </c>
     </row>
   </sheetData>
@@ -12614,7 +12614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5F6D29-DB4D-440F-A1A6-8B925DD78339}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D6D1D7-AB38-4ECA-9138-BB5B1C4D7CFC}">
   <dimension ref="B9:Z59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12726,7 +12726,7 @@
         <v>642</v>
       </c>
       <c r="K11" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="L11">
         <v>0.64021427611097514</v>
@@ -12759,7 +12759,7 @@
         <v>740</v>
       </c>
       <c r="X11" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="Y11">
         <v>17.603249999999999</v>
@@ -12794,7 +12794,7 @@
         <v>644</v>
       </c>
       <c r="K12" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="L12">
         <v>3.683157674608327</v>
@@ -12827,7 +12827,7 @@
         <v>742</v>
       </c>
       <c r="X12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Y12">
         <v>11.58525</v>
@@ -12895,7 +12895,7 @@
         <v>744</v>
       </c>
       <c r="X13" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="Y13">
         <v>5.7000000000000002E-2</v>
@@ -12930,7 +12930,7 @@
         <v>648</v>
       </c>
       <c r="K14" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="L14">
         <v>2.5290705136145335</v>
@@ -12963,7 +12963,7 @@
         <v>746</v>
       </c>
       <c r="X14" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="Y14">
         <v>11.2965</v>
@@ -12998,7 +12998,7 @@
         <v>650</v>
       </c>
       <c r="K15" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="L15">
         <v>2.1620342624302693</v>
@@ -13031,7 +13031,7 @@
         <v>748</v>
       </c>
       <c r="X15" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="Y15">
         <v>0.83925000000000005</v>
@@ -13066,7 +13066,7 @@
         <v>652</v>
       </c>
       <c r="K16" t="s">
-        <v>606</v>
+        <v>568</v>
       </c>
       <c r="L16">
         <v>0.10228431008717309</v>
@@ -13099,7 +13099,7 @@
         <v>750</v>
       </c>
       <c r="X16" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="Y16">
         <v>2.0332499999999998</v>
@@ -13134,7 +13134,7 @@
         <v>654</v>
       </c>
       <c r="K17" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="L17">
         <v>0.26374115795515951</v>
@@ -13167,7 +13167,7 @@
         <v>752</v>
       </c>
       <c r="X17" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="Y17">
         <v>5.8237500000000004</v>
@@ -13202,7 +13202,7 @@
         <v>656</v>
       </c>
       <c r="K18" t="s">
-        <v>607</v>
+        <v>569</v>
       </c>
       <c r="L18">
         <v>1.0775690479395925</v>
@@ -13235,7 +13235,7 @@
         <v>754</v>
       </c>
       <c r="X18" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="Y18">
         <v>16.887</v>
@@ -13270,7 +13270,7 @@
         <v>658</v>
       </c>
       <c r="K19" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="L19">
         <v>1.644864133979123</v>
@@ -13303,7 +13303,7 @@
         <v>756</v>
       </c>
       <c r="X19" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="Y19">
         <v>17.089500000000001</v>
@@ -13338,7 +13338,7 @@
         <v>660</v>
       </c>
       <c r="K20" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L20">
         <v>4.1793335626386838</v>
@@ -13371,7 +13371,7 @@
         <v>758</v>
       </c>
       <c r="X20" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="Y20">
         <v>5.4255000000000004</v>
@@ -13406,7 +13406,7 @@
         <v>662</v>
       </c>
       <c r="K21" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="L21">
         <v>0.10220883742433164</v>
@@ -13441,7 +13441,7 @@
         <v>664</v>
       </c>
       <c r="K22" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="L22">
         <v>3.2456117052218421</v>
@@ -13476,7 +13476,7 @@
         <v>666</v>
       </c>
       <c r="K23" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="L23">
         <v>3.822617103272679</v>
@@ -13511,7 +13511,7 @@
         <v>668</v>
       </c>
       <c r="K24" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="L24">
         <v>0.18120178223038519</v>
@@ -13546,7 +13546,7 @@
         <v>670</v>
       </c>
       <c r="K25" t="s">
-        <v>565</v>
+        <v>604</v>
       </c>
       <c r="L25">
         <v>1.2636771265917695</v>
@@ -13581,7 +13581,7 @@
         <v>672</v>
       </c>
       <c r="K26" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="L26">
         <v>2.5500240416298969</v>
@@ -13616,7 +13616,7 @@
         <v>674</v>
       </c>
       <c r="K27" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="L27">
         <v>4.0346953063254611</v>
@@ -13651,7 +13651,7 @@
         <v>676</v>
       </c>
       <c r="K28" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="L28">
         <v>2.4674795572908166</v>
@@ -13686,7 +13686,7 @@
         <v>678</v>
       </c>
       <c r="K29" t="s">
-        <v>608</v>
+        <v>570</v>
       </c>
       <c r="L29">
         <v>0.19671799304243257</v>
@@ -13756,7 +13756,7 @@
         <v>682</v>
       </c>
       <c r="K31" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="L31">
         <v>0.70432433684539619</v>
@@ -13791,7 +13791,7 @@
         <v>684</v>
       </c>
       <c r="K32" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="L32">
         <v>0.14326997649193718</v>
@@ -13826,7 +13826,7 @@
         <v>686</v>
       </c>
       <c r="K33" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="L33">
         <v>2.5135228824118248E-2</v>
@@ -13861,7 +13861,7 @@
         <v>688</v>
       </c>
       <c r="K34" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="L34">
         <v>0.60333316217563482</v>
@@ -13896,7 +13896,7 @@
         <v>690</v>
       </c>
       <c r="K35" t="s">
-        <v>566</v>
+        <v>605</v>
       </c>
       <c r="L35">
         <v>0.61002023046213527</v>
@@ -13931,7 +13931,7 @@
         <v>692</v>
       </c>
       <c r="K36" t="s">
-        <v>604</v>
+        <v>584</v>
       </c>
       <c r="L36">
         <v>5.5124889677616896E-2</v>
@@ -13966,7 +13966,7 @@
         <v>694</v>
       </c>
       <c r="K37" t="s">
-        <v>567</v>
+        <v>606</v>
       </c>
       <c r="L37">
         <v>0.19696072330654418</v>
@@ -14001,7 +14001,7 @@
         <v>696</v>
       </c>
       <c r="K38" t="s">
-        <v>568</v>
+        <v>607</v>
       </c>
       <c r="L38">
         <v>0.37453679972687481</v>
@@ -14036,7 +14036,7 @@
         <v>698</v>
       </c>
       <c r="K39" t="s">
-        <v>609</v>
+        <v>571</v>
       </c>
       <c r="L39">
         <v>2.9266524214395733</v>
@@ -14071,7 +14071,7 @@
         <v>700</v>
       </c>
       <c r="K40" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="L40">
         <v>0.46102512715199689</v>
@@ -14106,7 +14106,7 @@
         <v>702</v>
       </c>
       <c r="K41" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -14141,7 +14141,7 @@
         <v>704</v>
       </c>
       <c r="K42" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="L42">
         <v>1.9780607647145438</v>
@@ -14176,7 +14176,7 @@
         <v>706</v>
       </c>
       <c r="K43" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="L43">
         <v>0.80689812107944159</v>
@@ -14211,7 +14211,7 @@
         <v>708</v>
       </c>
       <c r="K44" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="L44">
         <v>0.1886799653533156</v>
@@ -14246,7 +14246,7 @@
         <v>710</v>
       </c>
       <c r="K45" t="s">
-        <v>573</v>
+        <v>595</v>
       </c>
       <c r="L45">
         <v>2.577065692017253</v>
@@ -14281,7 +14281,7 @@
         <v>712</v>
       </c>
       <c r="K46" t="s">
-        <v>610</v>
+        <v>572</v>
       </c>
       <c r="L46">
         <v>0.32349873740765611</v>
@@ -14316,7 +14316,7 @@
         <v>714</v>
       </c>
       <c r="K47" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -14351,7 +14351,7 @@
         <v>716</v>
       </c>
       <c r="K48" t="s">
-        <v>569</v>
+        <v>608</v>
       </c>
       <c r="L48">
         <v>2.3210450729876548</v>
@@ -14386,7 +14386,7 @@
         <v>718</v>
       </c>
       <c r="K49" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="L49">
         <v>1.4641560353950904</v>
@@ -14421,7 +14421,7 @@
         <v>720</v>
       </c>
       <c r="K50" t="s">
-        <v>570</v>
+        <v>609</v>
       </c>
       <c r="L50">
         <v>4.3172734082397007E-3</v>
@@ -14456,7 +14456,7 @@
         <v>722</v>
       </c>
       <c r="K51" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="L51">
         <v>2.3327457542865271</v>
@@ -14491,7 +14491,7 @@
         <v>724</v>
       </c>
       <c r="K52" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="L52">
         <v>0.64220735366408732</v>
@@ -14526,7 +14526,7 @@
         <v>726</v>
       </c>
       <c r="K53" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="L53">
         <v>0.20805219904440039</v>
@@ -14561,7 +14561,7 @@
         <v>728</v>
       </c>
       <c r="K54" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="L54">
         <v>1.3018026354345156</v>
@@ -14596,7 +14596,7 @@
         <v>730</v>
       </c>
       <c r="K55" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="L55">
         <v>3.0871018425456893</v>
@@ -14631,7 +14631,7 @@
         <v>732</v>
       </c>
       <c r="K56" t="s">
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="L56">
         <v>3.1635610249840389</v>
@@ -14666,7 +14666,7 @@
         <v>734</v>
       </c>
       <c r="K57" t="s">
-        <v>572</v>
+        <v>611</v>
       </c>
       <c r="L57">
         <v>9.3245940212150449E-2</v>
@@ -14701,7 +14701,7 @@
         <v>736</v>
       </c>
       <c r="K58" t="s">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="L58">
         <v>0.28717016660662842</v>
@@ -14736,7 +14736,7 @@
         <v>738</v>
       </c>
       <c r="K59" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="L59">
         <v>0.93964202108728523</v>
@@ -14751,7 +14751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A768EA8-F20B-447B-9FE5-D126C235A138}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6876DEC9-A255-48A1-AA23-39A6941CDBC3}">
   <dimension ref="B9:Y159"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19812,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D17B4E08-782B-43B6-8131-847B45BF21D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B940BCC8-5E6C-4922-9170-484D6E629B09}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936CEFD3-7387-4E60-B74E-6CE72A6AFF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6842A01F-7BE8-4A3D-B9C9-7A0B3B840676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1014,6 +1014,60 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_041</t>
   </si>
   <si>
@@ -1026,6 +1080,90 @@
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_009</t>
   </si>
   <si>
@@ -1050,112 +1188,76 @@
     <t>connecting solar to buses in cluster 45</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
+    <t>distr_solelc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_005</t>
@@ -1200,108 +1302,6 @@
     <t>connecting solar to buses in cluster 48</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1317,12 +1317,81 @@
     <t>e_Mielec_POL</t>
   </si>
   <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>e_Lublin_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
     <t>e_KedzierzynKozle_POL</t>
   </si>
   <si>
     <t>e_Szczecin_POL</t>
   </si>
   <si>
+    <t>e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Siedlce_POL</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>e_Belchatow_POL</t>
+  </si>
+  <si>
+    <t>e_Zabrze_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
     <t>e_Slupsk_POL</t>
   </si>
   <si>
@@ -1335,58 +1404,40 @@
     <t>e_BielskoBiala_POL</t>
   </si>
   <si>
-    <t>e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL</t>
-  </si>
-  <si>
-    <t>e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Lublin_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Grudziadz_POL</t>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
   </si>
   <si>
     <t>e_Lukow_POL</t>
@@ -1410,55 +1461,184 @@
     <t>e_Wloclawek_POL</t>
   </si>
   <si>
-    <t>e_Lubin_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>e_Poznan_POL</t>
-  </si>
-  <si>
-    <t>e_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL</t>
-  </si>
-  <si>
-    <t>e_Siedlce_POL</t>
-  </si>
-  <si>
-    <t>e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>e_Belchatow_POL</t>
-  </si>
-  <si>
-    <t>e_Zabrze_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>e_Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>e_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>e_Grajewo_POL</t>
+    <t>distr_wonelc_won_POL_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_003</t>
@@ -1473,88 +1653,76 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_014</t>
@@ -1587,172 +1755,94 @@
     <t>connecting wind onshore to buses in cluster 49</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
   </si>
   <si>
     <t>elc_won_POL_003</t>
@@ -1761,46 +1851,40 @@
     <t>elc_won_POL_020</t>
   </si>
   <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>elc_won_POL_034</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>elc_won_POL_041</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>elc_won_POL_030</t>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
@@ -1818,88 +1902,58 @@
     <t>elc_won_POL_049</t>
   </si>
   <si>
-    <t>elc_won_POL_026</t>
-  </si>
-  <si>
-    <t>elc_won_POL_048</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>elc_won_POL_032</t>
-  </si>
-  <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
-    <t>elc_won_POL_042</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>elc_won_POL_037</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>elc_won_POL_023</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>elc_won_POL_025</t>
-  </si>
-  <si>
-    <t>elc_won_POL_027</t>
-  </si>
-  <si>
-    <t>elc_won_POL_028</t>
-  </si>
-  <si>
-    <t>elc_won_POL_038</t>
-  </si>
-  <si>
-    <t>elc_won_POL_040</t>
-  </si>
-  <si>
-    <t>elc_won_POL_046</t>
-  </si>
-  <si>
-    <t>elc_won_POL_047</t>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_002</t>
@@ -1908,88 +1962,34 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
   </si>
   <si>
     <t>elc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -6534,7 +6534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A8D779-F3C1-4A6E-9D6D-0A6F6C3A3C72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2A14DB-4FC5-41D4-8B66-8A79EC5CD875}">
   <dimension ref="B9:BD61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6811,13 +6811,13 @@
         <v>563</v>
       </c>
       <c r="AN11" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="AO11">
-        <v>0.99790284855194045</v>
+        <v>0.99777778253795524</v>
       </c>
       <c r="AP11">
-        <v>35.874797800938026</v>
+        <v>36.020821886415746</v>
       </c>
       <c r="AR11" t="s">
         <v>307</v>
@@ -6847,13 +6847,13 @@
         <v>632</v>
       </c>
       <c r="BB11" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="BC11">
-        <v>0.99478860441526007</v>
+        <v>0.99436455351944619</v>
       </c>
       <c r="BD11">
-        <v>610.20976015093845</v>
+        <v>728.41730490967211</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6957,13 +6957,13 @@
         <v>564</v>
       </c>
       <c r="AN12" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="AO12">
-        <v>0.99856107979091546</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AP12">
-        <v>26.622770797002293</v>
+        <v>23.107973955380711</v>
       </c>
       <c r="AR12" t="s">
         <v>307</v>
@@ -6993,13 +6993,13 @@
         <v>633</v>
       </c>
       <c r="BB12" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="BC12">
-        <v>0.99378504174620896</v>
+        <v>0.99784666475123052</v>
       </c>
       <c r="BD12">
-        <v>761.13276667340403</v>
+        <v>434.14794560012712</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7103,13 +7103,13 @@
         <v>565</v>
       </c>
       <c r="AN13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO13">
-        <v>0.99845480529905328</v>
+        <v>0.99649252363612195</v>
       </c>
       <c r="AP13">
-        <v>47.820994144128512</v>
+        <v>28.983218493781202</v>
       </c>
       <c r="AR13" t="s">
         <v>307</v>
@@ -7139,13 +7139,13 @@
         <v>634</v>
       </c>
       <c r="BB13" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="BC13">
-        <v>0.99671396210736585</v>
+        <v>0.99503061728845632</v>
       </c>
       <c r="BD13">
-        <v>535.75153841730867</v>
+        <v>669.38461499965297</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7210,16 +7210,16 @@
         <v>316</v>
       </c>
       <c r="Y14" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="Z14" t="s">
         <v>417</v>
       </c>
       <c r="AA14">
-        <v>0.9976031883518911</v>
+        <v>0.99762279320259084</v>
       </c>
       <c r="AB14">
-        <v>58.963512461864056</v>
+        <v>50.682816539915542</v>
       </c>
       <c r="AD14" t="s">
         <v>307</v>
@@ -7249,13 +7249,13 @@
         <v>566</v>
       </c>
       <c r="AN14" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="AO14">
-        <v>0.9991052659747558</v>
+        <v>0.99767811393002859</v>
       </c>
       <c r="AP14">
-        <v>12.019055461720432</v>
+        <v>30.875049982999808</v>
       </c>
       <c r="AR14" t="s">
         <v>307</v>
@@ -7285,13 +7285,13 @@
         <v>635</v>
       </c>
       <c r="BB14" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="BC14">
-        <v>0.99498581429447941</v>
+        <v>0.99635015248973569</v>
       </c>
       <c r="BD14">
-        <v>682.74537814765154</v>
+        <v>366.10125775280716</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7356,16 +7356,16 @@
         <v>318</v>
       </c>
       <c r="Y15" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="Z15" t="s">
         <v>418</v>
       </c>
       <c r="AA15">
-        <v>0.99870289970840342</v>
+        <v>0.99782727135381688</v>
       </c>
       <c r="AB15">
-        <v>23.107973955380711</v>
+        <v>30.875049982999808</v>
       </c>
       <c r="AD15" t="s">
         <v>307</v>
@@ -7395,13 +7395,13 @@
         <v>567</v>
       </c>
       <c r="AN15" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="AO15">
-        <v>0.99850473493624492</v>
+        <v>0.99764304373832691</v>
       </c>
       <c r="AP15">
-        <v>27.496123184453968</v>
+        <v>42.327567967950763</v>
       </c>
       <c r="AR15" t="s">
         <v>307</v>
@@ -7431,13 +7431,13 @@
         <v>636</v>
       </c>
       <c r="BB15" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="BC15">
-        <v>0.99705787611047647</v>
+        <v>0.99378504174620896</v>
       </c>
       <c r="BD15">
-        <v>516.05305554711185</v>
+        <v>761.13276667340403</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7502,16 +7502,16 @@
         <v>320</v>
       </c>
       <c r="Y16" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Z16" t="s">
         <v>419</v>
       </c>
       <c r="AA16">
-        <v>0.99679205626668776</v>
+        <v>0.99795655945864681</v>
       </c>
       <c r="AB16">
-        <v>28.983218493781202</v>
+        <v>75.277133913292474</v>
       </c>
       <c r="AD16" t="s">
         <v>307</v>
@@ -7541,13 +7541,13 @@
         <v>568</v>
       </c>
       <c r="AN16" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="AO16">
-        <v>0.99837593922723478</v>
+        <v>0.99790384243262886</v>
       </c>
       <c r="AP16">
-        <v>25.205687076233477</v>
+        <v>72.461220387375079</v>
       </c>
       <c r="AR16" t="s">
         <v>307</v>
@@ -7577,13 +7577,13 @@
         <v>637</v>
       </c>
       <c r="BB16" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="BC16">
-        <v>0.99635015248973569</v>
+        <v>0.99249606766869936</v>
       </c>
       <c r="BD16">
-        <v>366.10125775280716</v>
+        <v>661.89204677750558</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7648,16 +7648,16 @@
         <v>322</v>
       </c>
       <c r="Y17" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="Z17" t="s">
         <v>420</v>
       </c>
       <c r="AA17">
-        <v>0.99713110094318969</v>
+        <v>0.99874893763362849</v>
       </c>
       <c r="AB17">
-        <v>34.34566125862937</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AD17" t="s">
         <v>307</v>
@@ -7687,13 +7687,13 @@
         <v>569</v>
       </c>
       <c r="AN17" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="AO17">
-        <v>0.99757815671697558</v>
+        <v>0.99797028609854399</v>
       </c>
       <c r="AP17">
-        <v>51.990142494672078</v>
+        <v>34.892661212818595</v>
       </c>
       <c r="AR17" t="s">
         <v>307</v>
@@ -7723,13 +7723,13 @@
         <v>638</v>
       </c>
       <c r="BB17" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="BC17">
-        <v>0.99436455351944619</v>
+        <v>0.99671396210736585</v>
       </c>
       <c r="BD17">
-        <v>728.41730490967211</v>
+        <v>535.75153841730867</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7794,16 +7794,16 @@
         <v>324</v>
       </c>
       <c r="Y18" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="Z18" t="s">
         <v>421</v>
       </c>
       <c r="AA18">
-        <v>0.99749963479302273</v>
+        <v>0.99755900053893942</v>
       </c>
       <c r="AB18">
-        <v>49.14481327115881</v>
+        <v>42.327567967950763</v>
       </c>
       <c r="AD18" t="s">
         <v>307</v>
@@ -7833,13 +7833,13 @@
         <v>570</v>
       </c>
       <c r="AN18" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO18">
-        <v>0.99916488913437129</v>
+        <v>0.99863161241655762</v>
       </c>
       <c r="AP18">
-        <v>15.260625790927634</v>
+        <v>48.306707937232645</v>
       </c>
       <c r="AR18" t="s">
         <v>307</v>
@@ -7869,13 +7869,13 @@
         <v>639</v>
       </c>
       <c r="BB18" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="BC18">
-        <v>0.99249606766869936</v>
+        <v>0.99498581429447941</v>
       </c>
       <c r="BD18">
-        <v>661.89204677750558</v>
+        <v>682.74537814765154</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7940,16 +7940,16 @@
         <v>326</v>
       </c>
       <c r="Y19" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="Z19" t="s">
         <v>422</v>
       </c>
       <c r="AA19">
-        <v>0.9985687661763365</v>
+        <v>0.99776786767941794</v>
       </c>
       <c r="AB19">
-        <v>50.93040927578344</v>
+        <v>27.059822883365296</v>
       </c>
       <c r="AD19" t="s">
         <v>307</v>
@@ -7979,13 +7979,13 @@
         <v>571</v>
       </c>
       <c r="AN19" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AO19">
-        <v>0.99729296780855581</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AP19">
-        <v>49.14481327115881</v>
+        <v>24.883658184919245</v>
       </c>
       <c r="AR19" t="s">
         <v>307</v>
@@ -8015,13 +8015,13 @@
         <v>640</v>
       </c>
       <c r="BB19" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="BC19">
-        <v>0.99784666475123052</v>
+        <v>0.99705787611047647</v>
       </c>
       <c r="BD19">
-        <v>434.14794560012712</v>
+        <v>516.05305554711185</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8086,16 +8086,16 @@
         <v>328</v>
       </c>
       <c r="Y20" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="Z20" t="s">
         <v>423</v>
       </c>
       <c r="AA20">
-        <v>0.99811506665856298</v>
+        <v>0.99789789449716026</v>
       </c>
       <c r="AB20">
-        <v>35.874797800938026</v>
+        <v>39.831307398714806</v>
       </c>
       <c r="AD20" t="s">
         <v>307</v>
@@ -8128,10 +8128,10 @@
         <v>458</v>
       </c>
       <c r="AO20">
-        <v>0.99921633401208909</v>
+        <v>0.99845480529905328</v>
       </c>
       <c r="AP20">
-        <v>12.729766626457181</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AR20" t="s">
         <v>307</v>
@@ -8161,13 +8161,13 @@
         <v>641</v>
       </c>
       <c r="BB20" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="BC20">
-        <v>0.99503061728845632</v>
+        <v>0.99478860441526007</v>
       </c>
       <c r="BD20">
-        <v>669.38461499965297</v>
+        <v>610.20976015093845</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8232,16 +8232,16 @@
         <v>330</v>
       </c>
       <c r="Y21" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="Z21" t="s">
         <v>424</v>
       </c>
       <c r="AA21">
-        <v>0.99852418793335518</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AB21">
-        <v>25.205687076233477</v>
+        <v>45.737867404715672</v>
       </c>
       <c r="AD21" t="s">
         <v>307</v>
@@ -8271,13 +8271,13 @@
         <v>573</v>
       </c>
       <c r="AN21" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="AO21">
-        <v>0.99863161241655762</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AP21">
-        <v>48.306707937232645</v>
+        <v>12.019055461720432</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8342,16 +8342,16 @@
         <v>332</v>
       </c>
       <c r="Y22" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="Z22" t="s">
         <v>425</v>
       </c>
       <c r="AA22">
-        <v>0.99713671217394562</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AB22">
-        <v>51.990142494672078</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AD22" t="s">
         <v>307</v>
@@ -8381,13 +8381,13 @@
         <v>574</v>
       </c>
       <c r="AN22" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="AO22">
-        <v>0.99864365615724771</v>
+        <v>0.99850473493624492</v>
       </c>
       <c r="AP22">
-        <v>24.883658184919245</v>
+        <v>27.496123184453968</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>334</v>
       </c>
       <c r="Y23" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="Z23" t="s">
         <v>426</v>
       </c>
       <c r="AA23">
-        <v>0.99774884372261763</v>
+        <v>0.9976031883518911</v>
       </c>
       <c r="AB23">
-        <v>84.621736519387298</v>
+        <v>58.963512461864056</v>
       </c>
       <c r="AD23" t="s">
         <v>307</v>
@@ -8491,13 +8491,13 @@
         <v>575</v>
       </c>
       <c r="AN23" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="AO23">
-        <v>0.9967210177786987</v>
+        <v>0.99871472031655018</v>
       </c>
       <c r="AP23">
-        <v>34.34566125862937</v>
+        <v>28.428965886446147</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8562,16 +8562,16 @@
         <v>336</v>
       </c>
       <c r="Y24" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="Z24" t="s">
         <v>427</v>
       </c>
       <c r="AA24">
-        <v>0.99782029353787438</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AB24">
-        <v>23.861203412894469</v>
+        <v>23.107973955380711</v>
       </c>
       <c r="AD24" t="s">
         <v>307</v>
@@ -8601,13 +8601,13 @@
         <v>576</v>
       </c>
       <c r="AN24" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AO24">
-        <v>0.99777922331243873</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AP24">
-        <v>61.086483632538339</v>
+        <v>23.861203412894469</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>338</v>
       </c>
       <c r="Y25" t="s">
-        <v>305</v>
+        <v>255</v>
       </c>
       <c r="Z25" t="s">
         <v>428</v>
       </c>
       <c r="AA25">
-        <v>0.99813022065694434</v>
+        <v>0.99871805281197423</v>
       </c>
       <c r="AB25">
-        <v>40.332510468654611</v>
+        <v>25.256759506353582</v>
       </c>
       <c r="AD25" t="s">
         <v>307</v>
@@ -8711,13 +8711,13 @@
         <v>577</v>
       </c>
       <c r="AN25" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO25">
-        <v>0.99777988747037838</v>
+        <v>0.99828876210676587</v>
       </c>
       <c r="AP25">
-        <v>36.605495131795273</v>
+        <v>28.334088028040785</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8782,16 +8782,16 @@
         <v>340</v>
       </c>
       <c r="Y26" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="Z26" t="s">
         <v>429</v>
       </c>
       <c r="AA26">
-        <v>0.99871805281197423</v>
+        <v>0.99637763901827192</v>
       </c>
       <c r="AB26">
-        <v>25.256759506353582</v>
+        <v>48.031259731727893</v>
       </c>
       <c r="AD26" t="s">
         <v>307</v>
@@ -8821,13 +8821,13 @@
         <v>578</v>
       </c>
       <c r="AN26" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="AO26">
-        <v>0.99828876210676587</v>
+        <v>0.9980121476893673</v>
       </c>
       <c r="AP26">
-        <v>28.334088028040785</v>
+        <v>30.863466083156009</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8892,16 +8892,16 @@
         <v>342</v>
       </c>
       <c r="Y27" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="Z27" t="s">
         <v>430</v>
       </c>
       <c r="AA27">
-        <v>0.99637763901827192</v>
+        <v>0.99873544632009026</v>
       </c>
       <c r="AB27">
-        <v>48.031259731727893</v>
+        <v>34.387878972174441</v>
       </c>
       <c r="AD27" t="s">
         <v>307</v>
@@ -8931,13 +8931,13 @@
         <v>579</v>
       </c>
       <c r="AN27" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="AO27">
-        <v>0.99839049347738307</v>
+        <v>0.99811519908104196</v>
       </c>
       <c r="AP27">
-        <v>75.277133913292474</v>
+        <v>41.186340097586395</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9002,16 +9002,16 @@
         <v>344</v>
       </c>
       <c r="Y28" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="Z28" t="s">
         <v>431</v>
       </c>
       <c r="AA28">
-        <v>0.99873544632009026</v>
+        <v>0.99761913939972058</v>
       </c>
       <c r="AB28">
-        <v>34.387878972174441</v>
+        <v>32.256845956342154</v>
       </c>
       <c r="AD28" t="s">
         <v>307</v>
@@ -9041,13 +9041,13 @@
         <v>580</v>
       </c>
       <c r="AN28" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="AO28">
-        <v>0.99697913305259955</v>
+        <v>0.9967210177786987</v>
       </c>
       <c r="AP28">
-        <v>58.519281729791345</v>
+        <v>34.34566125862937</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9112,16 +9112,16 @@
         <v>346</v>
       </c>
       <c r="Y29" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Z29" t="s">
         <v>432</v>
       </c>
       <c r="AA29">
-        <v>0.99755900053893942</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AB29">
-        <v>42.327567967950763</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AD29" t="s">
         <v>307</v>
@@ -9151,13 +9151,13 @@
         <v>581</v>
       </c>
       <c r="AN29" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="AO29">
-        <v>0.99757778563357669</v>
+        <v>0.99777922331243873</v>
       </c>
       <c r="AP29">
-        <v>45.221154662357485</v>
+        <v>61.086483632538339</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9222,16 +9222,16 @@
         <v>348</v>
       </c>
       <c r="Y30" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="Z30" t="s">
         <v>433</v>
       </c>
       <c r="AA30">
-        <v>0.99776786767941794</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AB30">
-        <v>27.059822883365296</v>
+        <v>12.729766626457181</v>
       </c>
       <c r="AD30" t="s">
         <v>307</v>
@@ -9261,13 +9261,13 @@
         <v>582</v>
       </c>
       <c r="AN30" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="AO30">
-        <v>0.99896573022887158</v>
+        <v>0.99777988747037838</v>
       </c>
       <c r="AP30">
-        <v>18.936001260254645</v>
+        <v>36.605495131795273</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9332,16 +9332,16 @@
         <v>350</v>
       </c>
       <c r="Y31" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="Z31" t="s">
         <v>434</v>
       </c>
       <c r="AA31">
-        <v>0.99789789449716026</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AB31">
-        <v>39.831307398714806</v>
+        <v>2.9143415731308986</v>
       </c>
       <c r="AD31" t="s">
         <v>307</v>
@@ -9371,13 +9371,13 @@
         <v>583</v>
       </c>
       <c r="AN31" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="AO31">
-        <v>0.99813022065694434</v>
+        <v>0.99751816641322844</v>
       </c>
       <c r="AP31">
-        <v>40.332510468654611</v>
+        <v>45.1502695224383</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9442,16 +9442,16 @@
         <v>352</v>
       </c>
       <c r="Y32" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Z32" t="s">
         <v>435</v>
       </c>
       <c r="AA32">
-        <v>0.99864365615724771</v>
+        <v>0.99815889366481214</v>
       </c>
       <c r="AB32">
-        <v>45.737867404715672</v>
+        <v>34.892661212818595</v>
       </c>
       <c r="AD32" t="s">
         <v>307</v>
@@ -9481,13 +9481,13 @@
         <v>584</v>
       </c>
       <c r="AN32" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="AO32">
-        <v>0.99871472031655018</v>
+        <v>0.99754431624006568</v>
       </c>
       <c r="AP32">
-        <v>28.428965886446147</v>
+        <v>32.256845956342154</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9552,16 +9552,16 @@
         <v>354</v>
       </c>
       <c r="Y33" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="Z33" t="s">
         <v>436</v>
       </c>
       <c r="AA33">
-        <v>0.9991052659747558</v>
+        <v>0.99811506665856298</v>
       </c>
       <c r="AB33">
-        <v>12.019055461720432</v>
+        <v>35.874797800938026</v>
       </c>
       <c r="AD33" t="s">
         <v>307</v>
@@ -9591,13 +9591,13 @@
         <v>585</v>
       </c>
       <c r="AN33" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="AO33">
-        <v>0.99782029353787438</v>
+        <v>0.99755521694544447</v>
       </c>
       <c r="AP33">
-        <v>23.861203412894469</v>
+        <v>50.682816539915542</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9662,16 +9662,16 @@
         <v>356</v>
       </c>
       <c r="Y34" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Z34" t="s">
         <v>437</v>
       </c>
       <c r="AA34">
-        <v>0.99762279320259084</v>
+        <v>0.99852418793335518</v>
       </c>
       <c r="AB34">
-        <v>50.682816539915542</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AD34" t="s">
         <v>307</v>
@@ -9701,13 +9701,13 @@
         <v>586</v>
       </c>
       <c r="AN34" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="AO34">
-        <v>0.9980121476893673</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AP34">
-        <v>30.863466083156009</v>
+        <v>2.9143415731308986</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9772,16 +9772,16 @@
         <v>358</v>
       </c>
       <c r="Y35" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="Z35" t="s">
         <v>438</v>
       </c>
       <c r="AA35">
-        <v>0.99782727135381688</v>
+        <v>0.99713671217394562</v>
       </c>
       <c r="AB35">
-        <v>30.875049982999808</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AD35" t="s">
         <v>307</v>
@@ -9811,13 +9811,13 @@
         <v>587</v>
       </c>
       <c r="AN35" t="s">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="AO35">
-        <v>0.99811519908104196</v>
+        <v>0.9975765595050764</v>
       </c>
       <c r="AP35">
-        <v>41.186340097586395</v>
+        <v>31.560996462068374</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9882,16 +9882,16 @@
         <v>360</v>
       </c>
       <c r="Y36" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Z36" t="s">
         <v>439</v>
       </c>
       <c r="AA36">
-        <v>0.99795655945864681</v>
+        <v>0.99774884372261763</v>
       </c>
       <c r="AB36">
-        <v>75.277133913292474</v>
+        <v>84.621736519387298</v>
       </c>
       <c r="AD36" t="s">
         <v>307</v>
@@ -9921,13 +9921,13 @@
         <v>588</v>
       </c>
       <c r="AN36" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="AO36">
-        <v>0.99649252363612195</v>
+        <v>0.99837593922723478</v>
       </c>
       <c r="AP36">
-        <v>28.983218493781202</v>
+        <v>25.205687076233477</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9992,16 +9992,16 @@
         <v>362</v>
       </c>
       <c r="Y37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Z37" t="s">
         <v>440</v>
       </c>
       <c r="AA37">
-        <v>0.99874893763362849</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AB37">
-        <v>27.496123184453968</v>
+        <v>23.861203412894469</v>
       </c>
       <c r="AD37" t="s">
         <v>307</v>
@@ -10034,10 +10034,10 @@
         <v>438</v>
       </c>
       <c r="AO37">
-        <v>0.99767811393002859</v>
+        <v>0.99757815671697558</v>
       </c>
       <c r="AP37">
-        <v>30.875049982999808</v>
+        <v>51.990142494672078</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10102,16 +10102,16 @@
         <v>364</v>
       </c>
       <c r="Y38" t="s">
-        <v>259</v>
+        <v>305</v>
       </c>
       <c r="Z38" t="s">
         <v>441</v>
       </c>
       <c r="AA38">
-        <v>0.99814724525850784</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AB38">
-        <v>47.820994144128512</v>
+        <v>40.332510468654611</v>
       </c>
       <c r="AD38" t="s">
         <v>307</v>
@@ -10144,10 +10144,10 @@
         <v>432</v>
       </c>
       <c r="AO38">
-        <v>0.99764304373832691</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AP38">
-        <v>42.327567967950763</v>
+        <v>15.260625790927634</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10212,16 +10212,16 @@
         <v>366</v>
       </c>
       <c r="Y39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Z39" t="s">
         <v>442</v>
       </c>
       <c r="AA39">
-        <v>0.99848201234520018</v>
+        <v>0.99679205626668776</v>
       </c>
       <c r="AB39">
-        <v>72.463654284142635</v>
+        <v>28.983218493781202</v>
       </c>
       <c r="AD39" t="s">
         <v>307</v>
@@ -10251,13 +10251,13 @@
         <v>591</v>
       </c>
       <c r="AN39" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="AO39">
-        <v>0.99790384243262886</v>
+        <v>0.99729296780855581</v>
       </c>
       <c r="AP39">
-        <v>72.461220387375079</v>
+        <v>49.14481327115881</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10322,16 +10322,16 @@
         <v>368</v>
       </c>
       <c r="Y40" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="Z40" t="s">
         <v>443</v>
       </c>
       <c r="AA40">
-        <v>0.99886290297361824</v>
+        <v>0.99713110094318969</v>
       </c>
       <c r="AB40">
-        <v>26.622770797002293</v>
+        <v>34.34566125862937</v>
       </c>
       <c r="AD40" t="s">
         <v>307</v>
@@ -10361,13 +10361,13 @@
         <v>592</v>
       </c>
       <c r="AN40" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="AO40">
-        <v>0.99797028609854399</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AP40">
-        <v>34.892661212818595</v>
+        <v>12.729766626457181</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10432,16 +10432,16 @@
         <v>370</v>
       </c>
       <c r="Y41" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="Z41" t="s">
         <v>444</v>
       </c>
       <c r="AA41">
-        <v>0.99779181951287421</v>
+        <v>0.99749963479302273</v>
       </c>
       <c r="AB41">
-        <v>61.086483632538339</v>
+        <v>49.14481327115881</v>
       </c>
       <c r="AD41" t="s">
         <v>307</v>
@@ -10471,13 +10471,13 @@
         <v>593</v>
       </c>
       <c r="AN41" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="AO41">
-        <v>0.99777778253795524</v>
+        <v>0.99790284855194045</v>
       </c>
       <c r="AP41">
-        <v>36.020821886415746</v>
+        <v>35.874797800938026</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10542,16 +10542,16 @@
         <v>372</v>
       </c>
       <c r="Y42" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="Z42" t="s">
         <v>445</v>
       </c>
       <c r="AA42">
-        <v>0.9978643471647114</v>
+        <v>0.9985687661763365</v>
       </c>
       <c r="AB42">
-        <v>31.560996462068374</v>
+        <v>50.93040927578344</v>
       </c>
       <c r="AD42" t="s">
         <v>307</v>
@@ -10581,13 +10581,13 @@
         <v>594</v>
       </c>
       <c r="AN42" t="s">
-        <v>418</v>
+        <v>460</v>
       </c>
       <c r="AO42">
-        <v>0.99870289970840342</v>
+        <v>0.99856107979091546</v>
       </c>
       <c r="AP42">
-        <v>23.107973955380711</v>
+        <v>26.622770797002293</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10652,16 +10652,16 @@
         <v>374</v>
       </c>
       <c r="Y43" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="Z43" t="s">
         <v>446</v>
       </c>
       <c r="AA43">
-        <v>0.99789011269484895</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AB43">
-        <v>36.605495131795273</v>
+        <v>33.253084498654445</v>
       </c>
       <c r="AD43" t="s">
         <v>307</v>
@@ -10691,13 +10691,13 @@
         <v>595</v>
       </c>
       <c r="AN43" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="AO43">
-        <v>0.9975765595050764</v>
+        <v>0.99632737337312927</v>
       </c>
       <c r="AP43">
-        <v>31.560996462068374</v>
+        <v>48.031259731727893</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10762,16 +10762,16 @@
         <v>376</v>
       </c>
       <c r="Y44" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="Z44" t="s">
         <v>447</v>
       </c>
       <c r="AA44">
-        <v>0.99783121031362565</v>
+        <v>0.99818636444109388</v>
       </c>
       <c r="AB44">
-        <v>51.165698000691506</v>
+        <v>45.221154662357485</v>
       </c>
       <c r="AD44" t="s">
         <v>307</v>
@@ -10801,13 +10801,13 @@
         <v>596</v>
       </c>
       <c r="AN44" t="s">
-        <v>463</v>
+        <v>423</v>
       </c>
       <c r="AO44">
-        <v>0.99751816641322844</v>
+        <v>0.99739127962445018</v>
       </c>
       <c r="AP44">
-        <v>45.1502695224383</v>
+        <v>39.831307398714806</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10872,16 +10872,16 @@
         <v>378</v>
       </c>
       <c r="Y45" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="Z45" t="s">
         <v>448</v>
       </c>
       <c r="AA45">
-        <v>0.99818636444109388</v>
+        <v>0.99843994478948561</v>
       </c>
       <c r="AB45">
-        <v>45.221154662357485</v>
+        <v>28.334088028040785</v>
       </c>
       <c r="AD45" t="s">
         <v>307</v>
@@ -10911,13 +10911,13 @@
         <v>597</v>
       </c>
       <c r="AN45" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="AO45">
-        <v>0.99754431624006568</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AP45">
-        <v>32.256845956342154</v>
+        <v>33.253084498654445</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10982,16 +10982,16 @@
         <v>380</v>
       </c>
       <c r="Y46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z46" t="s">
         <v>449</v>
       </c>
       <c r="AA46">
-        <v>0.99843994478948561</v>
+        <v>0.9983322364125492</v>
       </c>
       <c r="AB46">
-        <v>28.334088028040785</v>
+        <v>27.248239083262582</v>
       </c>
       <c r="AD46" t="s">
         <v>307</v>
@@ -11021,13 +11021,13 @@
         <v>598</v>
       </c>
       <c r="AN46" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="AO46">
-        <v>0.99755521694544447</v>
+        <v>0.99853353101054187</v>
       </c>
       <c r="AP46">
-        <v>50.682816539915542</v>
+        <v>18.693183403514499</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -11092,16 +11092,16 @@
         <v>382</v>
       </c>
       <c r="Y47" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Z47" t="s">
         <v>450</v>
       </c>
       <c r="AA47">
-        <v>0.9983322364125492</v>
+        <v>0.99795611274367535</v>
       </c>
       <c r="AB47">
-        <v>27.248239083262582</v>
+        <v>29.909469717927731</v>
       </c>
       <c r="AD47" t="s">
         <v>307</v>
@@ -11131,13 +11131,13 @@
         <v>599</v>
       </c>
       <c r="AN47" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AO47">
-        <v>0.99984169097848852</v>
+        <v>0.99747843498043831</v>
       </c>
       <c r="AP47">
-        <v>2.9143415731308986</v>
+        <v>46.334800039670455</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -11202,16 +11202,16 @@
         <v>384</v>
       </c>
       <c r="Y48" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="Z48" t="s">
         <v>451</v>
       </c>
       <c r="AA48">
-        <v>0.99795611274367535</v>
+        <v>0.99756835894174822</v>
       </c>
       <c r="AB48">
-        <v>29.909469717927731</v>
+        <v>36.020821886415746</v>
       </c>
       <c r="AD48" t="s">
         <v>307</v>
@@ -11241,13 +11241,13 @@
         <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AO48">
-        <v>0.99885698485202501</v>
+        <v>0.99466341005350978</v>
       </c>
       <c r="AP48">
-        <v>25.256759506353582</v>
+        <v>58.229467192272445</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -11312,16 +11312,16 @@
         <v>386</v>
       </c>
       <c r="Y49" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="Z49" t="s">
         <v>452</v>
       </c>
       <c r="AA49">
-        <v>0.99756835894174822</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AB49">
-        <v>36.020821886415746</v>
+        <v>23.31941562731657</v>
       </c>
       <c r="AD49" t="s">
         <v>307</v>
@@ -11351,13 +11351,13 @@
         <v>601</v>
       </c>
       <c r="AN49" t="s">
-        <v>414</v>
+        <v>464</v>
       </c>
       <c r="AO49">
-        <v>0.99709581552680626</v>
+        <v>0.9977732948939011</v>
       </c>
       <c r="AP49">
-        <v>53.231766754458491</v>
+        <v>51.165698000691506</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -11422,16 +11422,16 @@
         <v>388</v>
       </c>
       <c r="Y50" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="Z50" t="s">
         <v>453</v>
       </c>
       <c r="AA50">
-        <v>0.99872758388674931</v>
+        <v>0.99754569173664964</v>
       </c>
       <c r="AB50">
-        <v>23.31941562731657</v>
+        <v>45.1502695224383</v>
       </c>
       <c r="AD50" t="s">
         <v>307</v>
@@ -11461,13 +11461,13 @@
         <v>602</v>
       </c>
       <c r="AN50" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="AO50">
-        <v>0.99863950725251116</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AP50">
-        <v>34.387878972174441</v>
+        <v>23.31941562731657</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -11532,16 +11532,16 @@
         <v>390</v>
       </c>
       <c r="Y51" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="Z51" t="s">
         <v>454</v>
       </c>
       <c r="AA51">
-        <v>0.99818574894902312</v>
+        <v>0.99697644816659792</v>
       </c>
       <c r="AB51">
-        <v>33.253084498654445</v>
+        <v>58.519281729791345</v>
       </c>
       <c r="AD51" t="s">
         <v>307</v>
@@ -11571,13 +11571,13 @@
         <v>603</v>
       </c>
       <c r="AN51" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="AO51">
-        <v>0.99837520457423046</v>
+        <v>0.99885698485202501</v>
       </c>
       <c r="AP51">
-        <v>29.909469717927731</v>
+        <v>25.256759506353582</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -11681,13 +11681,13 @@
         <v>604</v>
       </c>
       <c r="AN52" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="AO52">
-        <v>0.99632737337312927</v>
+        <v>0.99709581552680626</v>
       </c>
       <c r="AP52">
-        <v>48.031259731727893</v>
+        <v>53.231766754458491</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -11752,16 +11752,16 @@
         <v>394</v>
       </c>
       <c r="Y53" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="Z53" t="s">
         <v>456</v>
       </c>
       <c r="AA53">
-        <v>0.99761913939972058</v>
+        <v>0.99834689519829145</v>
       </c>
       <c r="AB53">
-        <v>32.256845956342154</v>
+        <v>32.749623583141812</v>
       </c>
       <c r="AD53" t="s">
         <v>307</v>
@@ -11791,13 +11791,13 @@
         <v>605</v>
       </c>
       <c r="AN53" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="AO53">
-        <v>0.99739127962445018</v>
+        <v>0.99863950725251116</v>
       </c>
       <c r="AP53">
-        <v>39.831307398714806</v>
+        <v>34.387878972174441</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -11862,16 +11862,16 @@
         <v>396</v>
       </c>
       <c r="Y54" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="Z54" t="s">
         <v>457</v>
       </c>
       <c r="AA54">
-        <v>0.99916488913437129</v>
+        <v>0.99853303004525662</v>
       </c>
       <c r="AB54">
-        <v>15.260625790927634</v>
+        <v>18.693183403514499</v>
       </c>
       <c r="AD54" t="s">
         <v>307</v>
@@ -11901,13 +11901,13 @@
         <v>606</v>
       </c>
       <c r="AN54" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AO54">
-        <v>0.99818574894902312</v>
+        <v>0.99837520457423046</v>
       </c>
       <c r="AP54">
-        <v>33.253084498654445</v>
+        <v>29.909469717927731</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -11972,16 +11972,16 @@
         <v>398</v>
       </c>
       <c r="Y55" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="Z55" t="s">
         <v>458</v>
       </c>
       <c r="AA55">
-        <v>0.99921633401208909</v>
+        <v>0.99814724525850784</v>
       </c>
       <c r="AB55">
-        <v>12.729766626457181</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AD55" t="s">
         <v>307</v>
@@ -12011,13 +12011,13 @@
         <v>607</v>
       </c>
       <c r="AN55" t="s">
-        <v>462</v>
+        <v>419</v>
       </c>
       <c r="AO55">
-        <v>0.99853353101054187</v>
+        <v>0.99839049347738307</v>
       </c>
       <c r="AP55">
-        <v>18.693183403514499</v>
+        <v>75.277133913292474</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -12082,16 +12082,16 @@
         <v>400</v>
       </c>
       <c r="Y56" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="Z56" t="s">
         <v>459</v>
       </c>
       <c r="AA56">
-        <v>0.99984169097848852</v>
+        <v>0.99848201234520018</v>
       </c>
       <c r="AB56">
-        <v>2.9143415731308986</v>
+        <v>72.463654284142635</v>
       </c>
       <c r="AD56" t="s">
         <v>307</v>
@@ -12121,13 +12121,13 @@
         <v>608</v>
       </c>
       <c r="AN56" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO56">
-        <v>0.99747843498043831</v>
+        <v>0.99697913305259955</v>
       </c>
       <c r="AP56">
-        <v>46.334800039670455</v>
+        <v>58.519281729791345</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -12192,16 +12192,16 @@
         <v>402</v>
       </c>
       <c r="Y57" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="Z57" t="s">
         <v>460</v>
       </c>
       <c r="AA57">
-        <v>0.99815889366481214</v>
+        <v>0.99886290297361824</v>
       </c>
       <c r="AB57">
-        <v>34.892661212818595</v>
+        <v>26.622770797002293</v>
       </c>
       <c r="AD57" t="s">
         <v>307</v>
@@ -12231,13 +12231,13 @@
         <v>609</v>
       </c>
       <c r="AN57" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="AO57">
-        <v>0.99466341005350978</v>
+        <v>0.99757778563357669</v>
       </c>
       <c r="AP57">
-        <v>58.229467192272445</v>
+        <v>45.221154662357485</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -12302,16 +12302,16 @@
         <v>404</v>
       </c>
       <c r="Y58" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="Z58" t="s">
         <v>461</v>
       </c>
       <c r="AA58">
-        <v>0.99834689519829145</v>
+        <v>0.99779181951287421</v>
       </c>
       <c r="AB58">
-        <v>32.749623583141812</v>
+        <v>61.086483632538339</v>
       </c>
       <c r="AD58" t="s">
         <v>307</v>
@@ -12341,13 +12341,13 @@
         <v>610</v>
       </c>
       <c r="AN58" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO58">
-        <v>0.9977732948939011</v>
+        <v>0.99896573022887158</v>
       </c>
       <c r="AP58">
-        <v>51.165698000691506</v>
+        <v>18.936001260254645</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -12412,16 +12412,16 @@
         <v>406</v>
       </c>
       <c r="Y59" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="Z59" t="s">
         <v>462</v>
       </c>
       <c r="AA59">
-        <v>0.99853303004525662</v>
+        <v>0.9978643471647114</v>
       </c>
       <c r="AB59">
-        <v>18.693183403514499</v>
+        <v>31.560996462068374</v>
       </c>
       <c r="AD59" t="s">
         <v>307</v>
@@ -12451,13 +12451,13 @@
         <v>611</v>
       </c>
       <c r="AN59" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="AO59">
-        <v>0.99872758388674931</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AP59">
-        <v>23.31941562731657</v>
+        <v>40.332510468654611</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -12522,16 +12522,16 @@
         <v>408</v>
       </c>
       <c r="Y60" t="s">
-        <v>256</v>
+        <v>301</v>
       </c>
       <c r="Z60" t="s">
         <v>463</v>
       </c>
       <c r="AA60">
-        <v>0.99754569173664964</v>
+        <v>0.99789011269484895</v>
       </c>
       <c r="AB60">
-        <v>45.1502695224383</v>
+        <v>36.605495131795273</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -12596,16 +12596,16 @@
         <v>410</v>
       </c>
       <c r="Y61" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="Z61" t="s">
         <v>464</v>
       </c>
       <c r="AA61">
-        <v>0.99697644816659792</v>
+        <v>0.99783121031362565</v>
       </c>
       <c r="AB61">
-        <v>58.519281729791345</v>
+        <v>51.165698000691506</v>
       </c>
     </row>
   </sheetData>
@@ -12614,7 +12614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D6D1D7-AB38-4ECA-9138-BB5B1C4D7CFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259CDCD2-D204-4312-8B36-34116D1F80AC}">
   <dimension ref="B9:Z59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12726,7 +12726,7 @@
         <v>642</v>
       </c>
       <c r="K11" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="L11">
         <v>0.64021427611097514</v>
@@ -12759,7 +12759,7 @@
         <v>740</v>
       </c>
       <c r="X11" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="Y11">
         <v>17.603249999999999</v>
@@ -12794,7 +12794,7 @@
         <v>644</v>
       </c>
       <c r="K12" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="L12">
         <v>3.683157674608327</v>
@@ -12827,7 +12827,7 @@
         <v>742</v>
       </c>
       <c r="X12" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="Y12">
         <v>11.58525</v>
@@ -12862,7 +12862,7 @@
         <v>646</v>
       </c>
       <c r="K13" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="L13">
         <v>1.1133782162108721</v>
@@ -12895,7 +12895,7 @@
         <v>744</v>
       </c>
       <c r="X13" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="Y13">
         <v>5.7000000000000002E-2</v>
@@ -12930,7 +12930,7 @@
         <v>648</v>
       </c>
       <c r="K14" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="L14">
         <v>2.5290705136145335</v>
@@ -12963,7 +12963,7 @@
         <v>746</v>
       </c>
       <c r="X14" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="Y14">
         <v>11.2965</v>
@@ -12998,7 +12998,7 @@
         <v>650</v>
       </c>
       <c r="K15" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="L15">
         <v>2.1620342624302693</v>
@@ -13031,7 +13031,7 @@
         <v>748</v>
       </c>
       <c r="X15" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="Y15">
         <v>0.83925000000000005</v>
@@ -13066,7 +13066,7 @@
         <v>652</v>
       </c>
       <c r="K16" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="L16">
         <v>0.10228431008717309</v>
@@ -13099,7 +13099,7 @@
         <v>750</v>
       </c>
       <c r="X16" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="Y16">
         <v>2.0332499999999998</v>
@@ -13134,7 +13134,7 @@
         <v>654</v>
       </c>
       <c r="K17" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="L17">
         <v>0.26374115795515951</v>
@@ -13167,7 +13167,7 @@
         <v>752</v>
       </c>
       <c r="X17" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="Y17">
         <v>5.8237500000000004</v>
@@ -13202,7 +13202,7 @@
         <v>656</v>
       </c>
       <c r="K18" t="s">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="L18">
         <v>1.0775690479395925</v>
@@ -13235,7 +13235,7 @@
         <v>754</v>
       </c>
       <c r="X18" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="Y18">
         <v>16.887</v>
@@ -13270,7 +13270,7 @@
         <v>658</v>
       </c>
       <c r="K19" t="s">
-        <v>588</v>
+        <v>565</v>
       </c>
       <c r="L19">
         <v>1.644864133979123</v>
@@ -13303,7 +13303,7 @@
         <v>756</v>
       </c>
       <c r="X19" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="Y19">
         <v>17.089500000000001</v>
@@ -13338,7 +13338,7 @@
         <v>660</v>
       </c>
       <c r="K20" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="L20">
         <v>4.1793335626386838</v>
@@ -13371,7 +13371,7 @@
         <v>758</v>
       </c>
       <c r="X20" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="Y20">
         <v>5.4255000000000004</v>
@@ -13406,7 +13406,7 @@
         <v>662</v>
       </c>
       <c r="K21" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="L21">
         <v>0.10220883742433164</v>
@@ -13441,7 +13441,7 @@
         <v>664</v>
       </c>
       <c r="K22" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="L22">
         <v>3.2456117052218421</v>
@@ -13476,7 +13476,7 @@
         <v>666</v>
       </c>
       <c r="K23" t="s">
-        <v>589</v>
+        <v>566</v>
       </c>
       <c r="L23">
         <v>3.822617103272679</v>
@@ -13511,7 +13511,7 @@
         <v>668</v>
       </c>
       <c r="K24" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
       <c r="L24">
         <v>0.18120178223038519</v>
@@ -13546,7 +13546,7 @@
         <v>670</v>
       </c>
       <c r="K25" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="L25">
         <v>1.2636771265917695</v>
@@ -13581,7 +13581,7 @@
         <v>672</v>
       </c>
       <c r="K26" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="L26">
         <v>2.5500240416298969</v>
@@ -13616,7 +13616,7 @@
         <v>674</v>
       </c>
       <c r="K27" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="L27">
         <v>4.0346953063254611</v>
@@ -13651,7 +13651,7 @@
         <v>676</v>
       </c>
       <c r="K28" t="s">
-        <v>591</v>
+        <v>568</v>
       </c>
       <c r="L28">
         <v>2.4674795572908166</v>
@@ -13686,7 +13686,7 @@
         <v>678</v>
       </c>
       <c r="K29" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="L29">
         <v>0.19671799304243257</v>
@@ -13721,7 +13721,7 @@
         <v>680</v>
       </c>
       <c r="K30" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="L30">
         <v>0.46906534608342149</v>
@@ -13756,7 +13756,7 @@
         <v>682</v>
       </c>
       <c r="K31" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="L31">
         <v>0.70432433684539619</v>
@@ -13791,7 +13791,7 @@
         <v>684</v>
       </c>
       <c r="K32" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L32">
         <v>0.14326997649193718</v>
@@ -13826,7 +13826,7 @@
         <v>686</v>
       </c>
       <c r="K33" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="L33">
         <v>2.5135228824118248E-2</v>
@@ -13861,7 +13861,7 @@
         <v>688</v>
       </c>
       <c r="K34" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="L34">
         <v>0.60333316217563482</v>
@@ -13896,7 +13896,7 @@
         <v>690</v>
       </c>
       <c r="K35" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="L35">
         <v>0.61002023046213527</v>
@@ -13931,7 +13931,7 @@
         <v>692</v>
       </c>
       <c r="K36" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="L36">
         <v>5.5124889677616896E-2</v>
@@ -13966,7 +13966,7 @@
         <v>694</v>
       </c>
       <c r="K37" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="L37">
         <v>0.19696072330654418</v>
@@ -14001,7 +14001,7 @@
         <v>696</v>
       </c>
       <c r="K38" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="L38">
         <v>0.37453679972687481</v>
@@ -14036,7 +14036,7 @@
         <v>698</v>
       </c>
       <c r="K39" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="L39">
         <v>2.9266524214395733</v>
@@ -14071,7 +14071,7 @@
         <v>700</v>
       </c>
       <c r="K40" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L40">
         <v>0.46102512715199689</v>
@@ -14106,7 +14106,7 @@
         <v>702</v>
       </c>
       <c r="K41" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -14141,7 +14141,7 @@
         <v>704</v>
       </c>
       <c r="K42" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="L42">
         <v>1.9780607647145438</v>
@@ -14176,7 +14176,7 @@
         <v>706</v>
       </c>
       <c r="K43" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L43">
         <v>0.80689812107944159</v>
@@ -14211,7 +14211,7 @@
         <v>708</v>
       </c>
       <c r="K44" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="L44">
         <v>0.1886799653533156</v>
@@ -14246,7 +14246,7 @@
         <v>710</v>
       </c>
       <c r="K45" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="L45">
         <v>2.577065692017253</v>
@@ -14281,7 +14281,7 @@
         <v>712</v>
       </c>
       <c r="K46" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="L46">
         <v>0.32349873740765611</v>
@@ -14316,7 +14316,7 @@
         <v>714</v>
       </c>
       <c r="K47" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -14351,7 +14351,7 @@
         <v>716</v>
       </c>
       <c r="K48" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="L48">
         <v>2.3210450729876548</v>
@@ -14386,7 +14386,7 @@
         <v>718</v>
       </c>
       <c r="K49" t="s">
-        <v>593</v>
+        <v>563</v>
       </c>
       <c r="L49">
         <v>1.4641560353950904</v>
@@ -14421,7 +14421,7 @@
         <v>720</v>
       </c>
       <c r="K50" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="L50">
         <v>4.3172734082397007E-3</v>
@@ -14456,7 +14456,7 @@
         <v>722</v>
       </c>
       <c r="K51" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="L51">
         <v>2.3327457542865271</v>
@@ -14491,7 +14491,7 @@
         <v>724</v>
       </c>
       <c r="K52" t="s">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="L52">
         <v>0.64220735366408732</v>
@@ -14526,7 +14526,7 @@
         <v>726</v>
       </c>
       <c r="K53" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="L53">
         <v>0.20805219904440039</v>
@@ -14561,7 +14561,7 @@
         <v>728</v>
       </c>
       <c r="K54" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="L54">
         <v>1.3018026354345156</v>
@@ -14596,7 +14596,7 @@
         <v>730</v>
       </c>
       <c r="K55" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="L55">
         <v>3.0871018425456893</v>
@@ -14631,7 +14631,7 @@
         <v>732</v>
       </c>
       <c r="K56" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="L56">
         <v>3.1635610249840389</v>
@@ -14666,7 +14666,7 @@
         <v>734</v>
       </c>
       <c r="K57" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="L57">
         <v>9.3245940212150449E-2</v>
@@ -14701,7 +14701,7 @@
         <v>736</v>
       </c>
       <c r="K58" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="L58">
         <v>0.28717016660662842</v>
@@ -14736,7 +14736,7 @@
         <v>738</v>
       </c>
       <c r="K59" t="s">
-        <v>583</v>
+        <v>611</v>
       </c>
       <c r="L59">
         <v>0.93964202108728523</v>
@@ -14751,7 +14751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6876DEC9-A255-48A1-AA23-39A6941CDBC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C69ADA9-070D-4C24-9DF3-007EDB457510}">
   <dimension ref="B9:Y159"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19812,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B940BCC8-5E6C-4922-9170-484D6E629B09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24C8968-F251-4F0A-8974-4E9A185371D4}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6842A01F-7BE8-4A3D-B9C9-7A0B3B840676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5D4251-5B1D-46DE-96A8-D68ECB6FBB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1014,6 +1014,258 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_010</t>
   </si>
   <si>
@@ -1038,198 +1290,6 @@
     <t>connecting solar to buses in cluster 46</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_002</t>
   </si>
   <si>
@@ -1242,66 +1302,6 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1317,6 +1317,132 @@
     <t>e_Mielec_POL</t>
   </si>
   <si>
+    <t>e_Siedlce_POL</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>e_Belchatow_POL</t>
+  </si>
+  <si>
+    <t>e_Zabrze_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>e_Lukow_POL</t>
+  </si>
+  <si>
+    <t>e_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>e_Radom_POL</t>
+  </si>
+  <si>
+    <t>e_Lodz_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>e_Lublin_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>e_Pila_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
+  </si>
+  <si>
     <t>e_Olsztyn_POL</t>
   </si>
   <si>
@@ -1329,136 +1455,172 @@
     <t>e_Grudziadz_POL</t>
   </si>
   <si>
-    <t>e_Lublin_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL</t>
-  </si>
-  <si>
-    <t>e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Siedlce_POL</t>
-  </si>
-  <si>
-    <t>e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>e_Belchatow_POL</t>
-  </si>
-  <si>
-    <t>e_Zabrze_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL</t>
-  </si>
-  <si>
-    <t>e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>e_Pila_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>e_Poznan_POL</t>
-  </si>
-  <si>
-    <t>e_Wroclaw_POL</t>
-  </si>
-  <si>
     <t>e_Bialystok_POL</t>
   </si>
   <si>
     <t>e_Grajewo_POL</t>
   </si>
   <si>
-    <t>e_Elk_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>e_Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>e_Lukow_POL</t>
-  </si>
-  <si>
-    <t>e_Swidnica_POL</t>
-  </si>
-  <si>
-    <t>e_Radom_POL</t>
-  </si>
-  <si>
-    <t>e_Lodz_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Wloclawek_POL</t>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_039</t>
@@ -1467,42 +1629,6 @@
     <t>connecting wind onshore to buses in cluster 39</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_007</t>
   </si>
   <si>
@@ -1515,22 +1641,82 @@
     <t>connecting wind onshore to buses in cluster 34</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_026</t>
@@ -1545,162 +1731,6 @@
     <t>connecting wind onshore to buses in cluster 48</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_001</t>
   </si>
   <si>
@@ -1725,70 +1755,133 @@
     <t>connecting wind onshore to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_049</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
   </si>
   <si>
     <t>elc_won_POL_039</t>
   </si>
   <si>
-    <t>elc_won_POL_042</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>elc_won_POL_032</t>
-  </si>
-  <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
     <t>elc_won_POL_034</t>
   </si>
   <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
   </si>
   <si>
     <t>elc_won_POL_026</t>
@@ -1797,84 +1890,6 @@
     <t>elc_won_POL_048</t>
   </si>
   <si>
-    <t>elc_won_POL_030</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>elc_won_POL_041</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>elc_won_POL_037</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>elc_won_POL_025</t>
-  </si>
-  <si>
-    <t>elc_won_POL_027</t>
-  </si>
-  <si>
-    <t>elc_won_POL_028</t>
-  </si>
-  <si>
-    <t>elc_won_POL_038</t>
-  </si>
-  <si>
-    <t>elc_won_POL_040</t>
-  </si>
-  <si>
-    <t>elc_won_POL_046</t>
-  </si>
-  <si>
-    <t>elc_won_POL_047</t>
-  </si>
-  <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
@@ -1887,19 +1902,28 @@
     <t>elc_won_POL_033</t>
   </si>
   <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>elc_won_POL_049</t>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_001</t>
@@ -1908,12 +1932,6 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_008</t>
   </si>
   <si>
@@ -1926,18 +1944,6 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_004</t>
   </si>
   <si>
@@ -1956,30 +1962,27 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
   </si>
   <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
     <t>elc_wof_POL_008</t>
   </si>
   <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
@@ -1987,9 +1990,6 @@
   </si>
   <si>
     <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -6534,7 +6534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2A14DB-4FC5-41D4-8B66-8A79EC5CD875}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471F3D15-8897-493A-AD52-6A41F4AE2E6E}">
   <dimension ref="B9:BD61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6811,13 +6811,13 @@
         <v>563</v>
       </c>
       <c r="AN11" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="AO11">
-        <v>0.99777778253795524</v>
+        <v>0.99649252363612195</v>
       </c>
       <c r="AP11">
-        <v>36.020821886415746</v>
+        <v>28.983218493781202</v>
       </c>
       <c r="AR11" t="s">
         <v>307</v>
@@ -6847,13 +6847,13 @@
         <v>632</v>
       </c>
       <c r="BB11" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="BC11">
-        <v>0.99436455351944619</v>
+        <v>0.99378504174620896</v>
       </c>
       <c r="BD11">
-        <v>728.41730490967211</v>
+        <v>761.13276667340403</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6957,13 +6957,13 @@
         <v>564</v>
       </c>
       <c r="AN12" t="s">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="AO12">
-        <v>0.99870289970840342</v>
+        <v>0.99767811393002859</v>
       </c>
       <c r="AP12">
-        <v>23.107973955380711</v>
+        <v>30.875049982999808</v>
       </c>
       <c r="AR12" t="s">
         <v>307</v>
@@ -6993,13 +6993,13 @@
         <v>633</v>
       </c>
       <c r="BB12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="BC12">
-        <v>0.99784666475123052</v>
+        <v>0.99478860441526007</v>
       </c>
       <c r="BD12">
-        <v>434.14794560012712</v>
+        <v>610.20976015093845</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7103,13 +7103,13 @@
         <v>565</v>
       </c>
       <c r="AN13" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="AO13">
-        <v>0.99649252363612195</v>
+        <v>0.99764304373832691</v>
       </c>
       <c r="AP13">
-        <v>28.983218493781202</v>
+        <v>42.327567967950763</v>
       </c>
       <c r="AR13" t="s">
         <v>307</v>
@@ -7139,13 +7139,13 @@
         <v>634</v>
       </c>
       <c r="BB13" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="BC13">
-        <v>0.99503061728845632</v>
+        <v>0.99249606766869936</v>
       </c>
       <c r="BD13">
-        <v>669.38461499965297</v>
+        <v>661.89204677750558</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7210,16 +7210,16 @@
         <v>316</v>
       </c>
       <c r="Y14" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="Z14" t="s">
         <v>417</v>
       </c>
       <c r="AA14">
-        <v>0.99762279320259084</v>
+        <v>0.99761913939972058</v>
       </c>
       <c r="AB14">
-        <v>50.682816539915542</v>
+        <v>32.256845956342154</v>
       </c>
       <c r="AD14" t="s">
         <v>307</v>
@@ -7249,13 +7249,13 @@
         <v>566</v>
       </c>
       <c r="AN14" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="AO14">
-        <v>0.99767811393002859</v>
+        <v>0.99790384243262886</v>
       </c>
       <c r="AP14">
-        <v>30.875049982999808</v>
+        <v>72.461220387375079</v>
       </c>
       <c r="AR14" t="s">
         <v>307</v>
@@ -7285,13 +7285,13 @@
         <v>635</v>
       </c>
       <c r="BB14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="BC14">
-        <v>0.99635015248973569</v>
+        <v>0.99784666475123052</v>
       </c>
       <c r="BD14">
-        <v>366.10125775280716</v>
+        <v>434.14794560012712</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7356,16 +7356,16 @@
         <v>318</v>
       </c>
       <c r="Y15" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="Z15" t="s">
         <v>418</v>
       </c>
       <c r="AA15">
-        <v>0.99782727135381688</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AB15">
-        <v>30.875049982999808</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AD15" t="s">
         <v>307</v>
@@ -7395,13 +7395,13 @@
         <v>567</v>
       </c>
       <c r="AN15" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="AO15">
-        <v>0.99764304373832691</v>
+        <v>0.99797028609854399</v>
       </c>
       <c r="AP15">
-        <v>42.327567967950763</v>
+        <v>34.892661212818595</v>
       </c>
       <c r="AR15" t="s">
         <v>307</v>
@@ -7431,13 +7431,13 @@
         <v>636</v>
       </c>
       <c r="BB15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BC15">
-        <v>0.99378504174620896</v>
+        <v>0.99436455351944619</v>
       </c>
       <c r="BD15">
-        <v>761.13276667340403</v>
+        <v>728.41730490967211</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7502,16 +7502,16 @@
         <v>320</v>
       </c>
       <c r="Y16" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="Z16" t="s">
         <v>419</v>
       </c>
       <c r="AA16">
-        <v>0.99795655945864681</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AB16">
-        <v>75.277133913292474</v>
+        <v>12.729766626457181</v>
       </c>
       <c r="AD16" t="s">
         <v>307</v>
@@ -7541,13 +7541,13 @@
         <v>568</v>
       </c>
       <c r="AN16" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="AO16">
-        <v>0.99790384243262886</v>
+        <v>0.99828876210676587</v>
       </c>
       <c r="AP16">
-        <v>72.461220387375079</v>
+        <v>28.334088028040785</v>
       </c>
       <c r="AR16" t="s">
         <v>307</v>
@@ -7577,13 +7577,13 @@
         <v>637</v>
       </c>
       <c r="BB16" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="BC16">
-        <v>0.99249606766869936</v>
+        <v>0.99503061728845632</v>
       </c>
       <c r="BD16">
-        <v>661.89204677750558</v>
+        <v>669.38461499965297</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7648,16 +7648,16 @@
         <v>322</v>
       </c>
       <c r="Y17" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="Z17" t="s">
         <v>420</v>
       </c>
       <c r="AA17">
-        <v>0.99874893763362849</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AB17">
-        <v>27.496123184453968</v>
+        <v>2.9143415731308986</v>
       </c>
       <c r="AD17" t="s">
         <v>307</v>
@@ -7687,13 +7687,13 @@
         <v>569</v>
       </c>
       <c r="AN17" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="AO17">
-        <v>0.99797028609854399</v>
+        <v>0.9975765595050764</v>
       </c>
       <c r="AP17">
-        <v>34.892661212818595</v>
+        <v>31.560996462068374</v>
       </c>
       <c r="AR17" t="s">
         <v>307</v>
@@ -7723,13 +7723,13 @@
         <v>638</v>
       </c>
       <c r="BB17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="BC17">
-        <v>0.99671396210736585</v>
+        <v>0.99635015248973569</v>
       </c>
       <c r="BD17">
-        <v>535.75153841730867</v>
+        <v>366.10125775280716</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7794,16 +7794,16 @@
         <v>324</v>
       </c>
       <c r="Y18" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="Z18" t="s">
         <v>421</v>
       </c>
       <c r="AA18">
-        <v>0.99755900053893942</v>
+        <v>0.9978643471647114</v>
       </c>
       <c r="AB18">
-        <v>42.327567967950763</v>
+        <v>31.560996462068374</v>
       </c>
       <c r="AD18" t="s">
         <v>307</v>
@@ -7833,13 +7833,13 @@
         <v>570</v>
       </c>
       <c r="AN18" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AO18">
-        <v>0.99863161241655762</v>
+        <v>0.99839049347738307</v>
       </c>
       <c r="AP18">
-        <v>48.306707937232645</v>
+        <v>75.277133913292474</v>
       </c>
       <c r="AR18" t="s">
         <v>307</v>
@@ -7869,13 +7869,13 @@
         <v>639</v>
       </c>
       <c r="BB18" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="BC18">
-        <v>0.99498581429447941</v>
+        <v>0.99671396210736585</v>
       </c>
       <c r="BD18">
-        <v>682.74537814765154</v>
+        <v>535.75153841730867</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7940,16 +7940,16 @@
         <v>326</v>
       </c>
       <c r="Y19" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="Z19" t="s">
         <v>422</v>
       </c>
       <c r="AA19">
-        <v>0.99776786767941794</v>
+        <v>0.99789011269484895</v>
       </c>
       <c r="AB19">
-        <v>27.059822883365296</v>
+        <v>36.605495131795273</v>
       </c>
       <c r="AD19" t="s">
         <v>307</v>
@@ -7979,13 +7979,13 @@
         <v>571</v>
       </c>
       <c r="AN19" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="AO19">
-        <v>0.99864365615724771</v>
+        <v>0.99697913305259955</v>
       </c>
       <c r="AP19">
-        <v>24.883658184919245</v>
+        <v>58.519281729791345</v>
       </c>
       <c r="AR19" t="s">
         <v>307</v>
@@ -8015,13 +8015,13 @@
         <v>640</v>
       </c>
       <c r="BB19" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="BC19">
-        <v>0.99705787611047647</v>
+        <v>0.99498581429447941</v>
       </c>
       <c r="BD19">
-        <v>516.05305554711185</v>
+        <v>682.74537814765154</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8086,16 +8086,16 @@
         <v>328</v>
       </c>
       <c r="Y20" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="Z20" t="s">
         <v>423</v>
       </c>
       <c r="AA20">
-        <v>0.99789789449716026</v>
+        <v>0.99783121031362565</v>
       </c>
       <c r="AB20">
-        <v>39.831307398714806</v>
+        <v>51.165698000691506</v>
       </c>
       <c r="AD20" t="s">
         <v>307</v>
@@ -8125,13 +8125,13 @@
         <v>572</v>
       </c>
       <c r="AN20" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="AO20">
-        <v>0.99845480529905328</v>
+        <v>0.99757778563357669</v>
       </c>
       <c r="AP20">
-        <v>47.820994144128512</v>
+        <v>45.221154662357485</v>
       </c>
       <c r="AR20" t="s">
         <v>307</v>
@@ -8161,13 +8161,13 @@
         <v>641</v>
       </c>
       <c r="BB20" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="BC20">
-        <v>0.99478860441526007</v>
+        <v>0.99705787611047647</v>
       </c>
       <c r="BD20">
-        <v>610.20976015093845</v>
+        <v>516.05305554711185</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8232,16 +8232,16 @@
         <v>330</v>
       </c>
       <c r="Y21" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="Z21" t="s">
         <v>424</v>
       </c>
       <c r="AA21">
-        <v>0.99864365615724771</v>
+        <v>0.99814724525850784</v>
       </c>
       <c r="AB21">
-        <v>45.737867404715672</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AD21" t="s">
         <v>307</v>
@@ -8271,13 +8271,13 @@
         <v>573</v>
       </c>
       <c r="AN21" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="AO21">
-        <v>0.9991052659747558</v>
+        <v>0.99896573022887158</v>
       </c>
       <c r="AP21">
-        <v>12.019055461720432</v>
+        <v>18.936001260254645</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8342,16 +8342,16 @@
         <v>332</v>
       </c>
       <c r="Y22" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="Z22" t="s">
         <v>425</v>
       </c>
       <c r="AA22">
-        <v>0.9991052659747558</v>
+        <v>0.99848201234520018</v>
       </c>
       <c r="AB22">
-        <v>12.019055461720432</v>
+        <v>72.463654284142635</v>
       </c>
       <c r="AD22" t="s">
         <v>307</v>
@@ -8381,13 +8381,13 @@
         <v>574</v>
       </c>
       <c r="AN22" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="AO22">
-        <v>0.99850473493624492</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AP22">
-        <v>27.496123184453968</v>
+        <v>40.332510468654611</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>334</v>
       </c>
       <c r="Y23" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="Z23" t="s">
         <v>426</v>
       </c>
       <c r="AA23">
-        <v>0.9976031883518911</v>
+        <v>0.99886290297361824</v>
       </c>
       <c r="AB23">
-        <v>58.963512461864056</v>
+        <v>26.622770797002293</v>
       </c>
       <c r="AD23" t="s">
         <v>307</v>
@@ -8491,13 +8491,13 @@
         <v>575</v>
       </c>
       <c r="AN23" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AO23">
-        <v>0.99871472031655018</v>
+        <v>0.99845480529905328</v>
       </c>
       <c r="AP23">
-        <v>28.428965886446147</v>
+        <v>47.820994144128512</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8562,16 +8562,16 @@
         <v>336</v>
       </c>
       <c r="Y24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Z24" t="s">
         <v>427</v>
       </c>
       <c r="AA24">
-        <v>0.99870289970840342</v>
+        <v>0.99779181951287421</v>
       </c>
       <c r="AB24">
-        <v>23.107973955380711</v>
+        <v>61.086483632538339</v>
       </c>
       <c r="AD24" t="s">
         <v>307</v>
@@ -8601,13 +8601,13 @@
         <v>576</v>
       </c>
       <c r="AN24" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO24">
-        <v>0.99782029353787438</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AP24">
-        <v>23.861203412894469</v>
+        <v>12.019055461720432</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>338</v>
       </c>
       <c r="Y25" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z25" t="s">
         <v>428</v>
       </c>
       <c r="AA25">
-        <v>0.99871805281197423</v>
+        <v>0.99811506665856298</v>
       </c>
       <c r="AB25">
-        <v>25.256759506353582</v>
+        <v>35.874797800938026</v>
       </c>
       <c r="AD25" t="s">
         <v>307</v>
@@ -8711,13 +8711,13 @@
         <v>577</v>
       </c>
       <c r="AN25" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="AO25">
-        <v>0.99828876210676587</v>
+        <v>0.99850473493624492</v>
       </c>
       <c r="AP25">
-        <v>28.334088028040785</v>
+        <v>27.496123184453968</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8782,16 +8782,16 @@
         <v>340</v>
       </c>
       <c r="Y26" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s">
         <v>429</v>
       </c>
       <c r="AA26">
-        <v>0.99637763901827192</v>
+        <v>0.99852418793335518</v>
       </c>
       <c r="AB26">
-        <v>48.031259731727893</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AD26" t="s">
         <v>307</v>
@@ -8821,13 +8821,13 @@
         <v>578</v>
       </c>
       <c r="AN26" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="AO26">
-        <v>0.9980121476893673</v>
+        <v>0.9967210177786987</v>
       </c>
       <c r="AP26">
-        <v>30.863466083156009</v>
+        <v>34.34566125862937</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8892,16 +8892,16 @@
         <v>342</v>
       </c>
       <c r="Y27" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="Z27" t="s">
         <v>430</v>
       </c>
       <c r="AA27">
-        <v>0.99873544632009026</v>
+        <v>0.99713671217394562</v>
       </c>
       <c r="AB27">
-        <v>34.387878972174441</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AD27" t="s">
         <v>307</v>
@@ -8931,13 +8931,13 @@
         <v>579</v>
       </c>
       <c r="AN27" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="AO27">
-        <v>0.99811519908104196</v>
+        <v>0.99777922331243873</v>
       </c>
       <c r="AP27">
-        <v>41.186340097586395</v>
+        <v>61.086483632538339</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9002,16 +9002,16 @@
         <v>344</v>
       </c>
       <c r="Y28" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="Z28" t="s">
         <v>431</v>
       </c>
       <c r="AA28">
-        <v>0.99761913939972058</v>
+        <v>0.99774884372261763</v>
       </c>
       <c r="AB28">
-        <v>32.256845956342154</v>
+        <v>84.621736519387298</v>
       </c>
       <c r="AD28" t="s">
         <v>307</v>
@@ -9041,13 +9041,13 @@
         <v>580</v>
       </c>
       <c r="AN28" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="AO28">
-        <v>0.9967210177786987</v>
+        <v>0.99777988747037838</v>
       </c>
       <c r="AP28">
-        <v>34.34566125862937</v>
+        <v>36.605495131795273</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9112,16 +9112,16 @@
         <v>346</v>
       </c>
       <c r="Y29" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="Z29" t="s">
         <v>432</v>
       </c>
       <c r="AA29">
-        <v>0.99916488913437129</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AB29">
-        <v>15.260625790927634</v>
+        <v>23.861203412894469</v>
       </c>
       <c r="AD29" t="s">
         <v>307</v>
@@ -9151,13 +9151,13 @@
         <v>581</v>
       </c>
       <c r="AN29" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="AO29">
-        <v>0.99777922331243873</v>
+        <v>0.9980121476893673</v>
       </c>
       <c r="AP29">
-        <v>61.086483632538339</v>
+        <v>30.863466083156009</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9222,16 +9222,16 @@
         <v>348</v>
       </c>
       <c r="Y30" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="Z30" t="s">
         <v>433</v>
       </c>
       <c r="AA30">
-        <v>0.99921633401208909</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AB30">
-        <v>12.729766626457181</v>
+        <v>40.332510468654611</v>
       </c>
       <c r="AD30" t="s">
         <v>307</v>
@@ -9261,13 +9261,13 @@
         <v>582</v>
       </c>
       <c r="AN30" t="s">
-        <v>463</v>
+        <v>415</v>
       </c>
       <c r="AO30">
-        <v>0.99777988747037838</v>
+        <v>0.99811519908104196</v>
       </c>
       <c r="AP30">
-        <v>36.605495131795273</v>
+        <v>41.186340097586395</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9332,16 +9332,16 @@
         <v>350</v>
       </c>
       <c r="Y31" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="Z31" t="s">
         <v>434</v>
       </c>
       <c r="AA31">
-        <v>0.99984169097848852</v>
+        <v>0.99815889366481214</v>
       </c>
       <c r="AB31">
-        <v>2.9143415731308986</v>
+        <v>34.892661212818595</v>
       </c>
       <c r="AD31" t="s">
         <v>307</v>
@@ -9371,13 +9371,13 @@
         <v>583</v>
       </c>
       <c r="AN31" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="AO31">
-        <v>0.99751816641322844</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AP31">
-        <v>45.1502695224383</v>
+        <v>23.107973955380711</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9442,16 +9442,16 @@
         <v>352</v>
       </c>
       <c r="Y32" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="Z32" t="s">
         <v>435</v>
       </c>
       <c r="AA32">
-        <v>0.99815889366481214</v>
+        <v>0.9976031883518911</v>
       </c>
       <c r="AB32">
-        <v>34.892661212818595</v>
+        <v>58.963512461864056</v>
       </c>
       <c r="AD32" t="s">
         <v>307</v>
@@ -9481,13 +9481,13 @@
         <v>584</v>
       </c>
       <c r="AN32" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AO32">
-        <v>0.99754431624006568</v>
+        <v>0.99790284855194045</v>
       </c>
       <c r="AP32">
-        <v>32.256845956342154</v>
+        <v>35.874797800938026</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9552,16 +9552,16 @@
         <v>354</v>
       </c>
       <c r="Y33" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="Z33" t="s">
         <v>436</v>
       </c>
       <c r="AA33">
-        <v>0.99811506665856298</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AB33">
-        <v>35.874797800938026</v>
+        <v>23.107973955380711</v>
       </c>
       <c r="AD33" t="s">
         <v>307</v>
@@ -9591,13 +9591,13 @@
         <v>585</v>
       </c>
       <c r="AN33" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="AO33">
-        <v>0.99755521694544447</v>
+        <v>0.99856107979091546</v>
       </c>
       <c r="AP33">
-        <v>50.682816539915542</v>
+        <v>26.622770797002293</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9662,16 +9662,16 @@
         <v>356</v>
       </c>
       <c r="Y34" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="Z34" t="s">
         <v>437</v>
       </c>
       <c r="AA34">
-        <v>0.99852418793335518</v>
+        <v>0.99755900053893942</v>
       </c>
       <c r="AB34">
-        <v>25.205687076233477</v>
+        <v>42.327567967950763</v>
       </c>
       <c r="AD34" t="s">
         <v>307</v>
@@ -9701,13 +9701,13 @@
         <v>586</v>
       </c>
       <c r="AN34" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="AO34">
-        <v>0.99984169097848852</v>
+        <v>0.99751816641322844</v>
       </c>
       <c r="AP34">
-        <v>2.9143415731308986</v>
+        <v>45.1502695224383</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9772,16 +9772,16 @@
         <v>358</v>
       </c>
       <c r="Y35" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="Z35" t="s">
         <v>438</v>
       </c>
       <c r="AA35">
-        <v>0.99713671217394562</v>
+        <v>0.99776786767941794</v>
       </c>
       <c r="AB35">
-        <v>51.990142494672078</v>
+        <v>27.059822883365296</v>
       </c>
       <c r="AD35" t="s">
         <v>307</v>
@@ -9811,13 +9811,13 @@
         <v>587</v>
       </c>
       <c r="AN35" t="s">
-        <v>462</v>
+        <v>417</v>
       </c>
       <c r="AO35">
-        <v>0.9975765595050764</v>
+        <v>0.99754431624006568</v>
       </c>
       <c r="AP35">
-        <v>31.560996462068374</v>
+        <v>32.256845956342154</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9882,16 +9882,16 @@
         <v>360</v>
       </c>
       <c r="Y36" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="Z36" t="s">
         <v>439</v>
       </c>
       <c r="AA36">
-        <v>0.99774884372261763</v>
+        <v>0.99789789449716026</v>
       </c>
       <c r="AB36">
-        <v>84.621736519387298</v>
+        <v>39.831307398714806</v>
       </c>
       <c r="AD36" t="s">
         <v>307</v>
@@ -9921,13 +9921,13 @@
         <v>588</v>
       </c>
       <c r="AN36" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="AO36">
-        <v>0.99837593922723478</v>
+        <v>0.99755521694544447</v>
       </c>
       <c r="AP36">
-        <v>25.205687076233477</v>
+        <v>50.682816539915542</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9992,16 +9992,16 @@
         <v>362</v>
       </c>
       <c r="Y37" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="Z37" t="s">
         <v>440</v>
       </c>
       <c r="AA37">
-        <v>0.99782029353787438</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AB37">
-        <v>23.861203412894469</v>
+        <v>45.737867404715672</v>
       </c>
       <c r="AD37" t="s">
         <v>307</v>
@@ -10031,13 +10031,13 @@
         <v>589</v>
       </c>
       <c r="AN37" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="AO37">
-        <v>0.99757815671697558</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AP37">
-        <v>51.990142494672078</v>
+        <v>2.9143415731308986</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10102,16 +10102,16 @@
         <v>364</v>
       </c>
       <c r="Y38" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="Z38" t="s">
         <v>441</v>
       </c>
       <c r="AA38">
-        <v>0.99813022065694434</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AB38">
-        <v>40.332510468654611</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AD38" t="s">
         <v>307</v>
@@ -10141,13 +10141,13 @@
         <v>590</v>
       </c>
       <c r="AN38" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="AO38">
-        <v>0.99916488913437129</v>
+        <v>0.99777778253795524</v>
       </c>
       <c r="AP38">
-        <v>15.260625790927634</v>
+        <v>36.020821886415746</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10251,13 +10251,13 @@
         <v>591</v>
       </c>
       <c r="AN39" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="AO39">
-        <v>0.99729296780855581</v>
+        <v>0.99863161241655762</v>
       </c>
       <c r="AP39">
-        <v>49.14481327115881</v>
+        <v>48.306707937232645</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10361,13 +10361,13 @@
         <v>592</v>
       </c>
       <c r="AN40" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="AO40">
-        <v>0.99921633401208909</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AP40">
-        <v>12.729766626457181</v>
+        <v>24.883658184919245</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10471,13 +10471,13 @@
         <v>593</v>
       </c>
       <c r="AN41" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="AO41">
-        <v>0.99790284855194045</v>
+        <v>0.99837593922723478</v>
       </c>
       <c r="AP41">
-        <v>35.874797800938026</v>
+        <v>25.205687076233477</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10581,13 +10581,13 @@
         <v>594</v>
       </c>
       <c r="AN42" t="s">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="AO42">
-        <v>0.99856107979091546</v>
+        <v>0.99757815671697558</v>
       </c>
       <c r="AP42">
-        <v>26.622770797002293</v>
+        <v>51.990142494672078</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10691,13 +10691,13 @@
         <v>595</v>
       </c>
       <c r="AN43" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="AO43">
-        <v>0.99632737337312927</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AP43">
-        <v>48.031259731727893</v>
+        <v>15.260625790927634</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10801,13 +10801,13 @@
         <v>596</v>
       </c>
       <c r="AN44" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="AO44">
-        <v>0.99739127962445018</v>
+        <v>0.99729296780855581</v>
       </c>
       <c r="AP44">
-        <v>39.831307398714806</v>
+        <v>49.14481327115881</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10911,13 +10911,13 @@
         <v>597</v>
       </c>
       <c r="AN45" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="AO45">
-        <v>0.99818574894902312</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AP45">
-        <v>33.253084498654445</v>
+        <v>12.729766626457181</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -11021,13 +11021,13 @@
         <v>598</v>
       </c>
       <c r="AN46" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AO46">
-        <v>0.99853353101054187</v>
+        <v>0.99632737337312927</v>
       </c>
       <c r="AP46">
-        <v>18.693183403514499</v>
+        <v>48.031259731727893</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -11131,13 +11131,13 @@
         <v>599</v>
       </c>
       <c r="AN47" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="AO47">
-        <v>0.99747843498043831</v>
+        <v>0.99739127962445018</v>
       </c>
       <c r="AP47">
-        <v>46.334800039670455</v>
+        <v>39.831307398714806</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -11241,13 +11241,13 @@
         <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="AO48">
-        <v>0.99466341005350978</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AP48">
-        <v>58.229467192272445</v>
+        <v>33.253084498654445</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -11351,13 +11351,13 @@
         <v>601</v>
       </c>
       <c r="AN49" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="AO49">
-        <v>0.9977732948939011</v>
+        <v>0.99853353101054187</v>
       </c>
       <c r="AP49">
-        <v>51.165698000691506</v>
+        <v>18.693183403514499</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -11422,16 +11422,16 @@
         <v>388</v>
       </c>
       <c r="Y50" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="Z50" t="s">
         <v>453</v>
       </c>
       <c r="AA50">
-        <v>0.99754569173664964</v>
+        <v>0.99751567592854107</v>
       </c>
       <c r="AB50">
-        <v>45.1502695224383</v>
+        <v>46.334800039670455</v>
       </c>
       <c r="AD50" t="s">
         <v>307</v>
@@ -11461,13 +11461,13 @@
         <v>602</v>
       </c>
       <c r="AN50" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO50">
-        <v>0.99872758388674931</v>
+        <v>0.99747843498043831</v>
       </c>
       <c r="AP50">
-        <v>23.31941562731657</v>
+        <v>46.334800039670455</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -11532,16 +11532,16 @@
         <v>390</v>
       </c>
       <c r="Y51" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="Z51" t="s">
         <v>454</v>
       </c>
       <c r="AA51">
-        <v>0.99697644816659792</v>
+        <v>0.99871805281197423</v>
       </c>
       <c r="AB51">
-        <v>58.519281729791345</v>
+        <v>25.256759506353582</v>
       </c>
       <c r="AD51" t="s">
         <v>307</v>
@@ -11571,13 +11571,13 @@
         <v>603</v>
       </c>
       <c r="AN51" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="AO51">
-        <v>0.99885698485202501</v>
+        <v>0.99466341005350978</v>
       </c>
       <c r="AP51">
-        <v>25.256759506353582</v>
+        <v>58.229467192272445</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -11642,16 +11642,16 @@
         <v>392</v>
       </c>
       <c r="Y52" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="Z52" t="s">
         <v>455</v>
       </c>
       <c r="AA52">
-        <v>0.99751567592854107</v>
+        <v>0.99637763901827192</v>
       </c>
       <c r="AB52">
-        <v>46.334800039670455</v>
+        <v>48.031259731727893</v>
       </c>
       <c r="AD52" t="s">
         <v>307</v>
@@ -11681,13 +11681,13 @@
         <v>604</v>
       </c>
       <c r="AN52" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="AO52">
-        <v>0.99709581552680626</v>
+        <v>0.9977732948939011</v>
       </c>
       <c r="AP52">
-        <v>53.231766754458491</v>
+        <v>51.165698000691506</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -11752,16 +11752,16 @@
         <v>394</v>
       </c>
       <c r="Y53" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="Z53" t="s">
         <v>456</v>
       </c>
       <c r="AA53">
-        <v>0.99834689519829145</v>
+        <v>0.99873544632009026</v>
       </c>
       <c r="AB53">
-        <v>32.749623583141812</v>
+        <v>34.387878972174441</v>
       </c>
       <c r="AD53" t="s">
         <v>307</v>
@@ -11791,13 +11791,13 @@
         <v>605</v>
       </c>
       <c r="AN53" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="AO53">
-        <v>0.99863950725251116</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AP53">
-        <v>34.387878972174441</v>
+        <v>23.31941562731657</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -11862,16 +11862,16 @@
         <v>396</v>
       </c>
       <c r="Y54" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="Z54" t="s">
         <v>457</v>
       </c>
       <c r="AA54">
-        <v>0.99853303004525662</v>
+        <v>0.99834689519829145</v>
       </c>
       <c r="AB54">
-        <v>18.693183403514499</v>
+        <v>32.749623583141812</v>
       </c>
       <c r="AD54" t="s">
         <v>307</v>
@@ -11901,13 +11901,13 @@
         <v>606</v>
       </c>
       <c r="AN54" t="s">
-        <v>450</v>
+        <v>416</v>
       </c>
       <c r="AO54">
-        <v>0.99837520457423046</v>
+        <v>0.99871472031655018</v>
       </c>
       <c r="AP54">
-        <v>29.909469717927731</v>
+        <v>28.428965886446147</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -11972,16 +11972,16 @@
         <v>398</v>
       </c>
       <c r="Y55" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="Z55" t="s">
         <v>458</v>
       </c>
       <c r="AA55">
-        <v>0.99814724525850784</v>
+        <v>0.99853303004525662</v>
       </c>
       <c r="AB55">
-        <v>47.820994144128512</v>
+        <v>18.693183403514499</v>
       </c>
       <c r="AD55" t="s">
         <v>307</v>
@@ -12011,13 +12011,13 @@
         <v>607</v>
       </c>
       <c r="AN55" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="AO55">
-        <v>0.99839049347738307</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AP55">
-        <v>75.277133913292474</v>
+        <v>23.861203412894469</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -12082,16 +12082,16 @@
         <v>400</v>
       </c>
       <c r="Y56" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Z56" t="s">
         <v>459</v>
       </c>
       <c r="AA56">
-        <v>0.99848201234520018</v>
+        <v>0.99762279320259084</v>
       </c>
       <c r="AB56">
-        <v>72.463654284142635</v>
+        <v>50.682816539915542</v>
       </c>
       <c r="AD56" t="s">
         <v>307</v>
@@ -12124,10 +12124,10 @@
         <v>454</v>
       </c>
       <c r="AO56">
-        <v>0.99697913305259955</v>
+        <v>0.99885698485202501</v>
       </c>
       <c r="AP56">
-        <v>58.519281729791345</v>
+        <v>25.256759506353582</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -12192,16 +12192,16 @@
         <v>402</v>
       </c>
       <c r="Y57" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="Z57" t="s">
         <v>460</v>
       </c>
       <c r="AA57">
-        <v>0.99886290297361824</v>
+        <v>0.99782727135381688</v>
       </c>
       <c r="AB57">
-        <v>26.622770797002293</v>
+        <v>30.875049982999808</v>
       </c>
       <c r="AD57" t="s">
         <v>307</v>
@@ -12231,13 +12231,13 @@
         <v>609</v>
       </c>
       <c r="AN57" t="s">
-        <v>447</v>
+        <v>414</v>
       </c>
       <c r="AO57">
-        <v>0.99757778563357669</v>
+        <v>0.99709581552680626</v>
       </c>
       <c r="AP57">
-        <v>45.221154662357485</v>
+        <v>53.231766754458491</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -12302,16 +12302,16 @@
         <v>404</v>
       </c>
       <c r="Y58" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="Z58" t="s">
         <v>461</v>
       </c>
       <c r="AA58">
-        <v>0.99779181951287421</v>
+        <v>0.99795655945864681</v>
       </c>
       <c r="AB58">
-        <v>61.086483632538339</v>
+        <v>75.277133913292474</v>
       </c>
       <c r="AD58" t="s">
         <v>307</v>
@@ -12341,13 +12341,13 @@
         <v>610</v>
       </c>
       <c r="AN58" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="AO58">
-        <v>0.99896573022887158</v>
+        <v>0.99863950725251116</v>
       </c>
       <c r="AP58">
-        <v>18.936001260254645</v>
+        <v>34.387878972174441</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -12412,16 +12412,16 @@
         <v>406</v>
       </c>
       <c r="Y59" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="Z59" t="s">
         <v>462</v>
       </c>
       <c r="AA59">
-        <v>0.9978643471647114</v>
+        <v>0.99874893763362849</v>
       </c>
       <c r="AB59">
-        <v>31.560996462068374</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AD59" t="s">
         <v>307</v>
@@ -12451,13 +12451,13 @@
         <v>611</v>
       </c>
       <c r="AN59" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="AO59">
-        <v>0.99813022065694434</v>
+        <v>0.99837520457423046</v>
       </c>
       <c r="AP59">
-        <v>40.332510468654611</v>
+        <v>29.909469717927731</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -12522,16 +12522,16 @@
         <v>408</v>
       </c>
       <c r="Y60" t="s">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="Z60" t="s">
         <v>463</v>
       </c>
       <c r="AA60">
-        <v>0.99789011269484895</v>
+        <v>0.99754569173664964</v>
       </c>
       <c r="AB60">
-        <v>36.605495131795273</v>
+        <v>45.1502695224383</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -12596,16 +12596,16 @@
         <v>410</v>
       </c>
       <c r="Y61" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="Z61" t="s">
         <v>464</v>
       </c>
       <c r="AA61">
-        <v>0.99783121031362565</v>
+        <v>0.99697644816659792</v>
       </c>
       <c r="AB61">
-        <v>51.165698000691506</v>
+        <v>58.519281729791345</v>
       </c>
     </row>
   </sheetData>
@@ -12614,7 +12614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259CDCD2-D204-4312-8B36-34116D1F80AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECAC020-A819-48EB-AFC7-F2F34A8A2AAF}">
   <dimension ref="B9:Z59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12726,7 +12726,7 @@
         <v>642</v>
       </c>
       <c r="K11" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="L11">
         <v>0.64021427611097514</v>
@@ -12759,7 +12759,7 @@
         <v>740</v>
       </c>
       <c r="X11" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="Y11">
         <v>17.603249999999999</v>
@@ -12794,7 +12794,7 @@
         <v>644</v>
       </c>
       <c r="K12" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="L12">
         <v>3.683157674608327</v>
@@ -12827,7 +12827,7 @@
         <v>742</v>
       </c>
       <c r="X12" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="Y12">
         <v>11.58525</v>
@@ -12862,7 +12862,7 @@
         <v>646</v>
       </c>
       <c r="K13" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="L13">
         <v>1.1133782162108721</v>
@@ -12895,7 +12895,7 @@
         <v>744</v>
       </c>
       <c r="X13" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="Y13">
         <v>5.7000000000000002E-2</v>
@@ -12930,7 +12930,7 @@
         <v>648</v>
       </c>
       <c r="K14" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="L14">
         <v>2.5290705136145335</v>
@@ -12963,7 +12963,7 @@
         <v>746</v>
       </c>
       <c r="X14" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Y14">
         <v>11.2965</v>
@@ -12998,7 +12998,7 @@
         <v>650</v>
       </c>
       <c r="K15" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="L15">
         <v>2.1620342624302693</v>
@@ -13031,7 +13031,7 @@
         <v>748</v>
       </c>
       <c r="X15" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="Y15">
         <v>0.83925000000000005</v>
@@ -13066,7 +13066,7 @@
         <v>652</v>
       </c>
       <c r="K16" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="L16">
         <v>0.10228431008717309</v>
@@ -13099,7 +13099,7 @@
         <v>750</v>
       </c>
       <c r="X16" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="Y16">
         <v>2.0332499999999998</v>
@@ -13134,7 +13134,7 @@
         <v>654</v>
       </c>
       <c r="K17" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="L17">
         <v>0.26374115795515951</v>
@@ -13167,7 +13167,7 @@
         <v>752</v>
       </c>
       <c r="X17" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Y17">
         <v>5.8237500000000004</v>
@@ -13202,7 +13202,7 @@
         <v>656</v>
       </c>
       <c r="K18" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="L18">
         <v>1.0775690479395925</v>
@@ -13235,7 +13235,7 @@
         <v>754</v>
       </c>
       <c r="X18" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="Y18">
         <v>16.887</v>
@@ -13270,7 +13270,7 @@
         <v>658</v>
       </c>
       <c r="K19" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="L19">
         <v>1.644864133979123</v>
@@ -13303,7 +13303,7 @@
         <v>756</v>
       </c>
       <c r="X19" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="Y19">
         <v>17.089500000000001</v>
@@ -13338,7 +13338,7 @@
         <v>660</v>
       </c>
       <c r="K20" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="L20">
         <v>4.1793335626386838</v>
@@ -13371,7 +13371,7 @@
         <v>758</v>
       </c>
       <c r="X20" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Y20">
         <v>5.4255000000000004</v>
@@ -13406,7 +13406,7 @@
         <v>662</v>
       </c>
       <c r="K21" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="L21">
         <v>0.10220883742433164</v>
@@ -13441,7 +13441,7 @@
         <v>664</v>
       </c>
       <c r="K22" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L22">
         <v>3.2456117052218421</v>
@@ -13476,7 +13476,7 @@
         <v>666</v>
       </c>
       <c r="K23" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="L23">
         <v>3.822617103272679</v>
@@ -13511,7 +13511,7 @@
         <v>668</v>
       </c>
       <c r="K24" t="s">
-        <v>607</v>
+        <v>570</v>
       </c>
       <c r="L24">
         <v>0.18120178223038519</v>
@@ -13546,7 +13546,7 @@
         <v>670</v>
       </c>
       <c r="K25" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L25">
         <v>1.2636771265917695</v>
@@ -13581,7 +13581,7 @@
         <v>672</v>
       </c>
       <c r="K26" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="L26">
         <v>2.5500240416298969</v>
@@ -13616,7 +13616,7 @@
         <v>674</v>
       </c>
       <c r="K27" t="s">
-        <v>608</v>
+        <v>571</v>
       </c>
       <c r="L27">
         <v>4.0346953063254611</v>
@@ -13651,7 +13651,7 @@
         <v>676</v>
       </c>
       <c r="K28" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="L28">
         <v>2.4674795572908166</v>
@@ -13686,7 +13686,7 @@
         <v>678</v>
       </c>
       <c r="K29" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="L29">
         <v>0.19671799304243257</v>
@@ -13721,7 +13721,7 @@
         <v>680</v>
       </c>
       <c r="K30" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="L30">
         <v>0.46906534608342149</v>
@@ -13756,7 +13756,7 @@
         <v>682</v>
       </c>
       <c r="K31" t="s">
-        <v>609</v>
+        <v>572</v>
       </c>
       <c r="L31">
         <v>0.70432433684539619</v>
@@ -13791,7 +13791,7 @@
         <v>684</v>
       </c>
       <c r="K32" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="L32">
         <v>0.14326997649193718</v>
@@ -13826,7 +13826,7 @@
         <v>686</v>
       </c>
       <c r="K33" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="L33">
         <v>2.5135228824118248E-2</v>
@@ -13861,7 +13861,7 @@
         <v>688</v>
       </c>
       <c r="K34" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="L34">
         <v>0.60333316217563482</v>
@@ -13896,7 +13896,7 @@
         <v>690</v>
       </c>
       <c r="K35" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="L35">
         <v>0.61002023046213527</v>
@@ -13931,7 +13931,7 @@
         <v>692</v>
       </c>
       <c r="K36" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="L36">
         <v>5.5124889677616896E-2</v>
@@ -13966,7 +13966,7 @@
         <v>694</v>
       </c>
       <c r="K37" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="L37">
         <v>0.19696072330654418</v>
@@ -14001,7 +14001,7 @@
         <v>696</v>
       </c>
       <c r="K38" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L38">
         <v>0.37453679972687481</v>
@@ -14036,7 +14036,7 @@
         <v>698</v>
       </c>
       <c r="K39" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="L39">
         <v>2.9266524214395733</v>
@@ -14071,7 +14071,7 @@
         <v>700</v>
       </c>
       <c r="K40" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="L40">
         <v>0.46102512715199689</v>
@@ -14106,7 +14106,7 @@
         <v>702</v>
       </c>
       <c r="K41" t="s">
-        <v>610</v>
+        <v>573</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -14141,7 +14141,7 @@
         <v>704</v>
       </c>
       <c r="K42" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="L42">
         <v>1.9780607647145438</v>
@@ -14176,7 +14176,7 @@
         <v>706</v>
       </c>
       <c r="K43" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L43">
         <v>0.80689812107944159</v>
@@ -14211,7 +14211,7 @@
         <v>708</v>
       </c>
       <c r="K44" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="L44">
         <v>0.1886799653533156</v>
@@ -14246,7 +14246,7 @@
         <v>710</v>
       </c>
       <c r="K45" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="L45">
         <v>2.577065692017253</v>
@@ -14281,7 +14281,7 @@
         <v>712</v>
       </c>
       <c r="K46" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="L46">
         <v>0.32349873740765611</v>
@@ -14316,7 +14316,7 @@
         <v>714</v>
       </c>
       <c r="K47" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -14351,7 +14351,7 @@
         <v>716</v>
       </c>
       <c r="K48" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="L48">
         <v>2.3210450729876548</v>
@@ -14386,7 +14386,7 @@
         <v>718</v>
       </c>
       <c r="K49" t="s">
-        <v>563</v>
+        <v>590</v>
       </c>
       <c r="L49">
         <v>1.4641560353950904</v>
@@ -14421,7 +14421,7 @@
         <v>720</v>
       </c>
       <c r="K50" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="L50">
         <v>4.3172734082397007E-3</v>
@@ -14456,7 +14456,7 @@
         <v>722</v>
       </c>
       <c r="K51" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L51">
         <v>2.3327457542865271</v>
@@ -14491,7 +14491,7 @@
         <v>724</v>
       </c>
       <c r="K52" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="L52">
         <v>0.64220735366408732</v>
@@ -14526,7 +14526,7 @@
         <v>726</v>
       </c>
       <c r="K53" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L53">
         <v>0.20805219904440039</v>
@@ -14561,7 +14561,7 @@
         <v>728</v>
       </c>
       <c r="K54" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="L54">
         <v>1.3018026354345156</v>
@@ -14596,7 +14596,7 @@
         <v>730</v>
       </c>
       <c r="K55" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="L55">
         <v>3.0871018425456893</v>
@@ -14631,7 +14631,7 @@
         <v>732</v>
       </c>
       <c r="K56" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L56">
         <v>3.1635610249840389</v>
@@ -14666,7 +14666,7 @@
         <v>734</v>
       </c>
       <c r="K57" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="L57">
         <v>9.3245940212150449E-2</v>
@@ -14701,7 +14701,7 @@
         <v>736</v>
       </c>
       <c r="K58" t="s">
-        <v>576</v>
+        <v>607</v>
       </c>
       <c r="L58">
         <v>0.28717016660662842</v>
@@ -14736,7 +14736,7 @@
         <v>738</v>
       </c>
       <c r="K59" t="s">
-        <v>611</v>
+        <v>574</v>
       </c>
       <c r="L59">
         <v>0.93964202108728523</v>
@@ -14751,7 +14751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C69ADA9-070D-4C24-9DF3-007EDB457510}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D3FCDC-5602-43D0-883A-7B167AEBAFDC}">
   <dimension ref="B9:Y159"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19812,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24C8968-F251-4F0A-8974-4E9A185371D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF145D08-0B5C-4735-B68B-EC4DE4451785}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5D4251-5B1D-46DE-96A8-D68ECB6FBB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832F994F-CFFF-454A-93ED-4EC6F4867A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -990,18 +990,48 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_025</t>
   </si>
   <si>
@@ -1014,6 +1044,240 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_004</t>
   </si>
   <si>
@@ -1038,276 +1302,27 @@
     <t>connecting solar to buses in cluster 38</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD22</t>
   </si>
   <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>e_Pila_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
     <t>e_Skawina_POL</t>
   </si>
   <si>
@@ -1317,6 +1332,123 @@
     <t>e_Mielec_POL</t>
   </si>
   <si>
+    <t>e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_Lukow_POL</t>
+  </si>
+  <si>
+    <t>e_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>e_Radom_POL</t>
+  </si>
+  <si>
+    <t>e_Lodz_POL</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>e_Lublin_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
+  </si>
+  <si>
     <t>e_Siedlce_POL</t>
   </si>
   <si>
@@ -1329,136 +1461,160 @@
     <t>e_Zabrze_POL</t>
   </si>
   <si>
-    <t>e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>e_Lukow_POL</t>
-  </si>
-  <si>
-    <t>e_Swidnica_POL</t>
-  </si>
-  <si>
-    <t>e_Radom_POL</t>
-  </si>
-  <si>
-    <t>e_Lodz_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL</t>
-  </si>
-  <si>
-    <t>e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>e_Lublin_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL</t>
-  </si>
-  <si>
-    <t>e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>e_Pila_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>e_Lubin_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>e_Poznan_POL</t>
-  </si>
-  <si>
-    <t>e_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL</t>
-  </si>
-  <si>
-    <t>e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>e_Czestochowa_POL</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>e_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>e_Grajewo_POL</t>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_009</t>
@@ -1491,112 +1647,16 @@
     <t>connecting wind onshore to buses in cluster 32</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
+    <t>distr_wonelc_won_POL_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_002</t>
@@ -1623,52 +1683,28 @@
     <t>connecting wind onshore to buses in cluster 37</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_015</t>
@@ -1719,40 +1755,82 @@
     <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_049</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
@@ -1770,58 +1848,10 @@
     <t>elc_won_POL_032</t>
   </si>
   <si>
-    <t>elc_won_POL_030</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>elc_won_POL_049</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>elc_won_POL_041</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>elc_won_POL_042</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
   </si>
   <si>
     <t>elc_won_POL_002</t>
@@ -1836,28 +1866,16 @@
     <t>elc_won_POL_037</t>
   </si>
   <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>elc_won_POL_034</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
@@ -1884,22 +1902,34 @@
     <t>elc_won_POL_047</t>
   </si>
   <si>
-    <t>elc_won_POL_026</t>
-  </si>
-  <si>
-    <t>elc_won_POL_048</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>elc_won_POL_023</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_009</t>
@@ -1908,10 +1938,16 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_006</t>
@@ -1926,70 +1962,34 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
   </si>
   <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
-    <t>elc_wof_POL_002</t>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_003</t>
   </si>
   <si>
     <t>elc_wof_POL_006</t>
   </si>
   <si>
     <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -6534,7 +6534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471F3D15-8897-493A-AD52-6A41F4AE2E6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195ABC74-6C60-4C90-BAEA-2981B74B18A4}">
   <dimension ref="B9:BD61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6772,16 +6772,16 @@
         <v>308</v>
       </c>
       <c r="Y11" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="Z11" t="s">
         <v>414</v>
       </c>
       <c r="AA11">
-        <v>0.99751836673919181</v>
+        <v>0.99679205626668776</v>
       </c>
       <c r="AB11">
-        <v>50.515025114296037</v>
+        <v>28.983218493781202</v>
       </c>
       <c r="AD11" t="s">
         <v>307</v>
@@ -6811,13 +6811,13 @@
         <v>563</v>
       </c>
       <c r="AN11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AO11">
-        <v>0.99649252363612195</v>
+        <v>0.99790284855194045</v>
       </c>
       <c r="AP11">
-        <v>28.983218493781202</v>
+        <v>35.874797800938026</v>
       </c>
       <c r="AR11" t="s">
         <v>307</v>
@@ -6847,13 +6847,13 @@
         <v>632</v>
       </c>
       <c r="BB11" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="BC11">
-        <v>0.99378504174620896</v>
+        <v>0.99436455351944619</v>
       </c>
       <c r="BD11">
-        <v>761.13276667340403</v>
+        <v>728.41730490967211</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6918,16 +6918,16 @@
         <v>312</v>
       </c>
       <c r="Y12" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="Z12" t="s">
         <v>415</v>
       </c>
       <c r="AA12">
-        <v>0.99774808836727491</v>
+        <v>0.99713110094318969</v>
       </c>
       <c r="AB12">
-        <v>41.186340097586395</v>
+        <v>34.34566125862937</v>
       </c>
       <c r="AD12" t="s">
         <v>307</v>
@@ -6957,13 +6957,13 @@
         <v>564</v>
       </c>
       <c r="AN12" t="s">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="AO12">
-        <v>0.99767811393002859</v>
+        <v>0.99856107979091546</v>
       </c>
       <c r="AP12">
-        <v>30.875049982999808</v>
+        <v>26.622770797002293</v>
       </c>
       <c r="AR12" t="s">
         <v>307</v>
@@ -6993,13 +6993,13 @@
         <v>633</v>
       </c>
       <c r="BB12" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="BC12">
-        <v>0.99478860441526007</v>
+        <v>0.99671396210736585</v>
       </c>
       <c r="BD12">
-        <v>610.20976015093845</v>
+        <v>535.75153841730867</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7064,16 +7064,16 @@
         <v>314</v>
       </c>
       <c r="Y13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Z13" t="s">
         <v>416</v>
       </c>
       <c r="AA13">
-        <v>0.99828790514523624</v>
+        <v>0.99749963479302273</v>
       </c>
       <c r="AB13">
-        <v>28.428965886446147</v>
+        <v>49.14481327115881</v>
       </c>
       <c r="AD13" t="s">
         <v>307</v>
@@ -7103,13 +7103,13 @@
         <v>565</v>
       </c>
       <c r="AN13" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="AO13">
-        <v>0.99764304373832691</v>
+        <v>0.99845480529905328</v>
       </c>
       <c r="AP13">
-        <v>42.327567967950763</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AR13" t="s">
         <v>307</v>
@@ -7139,13 +7139,13 @@
         <v>634</v>
       </c>
       <c r="BB13" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="BC13">
-        <v>0.99249606766869936</v>
+        <v>0.99498581429447941</v>
       </c>
       <c r="BD13">
-        <v>661.89204677750558</v>
+        <v>682.74537814765154</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7210,16 +7210,16 @@
         <v>316</v>
       </c>
       <c r="Y14" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="Z14" t="s">
         <v>417</v>
       </c>
       <c r="AA14">
-        <v>0.99761913939972058</v>
+        <v>0.9985687661763365</v>
       </c>
       <c r="AB14">
-        <v>32.256845956342154</v>
+        <v>50.93040927578344</v>
       </c>
       <c r="AD14" t="s">
         <v>307</v>
@@ -7249,13 +7249,13 @@
         <v>566</v>
       </c>
       <c r="AN14" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="AO14">
-        <v>0.99790384243262886</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AP14">
-        <v>72.461220387375079</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AR14" t="s">
         <v>307</v>
@@ -7285,13 +7285,13 @@
         <v>635</v>
       </c>
       <c r="BB14" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BC14">
-        <v>0.99784666475123052</v>
+        <v>0.99705787611047647</v>
       </c>
       <c r="BD14">
-        <v>434.14794560012712</v>
+        <v>516.05305554711185</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7356,16 +7356,16 @@
         <v>318</v>
       </c>
       <c r="Y15" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="Z15" t="s">
         <v>418</v>
       </c>
       <c r="AA15">
-        <v>0.99916488913437129</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AB15">
-        <v>15.260625790927634</v>
+        <v>33.253084498654445</v>
       </c>
       <c r="AD15" t="s">
         <v>307</v>
@@ -7395,13 +7395,13 @@
         <v>567</v>
       </c>
       <c r="AN15" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="AO15">
-        <v>0.99797028609854399</v>
+        <v>0.99850473493624492</v>
       </c>
       <c r="AP15">
-        <v>34.892661212818595</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AR15" t="s">
         <v>307</v>
@@ -7431,13 +7431,13 @@
         <v>636</v>
       </c>
       <c r="BB15" t="s">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="BC15">
-        <v>0.99436455351944619</v>
+        <v>0.99478860441526007</v>
       </c>
       <c r="BD15">
-        <v>728.41730490967211</v>
+        <v>610.20976015093845</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7502,16 +7502,16 @@
         <v>320</v>
       </c>
       <c r="Y16" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="Z16" t="s">
         <v>419</v>
       </c>
       <c r="AA16">
-        <v>0.99921633401208909</v>
+        <v>0.99751836673919181</v>
       </c>
       <c r="AB16">
-        <v>12.729766626457181</v>
+        <v>50.515025114296037</v>
       </c>
       <c r="AD16" t="s">
         <v>307</v>
@@ -7541,13 +7541,13 @@
         <v>568</v>
       </c>
       <c r="AN16" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AO16">
-        <v>0.99828876210676587</v>
+        <v>0.99837593922723478</v>
       </c>
       <c r="AP16">
-        <v>28.334088028040785</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AR16" t="s">
         <v>307</v>
@@ -7577,13 +7577,13 @@
         <v>637</v>
       </c>
       <c r="BB16" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="BC16">
-        <v>0.99503061728845632</v>
+        <v>0.99378504174620896</v>
       </c>
       <c r="BD16">
-        <v>669.38461499965297</v>
+        <v>761.13276667340403</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7648,16 +7648,16 @@
         <v>322</v>
       </c>
       <c r="Y17" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="Z17" t="s">
         <v>420</v>
       </c>
       <c r="AA17">
-        <v>0.99984169097848852</v>
+        <v>0.99774808836727491</v>
       </c>
       <c r="AB17">
-        <v>2.9143415731308986</v>
+        <v>41.186340097586395</v>
       </c>
       <c r="AD17" t="s">
         <v>307</v>
@@ -7687,13 +7687,13 @@
         <v>569</v>
       </c>
       <c r="AN17" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="AO17">
-        <v>0.9975765595050764</v>
+        <v>0.99757815671697558</v>
       </c>
       <c r="AP17">
-        <v>31.560996462068374</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AR17" t="s">
         <v>307</v>
@@ -7723,13 +7723,13 @@
         <v>638</v>
       </c>
       <c r="BB17" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="BC17">
-        <v>0.99635015248973569</v>
+        <v>0.99503061728845632</v>
       </c>
       <c r="BD17">
-        <v>366.10125775280716</v>
+        <v>669.38461499965297</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7794,16 +7794,16 @@
         <v>324</v>
       </c>
       <c r="Y18" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="Z18" t="s">
         <v>421</v>
       </c>
       <c r="AA18">
-        <v>0.9978643471647114</v>
+        <v>0.99828790514523624</v>
       </c>
       <c r="AB18">
-        <v>31.560996462068374</v>
+        <v>28.428965886446147</v>
       </c>
       <c r="AD18" t="s">
         <v>307</v>
@@ -7833,13 +7833,13 @@
         <v>570</v>
       </c>
       <c r="AN18" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO18">
-        <v>0.99839049347738307</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AP18">
-        <v>75.277133913292474</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AR18" t="s">
         <v>307</v>
@@ -7869,13 +7869,13 @@
         <v>639</v>
       </c>
       <c r="BB18" t="s">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="BC18">
-        <v>0.99671396210736585</v>
+        <v>0.99635015248973569</v>
       </c>
       <c r="BD18">
-        <v>535.75153841730867</v>
+        <v>366.10125775280716</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7940,16 +7940,16 @@
         <v>326</v>
       </c>
       <c r="Y19" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="Z19" t="s">
         <v>422</v>
       </c>
       <c r="AA19">
-        <v>0.99789011269484895</v>
+        <v>0.9978643471647114</v>
       </c>
       <c r="AB19">
-        <v>36.605495131795273</v>
+        <v>31.560996462068374</v>
       </c>
       <c r="AD19" t="s">
         <v>307</v>
@@ -7979,13 +7979,13 @@
         <v>571</v>
       </c>
       <c r="AN19" t="s">
-        <v>464</v>
+        <v>416</v>
       </c>
       <c r="AO19">
-        <v>0.99697913305259955</v>
+        <v>0.99729296780855581</v>
       </c>
       <c r="AP19">
-        <v>58.519281729791345</v>
+        <v>49.14481327115881</v>
       </c>
       <c r="AR19" t="s">
         <v>307</v>
@@ -8015,13 +8015,13 @@
         <v>640</v>
       </c>
       <c r="BB19" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="BC19">
-        <v>0.99498581429447941</v>
+        <v>0.99249606766869936</v>
       </c>
       <c r="BD19">
-        <v>682.74537814765154</v>
+        <v>661.89204677750558</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8086,16 +8086,16 @@
         <v>328</v>
       </c>
       <c r="Y20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Z20" t="s">
         <v>423</v>
       </c>
       <c r="AA20">
-        <v>0.99783121031362565</v>
+        <v>0.99789011269484895</v>
       </c>
       <c r="AB20">
-        <v>51.165698000691506</v>
+        <v>36.605495131795273</v>
       </c>
       <c r="AD20" t="s">
         <v>307</v>
@@ -8125,13 +8125,13 @@
         <v>572</v>
       </c>
       <c r="AN20" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="AO20">
-        <v>0.99757778563357669</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AP20">
-        <v>45.221154662357485</v>
+        <v>12.729766626457181</v>
       </c>
       <c r="AR20" t="s">
         <v>307</v>
@@ -8161,13 +8161,13 @@
         <v>641</v>
       </c>
       <c r="BB20" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="BC20">
-        <v>0.99705787611047647</v>
+        <v>0.99784666475123052</v>
       </c>
       <c r="BD20">
-        <v>516.05305554711185</v>
+        <v>434.14794560012712</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8232,16 +8232,16 @@
         <v>330</v>
       </c>
       <c r="Y21" t="s">
-        <v>259</v>
+        <v>302</v>
       </c>
       <c r="Z21" t="s">
         <v>424</v>
       </c>
       <c r="AA21">
-        <v>0.99814724525850784</v>
+        <v>0.99783121031362565</v>
       </c>
       <c r="AB21">
-        <v>47.820994144128512</v>
+        <v>51.165698000691506</v>
       </c>
       <c r="AD21" t="s">
         <v>307</v>
@@ -8271,13 +8271,13 @@
         <v>573</v>
       </c>
       <c r="AN21" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="AO21">
-        <v>0.99896573022887158</v>
+        <v>0.99839049347738307</v>
       </c>
       <c r="AP21">
-        <v>18.936001260254645</v>
+        <v>75.277133913292474</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8342,16 +8342,16 @@
         <v>332</v>
       </c>
       <c r="Y22" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="Z22" t="s">
         <v>425</v>
       </c>
       <c r="AA22">
-        <v>0.99848201234520018</v>
+        <v>0.99871805281197423</v>
       </c>
       <c r="AB22">
-        <v>72.463654284142635</v>
+        <v>25.256759506353582</v>
       </c>
       <c r="AD22" t="s">
         <v>307</v>
@@ -8381,13 +8381,13 @@
         <v>574</v>
       </c>
       <c r="AN22" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="AO22">
-        <v>0.99813022065694434</v>
+        <v>0.99697913305259955</v>
       </c>
       <c r="AP22">
-        <v>40.332510468654611</v>
+        <v>58.519281729791345</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>334</v>
       </c>
       <c r="Y23" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="Z23" t="s">
         <v>426</v>
       </c>
       <c r="AA23">
-        <v>0.99886290297361824</v>
+        <v>0.99637763901827192</v>
       </c>
       <c r="AB23">
-        <v>26.622770797002293</v>
+        <v>48.031259731727893</v>
       </c>
       <c r="AD23" t="s">
         <v>307</v>
@@ -8491,13 +8491,13 @@
         <v>575</v>
       </c>
       <c r="AN23" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="AO23">
-        <v>0.99845480529905328</v>
+        <v>0.99757778563357669</v>
       </c>
       <c r="AP23">
-        <v>47.820994144128512</v>
+        <v>45.221154662357485</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8562,16 +8562,16 @@
         <v>336</v>
       </c>
       <c r="Y24" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="Z24" t="s">
         <v>427</v>
       </c>
       <c r="AA24">
-        <v>0.99779181951287421</v>
+        <v>0.99873544632009026</v>
       </c>
       <c r="AB24">
-        <v>61.086483632538339</v>
+        <v>34.387878972174441</v>
       </c>
       <c r="AD24" t="s">
         <v>307</v>
@@ -8601,13 +8601,13 @@
         <v>576</v>
       </c>
       <c r="AN24" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AO24">
-        <v>0.9991052659747558</v>
+        <v>0.99896573022887158</v>
       </c>
       <c r="AP24">
-        <v>12.019055461720432</v>
+        <v>18.936001260254645</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>338</v>
       </c>
       <c r="Y25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s">
         <v>428</v>
       </c>
       <c r="AA25">
-        <v>0.99811506665856298</v>
+        <v>0.99754569173664964</v>
       </c>
       <c r="AB25">
-        <v>35.874797800938026</v>
+        <v>45.1502695224383</v>
       </c>
       <c r="AD25" t="s">
         <v>307</v>
@@ -8711,13 +8711,13 @@
         <v>577</v>
       </c>
       <c r="AN25" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="AO25">
-        <v>0.99850473493624492</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AP25">
-        <v>27.496123184453968</v>
+        <v>40.332510468654611</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8782,16 +8782,16 @@
         <v>340</v>
       </c>
       <c r="Y26" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="Z26" t="s">
         <v>429</v>
       </c>
       <c r="AA26">
-        <v>0.99852418793335518</v>
+        <v>0.99697644816659792</v>
       </c>
       <c r="AB26">
-        <v>25.205687076233477</v>
+        <v>58.519281729791345</v>
       </c>
       <c r="AD26" t="s">
         <v>307</v>
@@ -8821,13 +8821,13 @@
         <v>578</v>
       </c>
       <c r="AN26" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="AO26">
-        <v>0.9967210177786987</v>
+        <v>0.9975765595050764</v>
       </c>
       <c r="AP26">
-        <v>34.34566125862937</v>
+        <v>31.560996462068374</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8892,16 +8892,16 @@
         <v>342</v>
       </c>
       <c r="Y27" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Z27" t="s">
         <v>430</v>
       </c>
       <c r="AA27">
-        <v>0.99713671217394562</v>
+        <v>0.99814724525850784</v>
       </c>
       <c r="AB27">
-        <v>51.990142494672078</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AD27" t="s">
         <v>307</v>
@@ -8931,13 +8931,13 @@
         <v>579</v>
       </c>
       <c r="AN27" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO27">
-        <v>0.99777922331243873</v>
+        <v>0.99863161241655762</v>
       </c>
       <c r="AP27">
-        <v>61.086483632538339</v>
+        <v>48.306707937232645</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9002,16 +9002,16 @@
         <v>344</v>
       </c>
       <c r="Y28" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="Z28" t="s">
         <v>431</v>
       </c>
       <c r="AA28">
-        <v>0.99774884372261763</v>
+        <v>0.99848201234520018</v>
       </c>
       <c r="AB28">
-        <v>84.621736519387298</v>
+        <v>72.463654284142635</v>
       </c>
       <c r="AD28" t="s">
         <v>307</v>
@@ -9041,13 +9041,13 @@
         <v>580</v>
       </c>
       <c r="AN28" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="AO28">
-        <v>0.99777988747037838</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AP28">
-        <v>36.605495131795273</v>
+        <v>24.883658184919245</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9112,16 +9112,16 @@
         <v>346</v>
       </c>
       <c r="Y29" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="Z29" t="s">
         <v>432</v>
       </c>
       <c r="AA29">
-        <v>0.99782029353787438</v>
+        <v>0.99886290297361824</v>
       </c>
       <c r="AB29">
-        <v>23.861203412894469</v>
+        <v>26.622770797002293</v>
       </c>
       <c r="AD29" t="s">
         <v>307</v>
@@ -9151,13 +9151,13 @@
         <v>581</v>
       </c>
       <c r="AN29" t="s">
-        <v>457</v>
+        <v>415</v>
       </c>
       <c r="AO29">
-        <v>0.9980121476893673</v>
+        <v>0.9967210177786987</v>
       </c>
       <c r="AP29">
-        <v>30.863466083156009</v>
+        <v>34.34566125862937</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9222,16 +9222,16 @@
         <v>348</v>
       </c>
       <c r="Y30" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="Z30" t="s">
         <v>433</v>
       </c>
       <c r="AA30">
-        <v>0.99813022065694434</v>
+        <v>0.99779181951287421</v>
       </c>
       <c r="AB30">
-        <v>40.332510468654611</v>
+        <v>61.086483632538339</v>
       </c>
       <c r="AD30" t="s">
         <v>307</v>
@@ -9261,13 +9261,13 @@
         <v>582</v>
       </c>
       <c r="AN30" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="AO30">
-        <v>0.99811519908104196</v>
+        <v>0.99777922331243873</v>
       </c>
       <c r="AP30">
-        <v>41.186340097586395</v>
+        <v>61.086483632538339</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9332,16 +9332,16 @@
         <v>350</v>
       </c>
       <c r="Y31" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="Z31" t="s">
         <v>434</v>
       </c>
       <c r="AA31">
-        <v>0.99815889366481214</v>
+        <v>0.9976031883518911</v>
       </c>
       <c r="AB31">
-        <v>34.892661212818595</v>
+        <v>58.963512461864056</v>
       </c>
       <c r="AD31" t="s">
         <v>307</v>
@@ -9371,13 +9371,13 @@
         <v>583</v>
       </c>
       <c r="AN31" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="AO31">
-        <v>0.99870289970840342</v>
+        <v>0.99777988747037838</v>
       </c>
       <c r="AP31">
-        <v>23.107973955380711</v>
+        <v>36.605495131795273</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9442,16 +9442,16 @@
         <v>352</v>
       </c>
       <c r="Y32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Z32" t="s">
         <v>435</v>
       </c>
       <c r="AA32">
-        <v>0.9976031883518911</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AB32">
-        <v>58.963512461864056</v>
+        <v>23.107973955380711</v>
       </c>
       <c r="AD32" t="s">
         <v>307</v>
@@ -9481,13 +9481,13 @@
         <v>584</v>
       </c>
       <c r="AN32" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="AO32">
-        <v>0.99790284855194045</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AP32">
-        <v>35.874797800938026</v>
+        <v>23.107973955380711</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9552,16 +9552,16 @@
         <v>354</v>
       </c>
       <c r="Y33" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="Z33" t="s">
         <v>436</v>
       </c>
       <c r="AA33">
-        <v>0.99870289970840342</v>
+        <v>0.99755900053893942</v>
       </c>
       <c r="AB33">
-        <v>23.107973955380711</v>
+        <v>42.327567967950763</v>
       </c>
       <c r="AD33" t="s">
         <v>307</v>
@@ -9591,13 +9591,13 @@
         <v>585</v>
       </c>
       <c r="AN33" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="AO33">
-        <v>0.99856107979091546</v>
+        <v>0.99828876210676587</v>
       </c>
       <c r="AP33">
-        <v>26.622770797002293</v>
+        <v>28.334088028040785</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9662,16 +9662,16 @@
         <v>356</v>
       </c>
       <c r="Y34" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Z34" t="s">
         <v>437</v>
       </c>
       <c r="AA34">
-        <v>0.99755900053893942</v>
+        <v>0.99776786767941794</v>
       </c>
       <c r="AB34">
-        <v>42.327567967950763</v>
+        <v>27.059822883365296</v>
       </c>
       <c r="AD34" t="s">
         <v>307</v>
@@ -9701,13 +9701,13 @@
         <v>586</v>
       </c>
       <c r="AN34" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AO34">
-        <v>0.99751816641322844</v>
+        <v>0.9980121476893673</v>
       </c>
       <c r="AP34">
-        <v>45.1502695224383</v>
+        <v>30.863466083156009</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9772,16 +9772,16 @@
         <v>358</v>
       </c>
       <c r="Y35" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Z35" t="s">
         <v>438</v>
       </c>
       <c r="AA35">
-        <v>0.99776786767941794</v>
+        <v>0.99789789449716026</v>
       </c>
       <c r="AB35">
-        <v>27.059822883365296</v>
+        <v>39.831307398714806</v>
       </c>
       <c r="AD35" t="s">
         <v>307</v>
@@ -9811,13 +9811,13 @@
         <v>587</v>
       </c>
       <c r="AN35" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AO35">
-        <v>0.99754431624006568</v>
+        <v>0.99811519908104196</v>
       </c>
       <c r="AP35">
-        <v>32.256845956342154</v>
+        <v>41.186340097586395</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9882,16 +9882,16 @@
         <v>360</v>
       </c>
       <c r="Y36" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="Z36" t="s">
         <v>439</v>
       </c>
       <c r="AA36">
-        <v>0.99789789449716026</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AB36">
-        <v>39.831307398714806</v>
+        <v>45.737867404715672</v>
       </c>
       <c r="AD36" t="s">
         <v>307</v>
@@ -9921,13 +9921,13 @@
         <v>588</v>
       </c>
       <c r="AN36" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="AO36">
-        <v>0.99755521694544447</v>
+        <v>0.99777778253795524</v>
       </c>
       <c r="AP36">
-        <v>50.682816539915542</v>
+        <v>36.020821886415746</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9992,16 +9992,16 @@
         <v>362</v>
       </c>
       <c r="Y37" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="Z37" t="s">
         <v>440</v>
       </c>
       <c r="AA37">
-        <v>0.99864365615724771</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AB37">
-        <v>45.737867404715672</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AD37" t="s">
         <v>307</v>
@@ -10031,13 +10031,13 @@
         <v>589</v>
       </c>
       <c r="AN37" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AO37">
-        <v>0.99984169097848852</v>
+        <v>0.99649252363612195</v>
       </c>
       <c r="AP37">
-        <v>2.9143415731308986</v>
+        <v>28.983218493781202</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10102,16 +10102,16 @@
         <v>364</v>
       </c>
       <c r="Y38" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="Z38" t="s">
         <v>441</v>
       </c>
       <c r="AA38">
-        <v>0.9991052659747558</v>
+        <v>0.99811506665856298</v>
       </c>
       <c r="AB38">
-        <v>12.019055461720432</v>
+        <v>35.874797800938026</v>
       </c>
       <c r="AD38" t="s">
         <v>307</v>
@@ -10141,13 +10141,13 @@
         <v>590</v>
       </c>
       <c r="AN38" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AO38">
-        <v>0.99777778253795524</v>
+        <v>0.99767811393002859</v>
       </c>
       <c r="AP38">
-        <v>36.020821886415746</v>
+        <v>30.875049982999808</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10212,16 +10212,16 @@
         <v>366</v>
       </c>
       <c r="Y39" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Z39" t="s">
         <v>442</v>
       </c>
       <c r="AA39">
-        <v>0.99679205626668776</v>
+        <v>0.99852418793335518</v>
       </c>
       <c r="AB39">
-        <v>28.983218493781202</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AD39" t="s">
         <v>307</v>
@@ -10251,13 +10251,13 @@
         <v>591</v>
       </c>
       <c r="AN39" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="AO39">
-        <v>0.99863161241655762</v>
+        <v>0.99764304373832691</v>
       </c>
       <c r="AP39">
-        <v>48.306707937232645</v>
+        <v>42.327567967950763</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10322,16 +10322,16 @@
         <v>368</v>
       </c>
       <c r="Y40" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z40" t="s">
         <v>443</v>
       </c>
       <c r="AA40">
-        <v>0.99713110094318969</v>
+        <v>0.99713671217394562</v>
       </c>
       <c r="AB40">
-        <v>34.34566125862937</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AD40" t="s">
         <v>307</v>
@@ -10361,13 +10361,13 @@
         <v>592</v>
       </c>
       <c r="AN40" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AO40">
-        <v>0.99864365615724771</v>
+        <v>0.99790384243262886</v>
       </c>
       <c r="AP40">
-        <v>24.883658184919245</v>
+        <v>72.461220387375079</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10432,16 +10432,16 @@
         <v>370</v>
       </c>
       <c r="Y41" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="Z41" t="s">
         <v>444</v>
       </c>
       <c r="AA41">
-        <v>0.99749963479302273</v>
+        <v>0.99774884372261763</v>
       </c>
       <c r="AB41">
-        <v>49.14481327115881</v>
+        <v>84.621736519387298</v>
       </c>
       <c r="AD41" t="s">
         <v>307</v>
@@ -10471,13 +10471,13 @@
         <v>593</v>
       </c>
       <c r="AN41" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="AO41">
-        <v>0.99837593922723478</v>
+        <v>0.99797028609854399</v>
       </c>
       <c r="AP41">
-        <v>25.205687076233477</v>
+        <v>34.892661212818595</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10542,16 +10542,16 @@
         <v>372</v>
       </c>
       <c r="Y42" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Z42" t="s">
         <v>445</v>
       </c>
       <c r="AA42">
-        <v>0.9985687661763365</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AB42">
-        <v>50.93040927578344</v>
+        <v>23.861203412894469</v>
       </c>
       <c r="AD42" t="s">
         <v>307</v>
@@ -10581,13 +10581,13 @@
         <v>594</v>
       </c>
       <c r="AN42" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="AO42">
-        <v>0.99757815671697558</v>
+        <v>0.99871472031655018</v>
       </c>
       <c r="AP42">
-        <v>51.990142494672078</v>
+        <v>28.428965886446147</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10652,16 +10652,16 @@
         <v>374</v>
       </c>
       <c r="Y43" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="Z43" t="s">
         <v>446</v>
       </c>
       <c r="AA43">
-        <v>0.99818574894902312</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AB43">
-        <v>33.253084498654445</v>
+        <v>40.332510468654611</v>
       </c>
       <c r="AD43" t="s">
         <v>307</v>
@@ -10691,13 +10691,13 @@
         <v>595</v>
       </c>
       <c r="AN43" t="s">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="AO43">
-        <v>0.99916488913437129</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AP43">
-        <v>15.260625790927634</v>
+        <v>23.861203412894469</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10801,13 +10801,13 @@
         <v>596</v>
       </c>
       <c r="AN44" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="AO44">
-        <v>0.99729296780855581</v>
+        <v>0.99751816641322844</v>
       </c>
       <c r="AP44">
-        <v>49.14481327115881</v>
+        <v>45.1502695224383</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10911,13 +10911,13 @@
         <v>597</v>
       </c>
       <c r="AN45" t="s">
-        <v>419</v>
+        <v>461</v>
       </c>
       <c r="AO45">
-        <v>0.99921633401208909</v>
+        <v>0.99754431624006568</v>
       </c>
       <c r="AP45">
-        <v>12.729766626457181</v>
+        <v>32.256845956342154</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -11021,13 +11021,13 @@
         <v>598</v>
       </c>
       <c r="AN46" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO46">
-        <v>0.99632737337312927</v>
+        <v>0.99755521694544447</v>
       </c>
       <c r="AP46">
-        <v>48.031259731727893</v>
+        <v>50.682816539915542</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -11131,13 +11131,13 @@
         <v>599</v>
       </c>
       <c r="AN47" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="AO47">
-        <v>0.99739127962445018</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AP47">
-        <v>39.831307398714806</v>
+        <v>2.9143415731308986</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -11241,13 +11241,13 @@
         <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="AO48">
-        <v>0.99818574894902312</v>
+        <v>0.99885698485202501</v>
       </c>
       <c r="AP48">
-        <v>33.253084498654445</v>
+        <v>25.256759506353582</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -11351,13 +11351,13 @@
         <v>601</v>
       </c>
       <c r="AN49" t="s">
-        <v>458</v>
+        <v>419</v>
       </c>
       <c r="AO49">
-        <v>0.99853353101054187</v>
+        <v>0.99709581552680626</v>
       </c>
       <c r="AP49">
-        <v>18.693183403514499</v>
+        <v>53.231766754458491</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -11422,16 +11422,16 @@
         <v>388</v>
       </c>
       <c r="Y50" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="Z50" t="s">
         <v>453</v>
       </c>
       <c r="AA50">
-        <v>0.99751567592854107</v>
+        <v>0.99815889366481214</v>
       </c>
       <c r="AB50">
-        <v>46.334800039670455</v>
+        <v>34.892661212818595</v>
       </c>
       <c r="AD50" t="s">
         <v>307</v>
@@ -11461,13 +11461,13 @@
         <v>602</v>
       </c>
       <c r="AN50" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="AO50">
-        <v>0.99747843498043831</v>
+        <v>0.99863950725251116</v>
       </c>
       <c r="AP50">
-        <v>46.334800039670455</v>
+        <v>34.387878972174441</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -11532,16 +11532,16 @@
         <v>390</v>
       </c>
       <c r="Y51" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="Z51" t="s">
         <v>454</v>
       </c>
       <c r="AA51">
-        <v>0.99871805281197423</v>
+        <v>0.99762279320259084</v>
       </c>
       <c r="AB51">
-        <v>25.256759506353582</v>
+        <v>50.682816539915542</v>
       </c>
       <c r="AD51" t="s">
         <v>307</v>
@@ -11571,13 +11571,13 @@
         <v>603</v>
       </c>
       <c r="AN51" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="AO51">
-        <v>0.99466341005350978</v>
+        <v>0.99837520457423046</v>
       </c>
       <c r="AP51">
-        <v>58.229467192272445</v>
+        <v>29.909469717927731</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -11642,16 +11642,16 @@
         <v>392</v>
       </c>
       <c r="Y52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Z52" t="s">
         <v>455</v>
       </c>
       <c r="AA52">
-        <v>0.99637763901827192</v>
+        <v>0.99782727135381688</v>
       </c>
       <c r="AB52">
-        <v>48.031259731727893</v>
+        <v>30.875049982999808</v>
       </c>
       <c r="AD52" t="s">
         <v>307</v>
@@ -11681,13 +11681,13 @@
         <v>604</v>
       </c>
       <c r="AN52" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AO52">
-        <v>0.9977732948939011</v>
+        <v>0.99632737337312927</v>
       </c>
       <c r="AP52">
-        <v>51.165698000691506</v>
+        <v>48.031259731727893</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -11752,16 +11752,16 @@
         <v>394</v>
       </c>
       <c r="Y53" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="Z53" t="s">
         <v>456</v>
       </c>
       <c r="AA53">
-        <v>0.99873544632009026</v>
+        <v>0.99795655945864681</v>
       </c>
       <c r="AB53">
-        <v>34.387878972174441</v>
+        <v>75.277133913292474</v>
       </c>
       <c r="AD53" t="s">
         <v>307</v>
@@ -11791,13 +11791,13 @@
         <v>605</v>
       </c>
       <c r="AN53" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="AO53">
-        <v>0.99872758388674931</v>
+        <v>0.99739127962445018</v>
       </c>
       <c r="AP53">
-        <v>23.31941562731657</v>
+        <v>39.831307398714806</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -11862,16 +11862,16 @@
         <v>396</v>
       </c>
       <c r="Y54" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="Z54" t="s">
         <v>457</v>
       </c>
       <c r="AA54">
-        <v>0.99834689519829145</v>
+        <v>0.99874893763362849</v>
       </c>
       <c r="AB54">
-        <v>32.749623583141812</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AD54" t="s">
         <v>307</v>
@@ -11901,13 +11901,13 @@
         <v>606</v>
       </c>
       <c r="AN54" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AO54">
-        <v>0.99871472031655018</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AP54">
-        <v>28.428965886446147</v>
+        <v>33.253084498654445</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -11972,16 +11972,16 @@
         <v>398</v>
       </c>
       <c r="Y55" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="Z55" t="s">
         <v>458</v>
       </c>
       <c r="AA55">
-        <v>0.99853303004525662</v>
+        <v>0.99751567592854107</v>
       </c>
       <c r="AB55">
-        <v>18.693183403514499</v>
+        <v>46.334800039670455</v>
       </c>
       <c r="AD55" t="s">
         <v>307</v>
@@ -12011,13 +12011,13 @@
         <v>607</v>
       </c>
       <c r="AN55" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="AO55">
-        <v>0.99782029353787438</v>
+        <v>0.99853353101054187</v>
       </c>
       <c r="AP55">
-        <v>23.861203412894469</v>
+        <v>18.693183403514499</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -12082,16 +12082,16 @@
         <v>400</v>
       </c>
       <c r="Y56" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z56" t="s">
         <v>459</v>
       </c>
       <c r="AA56">
-        <v>0.99762279320259084</v>
+        <v>0.99834689519829145</v>
       </c>
       <c r="AB56">
-        <v>50.682816539915542</v>
+        <v>32.749623583141812</v>
       </c>
       <c r="AD56" t="s">
         <v>307</v>
@@ -12121,13 +12121,13 @@
         <v>608</v>
       </c>
       <c r="AN56" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AO56">
-        <v>0.99885698485202501</v>
+        <v>0.99747843498043831</v>
       </c>
       <c r="AP56">
-        <v>25.256759506353582</v>
+        <v>46.334800039670455</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -12192,16 +12192,16 @@
         <v>402</v>
       </c>
       <c r="Y57" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="Z57" t="s">
         <v>460</v>
       </c>
       <c r="AA57">
-        <v>0.99782727135381688</v>
+        <v>0.99853303004525662</v>
       </c>
       <c r="AB57">
-        <v>30.875049982999808</v>
+        <v>18.693183403514499</v>
       </c>
       <c r="AD57" t="s">
         <v>307</v>
@@ -12231,13 +12231,13 @@
         <v>609</v>
       </c>
       <c r="AN57" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="AO57">
-        <v>0.99709581552680626</v>
+        <v>0.99466341005350978</v>
       </c>
       <c r="AP57">
-        <v>53.231766754458491</v>
+        <v>58.229467192272445</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -12302,16 +12302,16 @@
         <v>404</v>
       </c>
       <c r="Y58" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="Z58" t="s">
         <v>461</v>
       </c>
       <c r="AA58">
-        <v>0.99795655945864681</v>
+        <v>0.99761913939972058</v>
       </c>
       <c r="AB58">
-        <v>75.277133913292474</v>
+        <v>32.256845956342154</v>
       </c>
       <c r="AD58" t="s">
         <v>307</v>
@@ -12341,13 +12341,13 @@
         <v>610</v>
       </c>
       <c r="AN58" t="s">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="AO58">
-        <v>0.99863950725251116</v>
+        <v>0.9977732948939011</v>
       </c>
       <c r="AP58">
-        <v>34.387878972174441</v>
+        <v>51.165698000691506</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -12412,16 +12412,16 @@
         <v>406</v>
       </c>
       <c r="Y59" t="s">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="Z59" t="s">
         <v>462</v>
       </c>
       <c r="AA59">
-        <v>0.99874893763362849</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AB59">
-        <v>27.496123184453968</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AD59" t="s">
         <v>307</v>
@@ -12451,13 +12451,13 @@
         <v>611</v>
       </c>
       <c r="AN59" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AO59">
-        <v>0.99837520457423046</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AP59">
-        <v>29.909469717927731</v>
+        <v>23.31941562731657</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -12522,16 +12522,16 @@
         <v>408</v>
       </c>
       <c r="Y60" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="Z60" t="s">
         <v>463</v>
       </c>
       <c r="AA60">
-        <v>0.99754569173664964</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AB60">
-        <v>45.1502695224383</v>
+        <v>12.729766626457181</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -12596,16 +12596,16 @@
         <v>410</v>
       </c>
       <c r="Y61" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="Z61" t="s">
         <v>464</v>
       </c>
       <c r="AA61">
-        <v>0.99697644816659792</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AB61">
-        <v>58.519281729791345</v>
+        <v>2.9143415731308986</v>
       </c>
     </row>
   </sheetData>
@@ -12614,7 +12614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECAC020-A819-48EB-AFC7-F2F34A8A2AAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F18D53C-086C-4BFA-B8F2-7D759E1D358F}">
   <dimension ref="B9:Z59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12726,7 +12726,7 @@
         <v>642</v>
       </c>
       <c r="K11" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="L11">
         <v>0.64021427611097514</v>
@@ -12759,7 +12759,7 @@
         <v>740</v>
       </c>
       <c r="X11" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="Y11">
         <v>17.603249999999999</v>
@@ -12794,7 +12794,7 @@
         <v>644</v>
       </c>
       <c r="K12" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="L12">
         <v>3.683157674608327</v>
@@ -12827,7 +12827,7 @@
         <v>742</v>
       </c>
       <c r="X12" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="Y12">
         <v>11.58525</v>
@@ -12862,7 +12862,7 @@
         <v>646</v>
       </c>
       <c r="K13" t="s">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="L13">
         <v>1.1133782162108721</v>
@@ -12895,7 +12895,7 @@
         <v>744</v>
       </c>
       <c r="X13" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Y13">
         <v>5.7000000000000002E-2</v>
@@ -12930,7 +12930,7 @@
         <v>648</v>
       </c>
       <c r="K14" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="L14">
         <v>2.5290705136145335</v>
@@ -12963,7 +12963,7 @@
         <v>746</v>
       </c>
       <c r="X14" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="Y14">
         <v>11.2965</v>
@@ -12998,7 +12998,7 @@
         <v>650</v>
       </c>
       <c r="K15" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="L15">
         <v>2.1620342624302693</v>
@@ -13031,7 +13031,7 @@
         <v>748</v>
       </c>
       <c r="X15" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="Y15">
         <v>0.83925000000000005</v>
@@ -13066,7 +13066,7 @@
         <v>652</v>
       </c>
       <c r="K16" t="s">
-        <v>593</v>
+        <v>568</v>
       </c>
       <c r="L16">
         <v>0.10228431008717309</v>
@@ -13099,7 +13099,7 @@
         <v>750</v>
       </c>
       <c r="X16" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="Y16">
         <v>2.0332499999999998</v>
@@ -13134,7 +13134,7 @@
         <v>654</v>
       </c>
       <c r="K17" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="L17">
         <v>0.26374115795515951</v>
@@ -13167,7 +13167,7 @@
         <v>752</v>
       </c>
       <c r="X17" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="Y17">
         <v>5.8237500000000004</v>
@@ -13202,7 +13202,7 @@
         <v>656</v>
       </c>
       <c r="K18" t="s">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="L18">
         <v>1.0775690479395925</v>
@@ -13235,7 +13235,7 @@
         <v>754</v>
       </c>
       <c r="X18" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Y18">
         <v>16.887</v>
@@ -13270,7 +13270,7 @@
         <v>658</v>
       </c>
       <c r="K19" t="s">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="L19">
         <v>1.644864133979123</v>
@@ -13303,7 +13303,7 @@
         <v>756</v>
       </c>
       <c r="X19" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="Y19">
         <v>17.089500000000001</v>
@@ -13338,7 +13338,7 @@
         <v>660</v>
       </c>
       <c r="K20" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="L20">
         <v>4.1793335626386838</v>
@@ -13371,7 +13371,7 @@
         <v>758</v>
       </c>
       <c r="X20" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="Y20">
         <v>5.4255000000000004</v>
@@ -13406,7 +13406,7 @@
         <v>662</v>
       </c>
       <c r="K21" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="L21">
         <v>0.10220883742433164</v>
@@ -13441,7 +13441,7 @@
         <v>664</v>
       </c>
       <c r="K22" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="L22">
         <v>3.2456117052218421</v>
@@ -13476,7 +13476,7 @@
         <v>666</v>
       </c>
       <c r="K23" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="L23">
         <v>3.822617103272679</v>
@@ -13511,7 +13511,7 @@
         <v>668</v>
       </c>
       <c r="K24" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L24">
         <v>0.18120178223038519</v>
@@ -13546,7 +13546,7 @@
         <v>670</v>
       </c>
       <c r="K25" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="L25">
         <v>1.2636771265917695</v>
@@ -13581,7 +13581,7 @@
         <v>672</v>
       </c>
       <c r="K26" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="L26">
         <v>2.5500240416298969</v>
@@ -13616,7 +13616,7 @@
         <v>674</v>
       </c>
       <c r="K27" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="L27">
         <v>4.0346953063254611</v>
@@ -13651,7 +13651,7 @@
         <v>676</v>
       </c>
       <c r="K28" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="L28">
         <v>2.4674795572908166</v>
@@ -13686,7 +13686,7 @@
         <v>678</v>
       </c>
       <c r="K29" t="s">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="L29">
         <v>0.19671799304243257</v>
@@ -13721,7 +13721,7 @@
         <v>680</v>
       </c>
       <c r="K30" t="s">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="L30">
         <v>0.46906534608342149</v>
@@ -13756,7 +13756,7 @@
         <v>682</v>
       </c>
       <c r="K31" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="L31">
         <v>0.70432433684539619</v>
@@ -13791,7 +13791,7 @@
         <v>684</v>
       </c>
       <c r="K32" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="L32">
         <v>0.14326997649193718</v>
@@ -13826,7 +13826,7 @@
         <v>686</v>
       </c>
       <c r="K33" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="L33">
         <v>2.5135228824118248E-2</v>
@@ -13861,7 +13861,7 @@
         <v>688</v>
       </c>
       <c r="K34" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="L34">
         <v>0.60333316217563482</v>
@@ -13896,7 +13896,7 @@
         <v>690</v>
       </c>
       <c r="K35" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="L35">
         <v>0.61002023046213527</v>
@@ -13931,7 +13931,7 @@
         <v>692</v>
       </c>
       <c r="K36" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="L36">
         <v>5.5124889677616896E-2</v>
@@ -13966,7 +13966,7 @@
         <v>694</v>
       </c>
       <c r="K37" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="L37">
         <v>0.19696072330654418</v>
@@ -14001,7 +14001,7 @@
         <v>696</v>
       </c>
       <c r="K38" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="L38">
         <v>0.37453679972687481</v>
@@ -14036,7 +14036,7 @@
         <v>698</v>
       </c>
       <c r="K39" t="s">
-        <v>596</v>
+        <v>571</v>
       </c>
       <c r="L39">
         <v>2.9266524214395733</v>
@@ -14071,7 +14071,7 @@
         <v>700</v>
       </c>
       <c r="K40" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="L40">
         <v>0.46102512715199689</v>
@@ -14106,7 +14106,7 @@
         <v>702</v>
       </c>
       <c r="K41" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -14141,7 +14141,7 @@
         <v>704</v>
       </c>
       <c r="K42" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="L42">
         <v>1.9780607647145438</v>
@@ -14176,7 +14176,7 @@
         <v>706</v>
       </c>
       <c r="K43" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="L43">
         <v>0.80689812107944159</v>
@@ -14211,7 +14211,7 @@
         <v>708</v>
       </c>
       <c r="K44" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="L44">
         <v>0.1886799653533156</v>
@@ -14246,7 +14246,7 @@
         <v>710</v>
       </c>
       <c r="K45" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="L45">
         <v>2.577065692017253</v>
@@ -14281,7 +14281,7 @@
         <v>712</v>
       </c>
       <c r="K46" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="L46">
         <v>0.32349873740765611</v>
@@ -14316,7 +14316,7 @@
         <v>714</v>
       </c>
       <c r="K47" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -14351,7 +14351,7 @@
         <v>716</v>
       </c>
       <c r="K48" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="L48">
         <v>2.3210450729876548</v>
@@ -14386,7 +14386,7 @@
         <v>718</v>
       </c>
       <c r="K49" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="L49">
         <v>1.4641560353950904</v>
@@ -14421,7 +14421,7 @@
         <v>720</v>
       </c>
       <c r="K50" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="L50">
         <v>4.3172734082397007E-3</v>
@@ -14456,7 +14456,7 @@
         <v>722</v>
       </c>
       <c r="K51" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="L51">
         <v>2.3327457542865271</v>
@@ -14491,7 +14491,7 @@
         <v>724</v>
       </c>
       <c r="K52" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L52">
         <v>0.64220735366408732</v>
@@ -14526,7 +14526,7 @@
         <v>726</v>
       </c>
       <c r="K53" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="L53">
         <v>0.20805219904440039</v>
@@ -14561,7 +14561,7 @@
         <v>728</v>
       </c>
       <c r="K54" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="L54">
         <v>1.3018026354345156</v>
@@ -14596,7 +14596,7 @@
         <v>730</v>
       </c>
       <c r="K55" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="L55">
         <v>3.0871018425456893</v>
@@ -14631,7 +14631,7 @@
         <v>732</v>
       </c>
       <c r="K56" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="L56">
         <v>3.1635610249840389</v>
@@ -14666,7 +14666,7 @@
         <v>734</v>
       </c>
       <c r="K57" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="L57">
         <v>9.3245940212150449E-2</v>
@@ -14701,7 +14701,7 @@
         <v>736</v>
       </c>
       <c r="K58" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="L58">
         <v>0.28717016660662842</v>
@@ -14736,7 +14736,7 @@
         <v>738</v>
       </c>
       <c r="K59" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="L59">
         <v>0.93964202108728523</v>
@@ -14751,7 +14751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D3FCDC-5602-43D0-883A-7B167AEBAFDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC1595FB-6545-4ACA-86F6-F4D97F7510B6}">
   <dimension ref="B9:Y159"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19812,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF145D08-0B5C-4735-B68B-EC4DE4451785}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89708DF2-013E-4029-A1C6-D0847F91082E}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832F994F-CFFF-454A-93ED-4EC6F4867A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACD74A6-C852-4DA5-BFA8-4B93D0619E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -990,18 +990,42 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_009</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_012</t>
   </si>
   <si>
@@ -1020,46 +1044,154 @@
     <t>connecting solar to buses in cluster 45</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_028</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
+    <t>distr_solelc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_001</t>
@@ -1080,54 +1212,6 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_016</t>
   </si>
   <si>
@@ -1194,90 +1278,6 @@
     <t>connecting solar to buses in cluster 51</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_004</t>
   </si>
   <si>
@@ -1308,6 +1308,18 @@
     <t>ncap_cost~USD22</t>
   </si>
   <si>
+    <t>e_Skawina_POL</t>
+  </si>
+  <si>
+    <t>e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Mielec_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
     <t>e_Slupsk_POL</t>
   </si>
   <si>
@@ -1320,25 +1332,79 @@
     <t>e_BielskoBiala_POL</t>
   </si>
   <si>
+    <t>e_Lukow_POL</t>
+  </si>
+  <si>
+    <t>e_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>e_Radom_POL</t>
+  </si>
+  <si>
+    <t>e_Lodz_POL</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
     <t>e_Rzeszow_POL</t>
   </si>
   <si>
-    <t>e_Skawina_POL</t>
-  </si>
-  <si>
-    <t>e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Mielec_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Wloclawek_POL</t>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>e_Grajewo_POL</t>
   </si>
   <si>
     <t>e_Bydgoszcz_POL</t>
@@ -1350,30 +1416,6 @@
     <t>e_Tarnow_POL</t>
   </si>
   <si>
-    <t>e_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Lukow_POL</t>
-  </si>
-  <si>
-    <t>e_Swidnica_POL</t>
-  </si>
-  <si>
-    <t>e_Radom_POL</t>
-  </si>
-  <si>
-    <t>e_Lodz_POL</t>
-  </si>
-  <si>
-    <t>e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>e_Szczecin_POL</t>
-  </si>
-  <si>
     <t>e_Lublin_POL</t>
   </si>
   <si>
@@ -1407,48 +1449,6 @@
     <t>e_Pulawy_POL</t>
   </si>
   <si>
-    <t>e_Lubin_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>e_Poznan_POL</t>
-  </si>
-  <si>
-    <t>e_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>e_Konin_POL</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>e_Czestochowa_POL</t>
-  </si>
-  <si>
     <t>e_Siedlce_POL</t>
   </si>
   <si>
@@ -1461,6 +1461,228 @@
     <t>e_Zabrze_POL</t>
   </si>
   <si>
+    <t>distr_wonelc_won_POL_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_POL_003</t>
   </si>
   <si>
@@ -1473,90 +1695,6 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_007</t>
   </si>
   <si>
@@ -1569,144 +1707,6 @@
     <t>connecting wind onshore to buses in cluster 34</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_015</t>
   </si>
   <si>
@@ -1755,129 +1755,129 @@
     <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_049</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
+  </si>
+  <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
     <t>elc_won_POL_020</t>
   </si>
   <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>elc_won_POL_049</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
     <t>elc_won_POL_034</t>
   </si>
   <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>elc_won_POL_041</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>elc_won_POL_042</t>
-  </si>
-  <si>
-    <t>elc_won_POL_030</t>
-  </si>
-  <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>elc_won_POL_032</t>
-  </si>
-  <si>
-    <t>elc_won_POL_026</t>
-  </si>
-  <si>
-    <t>elc_won_POL_048</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>elc_won_POL_037</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>elc_won_POL_023</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
-  </si>
-  <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
@@ -1902,12 +1902,36 @@
     <t>elc_won_POL_047</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_004</t>
   </si>
   <si>
@@ -1926,10 +1950,10 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_009</t>
@@ -1938,33 +1962,21 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
+    <t>elc_wof_POL_002</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
   </si>
   <si>
+    <t>elc_wof_POL_003</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
@@ -1974,22 +1986,10 @@
     <t>elc_wof_POL_010</t>
   </si>
   <si>
-    <t>elc_wof_POL_002</t>
+    <t>elc_wof_POL_006</t>
   </si>
   <si>
     <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -6534,7 +6534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195ABC74-6C60-4C90-BAEA-2981B74B18A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E9CA94-CC50-4553-97C2-3590B0A62FA7}">
   <dimension ref="B9:BD61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6772,16 +6772,16 @@
         <v>308</v>
       </c>
       <c r="Y11" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="Z11" t="s">
         <v>414</v>
       </c>
       <c r="AA11">
-        <v>0.99679205626668776</v>
+        <v>0.99751836673919181</v>
       </c>
       <c r="AB11">
-        <v>28.983218493781202</v>
+        <v>50.515025114296037</v>
       </c>
       <c r="AD11" t="s">
         <v>307</v>
@@ -6811,13 +6811,13 @@
         <v>563</v>
       </c>
       <c r="AN11" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="AO11">
-        <v>0.99790284855194045</v>
+        <v>0.99828876210676587</v>
       </c>
       <c r="AP11">
-        <v>35.874797800938026</v>
+        <v>28.334088028040785</v>
       </c>
       <c r="AR11" t="s">
         <v>307</v>
@@ -6847,13 +6847,13 @@
         <v>632</v>
       </c>
       <c r="BB11" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="BC11">
-        <v>0.99436455351944619</v>
+        <v>0.99478860441526007</v>
       </c>
       <c r="BD11">
-        <v>728.41730490967211</v>
+        <v>610.20976015093845</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6918,16 +6918,16 @@
         <v>312</v>
       </c>
       <c r="Y12" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="Z12" t="s">
         <v>415</v>
       </c>
       <c r="AA12">
-        <v>0.99713110094318969</v>
+        <v>0.99774808836727491</v>
       </c>
       <c r="AB12">
-        <v>34.34566125862937</v>
+        <v>41.186340097586395</v>
       </c>
       <c r="AD12" t="s">
         <v>307</v>
@@ -6957,13 +6957,13 @@
         <v>564</v>
       </c>
       <c r="AN12" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AO12">
-        <v>0.99856107979091546</v>
+        <v>0.99777778253795524</v>
       </c>
       <c r="AP12">
-        <v>26.622770797002293</v>
+        <v>36.020821886415746</v>
       </c>
       <c r="AR12" t="s">
         <v>307</v>
@@ -6993,13 +6993,13 @@
         <v>633</v>
       </c>
       <c r="BB12" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="BC12">
-        <v>0.99671396210736585</v>
+        <v>0.99436455351944619</v>
       </c>
       <c r="BD12">
-        <v>535.75153841730867</v>
+        <v>728.41730490967211</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7064,16 +7064,16 @@
         <v>314</v>
       </c>
       <c r="Y13" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z13" t="s">
         <v>416</v>
       </c>
       <c r="AA13">
-        <v>0.99749963479302273</v>
+        <v>0.99828790514523624</v>
       </c>
       <c r="AB13">
-        <v>49.14481327115881</v>
+        <v>28.428965886446147</v>
       </c>
       <c r="AD13" t="s">
         <v>307</v>
@@ -7103,13 +7103,13 @@
         <v>565</v>
       </c>
       <c r="AN13" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="AO13">
-        <v>0.99845480529905328</v>
+        <v>0.9967210177786987</v>
       </c>
       <c r="AP13">
-        <v>47.820994144128512</v>
+        <v>34.34566125862937</v>
       </c>
       <c r="AR13" t="s">
         <v>307</v>
@@ -7139,13 +7139,13 @@
         <v>634</v>
       </c>
       <c r="BB13" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
       <c r="BC13">
-        <v>0.99498581429447941</v>
+        <v>0.99635015248973569</v>
       </c>
       <c r="BD13">
-        <v>682.74537814765154</v>
+        <v>366.10125775280716</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7210,16 +7210,16 @@
         <v>316</v>
       </c>
       <c r="Y14" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="Z14" t="s">
         <v>417</v>
       </c>
       <c r="AA14">
-        <v>0.9985687661763365</v>
+        <v>0.99815889366481214</v>
       </c>
       <c r="AB14">
-        <v>50.93040927578344</v>
+        <v>34.892661212818595</v>
       </c>
       <c r="AD14" t="s">
         <v>307</v>
@@ -7249,13 +7249,13 @@
         <v>566</v>
       </c>
       <c r="AN14" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="AO14">
-        <v>0.9991052659747558</v>
+        <v>0.99777922331243873</v>
       </c>
       <c r="AP14">
-        <v>12.019055461720432</v>
+        <v>61.086483632538339</v>
       </c>
       <c r="AR14" t="s">
         <v>307</v>
@@ -7285,13 +7285,13 @@
         <v>635</v>
       </c>
       <c r="BB14" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="BC14">
-        <v>0.99705787611047647</v>
+        <v>0.99503061728845632</v>
       </c>
       <c r="BD14">
-        <v>516.05305554711185</v>
+        <v>669.38461499965297</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7356,16 +7356,16 @@
         <v>318</v>
       </c>
       <c r="Y15" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="Z15" t="s">
         <v>418</v>
       </c>
       <c r="AA15">
-        <v>0.99818574894902312</v>
+        <v>0.99679205626668776</v>
       </c>
       <c r="AB15">
-        <v>33.253084498654445</v>
+        <v>28.983218493781202</v>
       </c>
       <c r="AD15" t="s">
         <v>307</v>
@@ -7395,13 +7395,13 @@
         <v>567</v>
       </c>
       <c r="AN15" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="AO15">
-        <v>0.99850473493624492</v>
+        <v>0.99777988747037838</v>
       </c>
       <c r="AP15">
-        <v>27.496123184453968</v>
+        <v>36.605495131795273</v>
       </c>
       <c r="AR15" t="s">
         <v>307</v>
@@ -7431,13 +7431,13 @@
         <v>636</v>
       </c>
       <c r="BB15" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="BC15">
-        <v>0.99478860441526007</v>
+        <v>0.99784666475123052</v>
       </c>
       <c r="BD15">
-        <v>610.20976015093845</v>
+        <v>434.14794560012712</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7502,16 +7502,16 @@
         <v>320</v>
       </c>
       <c r="Y16" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="Z16" t="s">
         <v>419</v>
       </c>
       <c r="AA16">
-        <v>0.99751836673919181</v>
+        <v>0.99713110094318969</v>
       </c>
       <c r="AB16">
-        <v>50.515025114296037</v>
+        <v>34.34566125862937</v>
       </c>
       <c r="AD16" t="s">
         <v>307</v>
@@ -7541,13 +7541,13 @@
         <v>568</v>
       </c>
       <c r="AN16" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO16">
-        <v>0.99837593922723478</v>
+        <v>0.9980121476893673</v>
       </c>
       <c r="AP16">
-        <v>25.205687076233477</v>
+        <v>30.863466083156009</v>
       </c>
       <c r="AR16" t="s">
         <v>307</v>
@@ -7577,13 +7577,13 @@
         <v>637</v>
       </c>
       <c r="BB16" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="BC16">
-        <v>0.99378504174620896</v>
+        <v>0.99671396210736585</v>
       </c>
       <c r="BD16">
-        <v>761.13276667340403</v>
+        <v>535.75153841730867</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7648,16 +7648,16 @@
         <v>322</v>
       </c>
       <c r="Y17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Z17" t="s">
         <v>420</v>
       </c>
       <c r="AA17">
-        <v>0.99774808836727491</v>
+        <v>0.99749963479302273</v>
       </c>
       <c r="AB17">
-        <v>41.186340097586395</v>
+        <v>49.14481327115881</v>
       </c>
       <c r="AD17" t="s">
         <v>307</v>
@@ -7687,13 +7687,13 @@
         <v>569</v>
       </c>
       <c r="AN17" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="AO17">
-        <v>0.99757815671697558</v>
+        <v>0.99811519908104196</v>
       </c>
       <c r="AP17">
-        <v>51.990142494672078</v>
+        <v>41.186340097586395</v>
       </c>
       <c r="AR17" t="s">
         <v>307</v>
@@ -7723,13 +7723,13 @@
         <v>638</v>
       </c>
       <c r="BB17" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="BC17">
-        <v>0.99503061728845632</v>
+        <v>0.99498581429447941</v>
       </c>
       <c r="BD17">
-        <v>669.38461499965297</v>
+        <v>682.74537814765154</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7794,16 +7794,16 @@
         <v>324</v>
       </c>
       <c r="Y18" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="Z18" t="s">
         <v>421</v>
       </c>
       <c r="AA18">
-        <v>0.99828790514523624</v>
+        <v>0.9985687661763365</v>
       </c>
       <c r="AB18">
-        <v>28.428965886446147</v>
+        <v>50.93040927578344</v>
       </c>
       <c r="AD18" t="s">
         <v>307</v>
@@ -7833,13 +7833,13 @@
         <v>570</v>
       </c>
       <c r="AN18" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="AO18">
-        <v>0.99916488913437129</v>
+        <v>0.99837593922723478</v>
       </c>
       <c r="AP18">
-        <v>15.260625790927634</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AR18" t="s">
         <v>307</v>
@@ -7869,13 +7869,13 @@
         <v>639</v>
       </c>
       <c r="BB18" t="s">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="BC18">
-        <v>0.99635015248973569</v>
+        <v>0.99705787611047647</v>
       </c>
       <c r="BD18">
-        <v>366.10125775280716</v>
+        <v>516.05305554711185</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7940,16 +7940,16 @@
         <v>326</v>
       </c>
       <c r="Y19" t="s">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="Z19" t="s">
         <v>422</v>
       </c>
       <c r="AA19">
-        <v>0.9978643471647114</v>
+        <v>0.99814724525850784</v>
       </c>
       <c r="AB19">
-        <v>31.560996462068374</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AD19" t="s">
         <v>307</v>
@@ -7979,13 +7979,13 @@
         <v>571</v>
       </c>
       <c r="AN19" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="AO19">
-        <v>0.99729296780855581</v>
+        <v>0.99757815671697558</v>
       </c>
       <c r="AP19">
-        <v>49.14481327115881</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AR19" t="s">
         <v>307</v>
@@ -8015,7 +8015,7 @@
         <v>640</v>
       </c>
       <c r="BB19" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="BC19">
         <v>0.99249606766869936</v>
@@ -8086,16 +8086,16 @@
         <v>328</v>
       </c>
       <c r="Y20" t="s">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="Z20" t="s">
         <v>423</v>
       </c>
       <c r="AA20">
-        <v>0.99789011269484895</v>
+        <v>0.99848201234520018</v>
       </c>
       <c r="AB20">
-        <v>36.605495131795273</v>
+        <v>72.463654284142635</v>
       </c>
       <c r="AD20" t="s">
         <v>307</v>
@@ -8125,13 +8125,13 @@
         <v>572</v>
       </c>
       <c r="AN20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AO20">
-        <v>0.99921633401208909</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AP20">
-        <v>12.729766626457181</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AR20" t="s">
         <v>307</v>
@@ -8161,13 +8161,13 @@
         <v>641</v>
       </c>
       <c r="BB20" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="BC20">
-        <v>0.99784666475123052</v>
+        <v>0.99378504174620896</v>
       </c>
       <c r="BD20">
-        <v>434.14794560012712</v>
+        <v>761.13276667340403</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8232,16 +8232,16 @@
         <v>330</v>
       </c>
       <c r="Y21" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="Z21" t="s">
         <v>424</v>
       </c>
       <c r="AA21">
-        <v>0.99783121031362565</v>
+        <v>0.99886290297361824</v>
       </c>
       <c r="AB21">
-        <v>51.165698000691506</v>
+        <v>26.622770797002293</v>
       </c>
       <c r="AD21" t="s">
         <v>307</v>
@@ -8271,13 +8271,13 @@
         <v>573</v>
       </c>
       <c r="AN21" t="s">
-        <v>456</v>
+        <v>420</v>
       </c>
       <c r="AO21">
-        <v>0.99839049347738307</v>
+        <v>0.99729296780855581</v>
       </c>
       <c r="AP21">
-        <v>75.277133913292474</v>
+        <v>49.14481327115881</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8342,16 +8342,16 @@
         <v>332</v>
       </c>
       <c r="Y22" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="Z22" t="s">
         <v>425</v>
       </c>
       <c r="AA22">
-        <v>0.99871805281197423</v>
+        <v>0.99779181951287421</v>
       </c>
       <c r="AB22">
-        <v>25.256759506353582</v>
+        <v>61.086483632538339</v>
       </c>
       <c r="AD22" t="s">
         <v>307</v>
@@ -8381,13 +8381,13 @@
         <v>574</v>
       </c>
       <c r="AN22" t="s">
-        <v>429</v>
+        <v>463</v>
       </c>
       <c r="AO22">
-        <v>0.99697913305259955</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AP22">
-        <v>58.519281729791345</v>
+        <v>12.729766626457181</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>334</v>
       </c>
       <c r="Y23" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s">
         <v>426</v>
       </c>
       <c r="AA23">
-        <v>0.99637763901827192</v>
+        <v>0.99762279320259084</v>
       </c>
       <c r="AB23">
-        <v>48.031259731727893</v>
+        <v>50.682816539915542</v>
       </c>
       <c r="AD23" t="s">
         <v>307</v>
@@ -8494,10 +8494,10 @@
         <v>447</v>
       </c>
       <c r="AO23">
-        <v>0.99757778563357669</v>
+        <v>0.99885698485202501</v>
       </c>
       <c r="AP23">
-        <v>45.221154662357485</v>
+        <v>25.256759506353582</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8562,16 +8562,16 @@
         <v>336</v>
       </c>
       <c r="Y24" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s">
         <v>427</v>
       </c>
       <c r="AA24">
-        <v>0.99873544632009026</v>
+        <v>0.99782727135381688</v>
       </c>
       <c r="AB24">
-        <v>34.387878972174441</v>
+        <v>30.875049982999808</v>
       </c>
       <c r="AD24" t="s">
         <v>307</v>
@@ -8601,13 +8601,13 @@
         <v>576</v>
       </c>
       <c r="AN24" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="AO24">
-        <v>0.99896573022887158</v>
+        <v>0.99709581552680626</v>
       </c>
       <c r="AP24">
-        <v>18.936001260254645</v>
+        <v>53.231766754458491</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>338</v>
       </c>
       <c r="Y25" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="Z25" t="s">
         <v>428</v>
       </c>
       <c r="AA25">
-        <v>0.99754569173664964</v>
+        <v>0.99795655945864681</v>
       </c>
       <c r="AB25">
-        <v>45.1502695224383</v>
+        <v>75.277133913292474</v>
       </c>
       <c r="AD25" t="s">
         <v>307</v>
@@ -8711,13 +8711,13 @@
         <v>577</v>
       </c>
       <c r="AN25" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO25">
-        <v>0.99813022065694434</v>
+        <v>0.99863950725251116</v>
       </c>
       <c r="AP25">
-        <v>40.332510468654611</v>
+        <v>34.387878972174441</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8782,16 +8782,16 @@
         <v>340</v>
       </c>
       <c r="Y26" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="Z26" t="s">
         <v>429</v>
       </c>
       <c r="AA26">
-        <v>0.99697644816659792</v>
+        <v>0.99874893763362849</v>
       </c>
       <c r="AB26">
-        <v>58.519281729791345</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AD26" t="s">
         <v>307</v>
@@ -8821,13 +8821,13 @@
         <v>578</v>
       </c>
       <c r="AN26" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="AO26">
-        <v>0.9975765595050764</v>
+        <v>0.99837520457423046</v>
       </c>
       <c r="AP26">
-        <v>31.560996462068374</v>
+        <v>29.909469717927731</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8892,16 +8892,16 @@
         <v>342</v>
       </c>
       <c r="Y27" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="Z27" t="s">
         <v>430</v>
       </c>
       <c r="AA27">
-        <v>0.99814724525850784</v>
+        <v>0.9978643471647114</v>
       </c>
       <c r="AB27">
-        <v>47.820994144128512</v>
+        <v>31.560996462068374</v>
       </c>
       <c r="AD27" t="s">
         <v>307</v>
@@ -8931,13 +8931,13 @@
         <v>579</v>
       </c>
       <c r="AN27" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="AO27">
-        <v>0.99863161241655762</v>
+        <v>0.99751816641322844</v>
       </c>
       <c r="AP27">
-        <v>48.306707937232645</v>
+        <v>45.1502695224383</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9002,16 +9002,16 @@
         <v>344</v>
       </c>
       <c r="Y28" t="s">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="Z28" t="s">
         <v>431</v>
       </c>
       <c r="AA28">
-        <v>0.99848201234520018</v>
+        <v>0.99789011269484895</v>
       </c>
       <c r="AB28">
-        <v>72.463654284142635</v>
+        <v>36.605495131795273</v>
       </c>
       <c r="AD28" t="s">
         <v>307</v>
@@ -9041,13 +9041,13 @@
         <v>580</v>
       </c>
       <c r="AN28" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="AO28">
-        <v>0.99864365615724771</v>
+        <v>0.99754431624006568</v>
       </c>
       <c r="AP28">
-        <v>24.883658184919245</v>
+        <v>32.256845956342154</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9112,16 +9112,16 @@
         <v>346</v>
       </c>
       <c r="Y29" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="Z29" t="s">
         <v>432</v>
       </c>
       <c r="AA29">
-        <v>0.99886290297361824</v>
+        <v>0.99783121031362565</v>
       </c>
       <c r="AB29">
-        <v>26.622770797002293</v>
+        <v>51.165698000691506</v>
       </c>
       <c r="AD29" t="s">
         <v>307</v>
@@ -9151,13 +9151,13 @@
         <v>581</v>
       </c>
       <c r="AN29" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="AO29">
-        <v>0.9967210177786987</v>
+        <v>0.99755521694544447</v>
       </c>
       <c r="AP29">
-        <v>34.34566125862937</v>
+        <v>50.682816539915542</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9222,16 +9222,16 @@
         <v>348</v>
       </c>
       <c r="Y30" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="Z30" t="s">
         <v>433</v>
       </c>
       <c r="AA30">
-        <v>0.99779181951287421</v>
+        <v>0.99818636444109388</v>
       </c>
       <c r="AB30">
-        <v>61.086483632538339</v>
+        <v>45.221154662357485</v>
       </c>
       <c r="AD30" t="s">
         <v>307</v>
@@ -9261,13 +9261,13 @@
         <v>582</v>
       </c>
       <c r="AN30" t="s">
-        <v>433</v>
+        <v>464</v>
       </c>
       <c r="AO30">
-        <v>0.99777922331243873</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AP30">
-        <v>61.086483632538339</v>
+        <v>2.9143415731308986</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9332,16 +9332,16 @@
         <v>350</v>
       </c>
       <c r="Y31" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="Z31" t="s">
         <v>434</v>
       </c>
       <c r="AA31">
-        <v>0.9976031883518911</v>
+        <v>0.99843994478948561</v>
       </c>
       <c r="AB31">
-        <v>58.963512461864056</v>
+        <v>28.334088028040785</v>
       </c>
       <c r="AD31" t="s">
         <v>307</v>
@@ -9371,13 +9371,13 @@
         <v>583</v>
       </c>
       <c r="AN31" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AO31">
-        <v>0.99777988747037838</v>
+        <v>0.99839049347738307</v>
       </c>
       <c r="AP31">
-        <v>36.605495131795273</v>
+        <v>75.277133913292474</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9442,16 +9442,16 @@
         <v>352</v>
       </c>
       <c r="Y32" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="Z32" t="s">
         <v>435</v>
       </c>
       <c r="AA32">
-        <v>0.99870289970840342</v>
+        <v>0.9983322364125492</v>
       </c>
       <c r="AB32">
-        <v>23.107973955380711</v>
+        <v>27.248239083262582</v>
       </c>
       <c r="AD32" t="s">
         <v>307</v>
@@ -9481,13 +9481,13 @@
         <v>584</v>
       </c>
       <c r="AN32" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AO32">
-        <v>0.99870289970840342</v>
+        <v>0.99697913305259955</v>
       </c>
       <c r="AP32">
-        <v>23.107973955380711</v>
+        <v>58.519281729791345</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9552,16 +9552,16 @@
         <v>354</v>
       </c>
       <c r="Y33" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="Z33" t="s">
         <v>436</v>
       </c>
       <c r="AA33">
-        <v>0.99755900053893942</v>
+        <v>0.99795611274367535</v>
       </c>
       <c r="AB33">
-        <v>42.327567967950763</v>
+        <v>29.909469717927731</v>
       </c>
       <c r="AD33" t="s">
         <v>307</v>
@@ -9591,13 +9591,13 @@
         <v>585</v>
       </c>
       <c r="AN33" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="AO33">
-        <v>0.99828876210676587</v>
+        <v>0.99757778563357669</v>
       </c>
       <c r="AP33">
-        <v>28.334088028040785</v>
+        <v>45.221154662357485</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9662,16 +9662,16 @@
         <v>356</v>
       </c>
       <c r="Y34" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="Z34" t="s">
         <v>437</v>
       </c>
       <c r="AA34">
-        <v>0.99776786767941794</v>
+        <v>0.99756835894174822</v>
       </c>
       <c r="AB34">
-        <v>27.059822883365296</v>
+        <v>36.020821886415746</v>
       </c>
       <c r="AD34" t="s">
         <v>307</v>
@@ -9701,13 +9701,13 @@
         <v>586</v>
       </c>
       <c r="AN34" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="AO34">
-        <v>0.9980121476893673</v>
+        <v>0.99896573022887158</v>
       </c>
       <c r="AP34">
-        <v>30.863466083156009</v>
+        <v>18.936001260254645</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9772,16 +9772,16 @@
         <v>358</v>
       </c>
       <c r="Y35" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="Z35" t="s">
         <v>438</v>
       </c>
       <c r="AA35">
-        <v>0.99789789449716026</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AB35">
-        <v>39.831307398714806</v>
+        <v>23.31941562731657</v>
       </c>
       <c r="AD35" t="s">
         <v>307</v>
@@ -9811,13 +9811,13 @@
         <v>587</v>
       </c>
       <c r="AN35" t="s">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="AO35">
-        <v>0.99811519908104196</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AP35">
-        <v>41.186340097586395</v>
+        <v>40.332510468654611</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9882,16 +9882,16 @@
         <v>360</v>
       </c>
       <c r="Y36" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="Z36" t="s">
         <v>439</v>
       </c>
       <c r="AA36">
-        <v>0.99864365615724771</v>
+        <v>0.9976031883518911</v>
       </c>
       <c r="AB36">
-        <v>45.737867404715672</v>
+        <v>58.963512461864056</v>
       </c>
       <c r="AD36" t="s">
         <v>307</v>
@@ -9921,13 +9921,13 @@
         <v>588</v>
       </c>
       <c r="AN36" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="AO36">
-        <v>0.99777778253795524</v>
+        <v>0.9975765595050764</v>
       </c>
       <c r="AP36">
-        <v>36.020821886415746</v>
+        <v>31.560996462068374</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9992,16 +9992,16 @@
         <v>362</v>
       </c>
       <c r="Y37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Z37" t="s">
         <v>440</v>
       </c>
       <c r="AA37">
-        <v>0.9991052659747558</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AB37">
-        <v>12.019055461720432</v>
+        <v>23.107973955380711</v>
       </c>
       <c r="AD37" t="s">
         <v>307</v>
@@ -10031,7 +10031,7 @@
         <v>589</v>
       </c>
       <c r="AN37" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AO37">
         <v>0.99649252363612195</v>
@@ -10102,16 +10102,16 @@
         <v>364</v>
       </c>
       <c r="Y38" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="Z38" t="s">
         <v>441</v>
       </c>
       <c r="AA38">
-        <v>0.99811506665856298</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AB38">
-        <v>35.874797800938026</v>
+        <v>33.253084498654445</v>
       </c>
       <c r="AD38" t="s">
         <v>307</v>
@@ -10141,7 +10141,7 @@
         <v>590</v>
       </c>
       <c r="AN38" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="AO38">
         <v>0.99767811393002859</v>
@@ -10212,16 +10212,16 @@
         <v>366</v>
       </c>
       <c r="Y39" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="Z39" t="s">
         <v>442</v>
       </c>
       <c r="AA39">
-        <v>0.99852418793335518</v>
+        <v>0.99751567592854107</v>
       </c>
       <c r="AB39">
-        <v>25.205687076233477</v>
+        <v>46.334800039670455</v>
       </c>
       <c r="AD39" t="s">
         <v>307</v>
@@ -10251,7 +10251,7 @@
         <v>591</v>
       </c>
       <c r="AN39" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="AO39">
         <v>0.99764304373832691</v>
@@ -10322,16 +10322,16 @@
         <v>368</v>
       </c>
       <c r="Y40" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Z40" t="s">
         <v>443</v>
       </c>
       <c r="AA40">
-        <v>0.99713671217394562</v>
+        <v>0.99834689519829145</v>
       </c>
       <c r="AB40">
-        <v>51.990142494672078</v>
+        <v>32.749623583141812</v>
       </c>
       <c r="AD40" t="s">
         <v>307</v>
@@ -10361,7 +10361,7 @@
         <v>592</v>
       </c>
       <c r="AN40" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="AO40">
         <v>0.99790384243262886</v>
@@ -10432,16 +10432,16 @@
         <v>370</v>
       </c>
       <c r="Y41" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="Z41" t="s">
         <v>444</v>
       </c>
       <c r="AA41">
-        <v>0.99774884372261763</v>
+        <v>0.99853303004525662</v>
       </c>
       <c r="AB41">
-        <v>84.621736519387298</v>
+        <v>18.693183403514499</v>
       </c>
       <c r="AD41" t="s">
         <v>307</v>
@@ -10471,7 +10471,7 @@
         <v>593</v>
       </c>
       <c r="AN41" t="s">
-        <v>453</v>
+        <v>417</v>
       </c>
       <c r="AO41">
         <v>0.99797028609854399</v>
@@ -10542,16 +10542,16 @@
         <v>372</v>
       </c>
       <c r="Y42" t="s">
-        <v>304</v>
+        <v>256</v>
       </c>
       <c r="Z42" t="s">
         <v>445</v>
       </c>
       <c r="AA42">
-        <v>0.99782029353787438</v>
+        <v>0.99754569173664964</v>
       </c>
       <c r="AB42">
-        <v>23.861203412894469</v>
+        <v>45.1502695224383</v>
       </c>
       <c r="AD42" t="s">
         <v>307</v>
@@ -10581,13 +10581,13 @@
         <v>594</v>
       </c>
       <c r="AN42" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="AO42">
-        <v>0.99871472031655018</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AP42">
-        <v>28.428965886446147</v>
+        <v>23.107973955380711</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10652,16 +10652,16 @@
         <v>374</v>
       </c>
       <c r="Y43" t="s">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c r="Z43" t="s">
         <v>446</v>
       </c>
       <c r="AA43">
-        <v>0.99813022065694434</v>
+        <v>0.99697644816659792</v>
       </c>
       <c r="AB43">
-        <v>40.332510468654611</v>
+        <v>58.519281729791345</v>
       </c>
       <c r="AD43" t="s">
         <v>307</v>
@@ -10691,13 +10691,13 @@
         <v>595</v>
       </c>
       <c r="AN43" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="AO43">
-        <v>0.99782029353787438</v>
+        <v>0.99845480529905328</v>
       </c>
       <c r="AP43">
-        <v>23.861203412894469</v>
+        <v>47.820994144128512</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10762,16 +10762,16 @@
         <v>376</v>
       </c>
       <c r="Y44" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="Z44" t="s">
         <v>447</v>
       </c>
       <c r="AA44">
-        <v>0.99818636444109388</v>
+        <v>0.99871805281197423</v>
       </c>
       <c r="AB44">
-        <v>45.221154662357485</v>
+        <v>25.256759506353582</v>
       </c>
       <c r="AD44" t="s">
         <v>307</v>
@@ -10801,13 +10801,13 @@
         <v>596</v>
       </c>
       <c r="AN44" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="AO44">
-        <v>0.99751816641322844</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AP44">
-        <v>45.1502695224383</v>
+        <v>12.019055461720432</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10872,16 +10872,16 @@
         <v>378</v>
       </c>
       <c r="Y45" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="Z45" t="s">
         <v>448</v>
       </c>
       <c r="AA45">
-        <v>0.99843994478948561</v>
+        <v>0.99637763901827192</v>
       </c>
       <c r="AB45">
-        <v>28.334088028040785</v>
+        <v>48.031259731727893</v>
       </c>
       <c r="AD45" t="s">
         <v>307</v>
@@ -10911,13 +10911,13 @@
         <v>597</v>
       </c>
       <c r="AN45" t="s">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="AO45">
-        <v>0.99754431624006568</v>
+        <v>0.99850473493624492</v>
       </c>
       <c r="AP45">
-        <v>32.256845956342154</v>
+        <v>27.496123184453968</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10982,16 +10982,16 @@
         <v>380</v>
       </c>
       <c r="Y46" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="Z46" t="s">
         <v>449</v>
       </c>
       <c r="AA46">
-        <v>0.9983322364125492</v>
+        <v>0.99873544632009026</v>
       </c>
       <c r="AB46">
-        <v>27.248239083262582</v>
+        <v>34.387878972174441</v>
       </c>
       <c r="AD46" t="s">
         <v>307</v>
@@ -11021,13 +11021,13 @@
         <v>598</v>
       </c>
       <c r="AN46" t="s">
-        <v>454</v>
+        <v>416</v>
       </c>
       <c r="AO46">
-        <v>0.99755521694544447</v>
+        <v>0.99871472031655018</v>
       </c>
       <c r="AP46">
-        <v>50.682816539915542</v>
+        <v>28.428965886446147</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -11092,16 +11092,16 @@
         <v>382</v>
       </c>
       <c r="Y47" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="Z47" t="s">
         <v>450</v>
       </c>
       <c r="AA47">
-        <v>0.99795611274367535</v>
+        <v>0.99755900053893942</v>
       </c>
       <c r="AB47">
-        <v>29.909469717927731</v>
+        <v>42.327567967950763</v>
       </c>
       <c r="AD47" t="s">
         <v>307</v>
@@ -11131,13 +11131,13 @@
         <v>599</v>
       </c>
       <c r="AN47" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AO47">
-        <v>0.99984169097848852</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AP47">
-        <v>2.9143415731308986</v>
+        <v>23.861203412894469</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -11202,16 +11202,16 @@
         <v>384</v>
       </c>
       <c r="Y48" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="Z48" t="s">
         <v>451</v>
       </c>
       <c r="AA48">
-        <v>0.99756835894174822</v>
+        <v>0.99776786767941794</v>
       </c>
       <c r="AB48">
-        <v>36.020821886415746</v>
+        <v>27.059822883365296</v>
       </c>
       <c r="AD48" t="s">
         <v>307</v>
@@ -11241,13 +11241,13 @@
         <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="AO48">
-        <v>0.99885698485202501</v>
+        <v>0.99790284855194045</v>
       </c>
       <c r="AP48">
-        <v>25.256759506353582</v>
+        <v>35.874797800938026</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -11312,16 +11312,16 @@
         <v>386</v>
       </c>
       <c r="Y49" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="Z49" t="s">
         <v>452</v>
       </c>
       <c r="AA49">
-        <v>0.99872758388674931</v>
+        <v>0.99789789449716026</v>
       </c>
       <c r="AB49">
-        <v>23.31941562731657</v>
+        <v>39.831307398714806</v>
       </c>
       <c r="AD49" t="s">
         <v>307</v>
@@ -11351,13 +11351,13 @@
         <v>601</v>
       </c>
       <c r="AN49" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AO49">
-        <v>0.99709581552680626</v>
+        <v>0.99856107979091546</v>
       </c>
       <c r="AP49">
-        <v>53.231766754458491</v>
+        <v>26.622770797002293</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -11422,16 +11422,16 @@
         <v>388</v>
       </c>
       <c r="Y50" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z50" t="s">
         <v>453</v>
       </c>
       <c r="AA50">
-        <v>0.99815889366481214</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AB50">
-        <v>34.892661212818595</v>
+        <v>45.737867404715672</v>
       </c>
       <c r="AD50" t="s">
         <v>307</v>
@@ -11461,13 +11461,13 @@
         <v>602</v>
       </c>
       <c r="AN50" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AO50">
-        <v>0.99863950725251116</v>
+        <v>0.99863161241655762</v>
       </c>
       <c r="AP50">
-        <v>34.387878972174441</v>
+        <v>48.306707937232645</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -11532,16 +11532,16 @@
         <v>390</v>
       </c>
       <c r="Y51" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="Z51" t="s">
         <v>454</v>
       </c>
       <c r="AA51">
-        <v>0.99762279320259084</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AB51">
-        <v>50.682816539915542</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AD51" t="s">
         <v>307</v>
@@ -11571,13 +11571,13 @@
         <v>603</v>
       </c>
       <c r="AN51" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AO51">
-        <v>0.99837520457423046</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AP51">
-        <v>29.909469717927731</v>
+        <v>24.883658184919245</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -11642,16 +11642,16 @@
         <v>392</v>
       </c>
       <c r="Y52" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="Z52" t="s">
         <v>455</v>
       </c>
       <c r="AA52">
-        <v>0.99782727135381688</v>
+        <v>0.99811506665856298</v>
       </c>
       <c r="AB52">
-        <v>30.875049982999808</v>
+        <v>35.874797800938026</v>
       </c>
       <c r="AD52" t="s">
         <v>307</v>
@@ -11681,7 +11681,7 @@
         <v>604</v>
       </c>
       <c r="AN52" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="AO52">
         <v>0.99632737337312927</v>
@@ -11752,16 +11752,16 @@
         <v>394</v>
       </c>
       <c r="Y53" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="Z53" t="s">
         <v>456</v>
       </c>
       <c r="AA53">
-        <v>0.99795655945864681</v>
+        <v>0.99852418793335518</v>
       </c>
       <c r="AB53">
-        <v>75.277133913292474</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AD53" t="s">
         <v>307</v>
@@ -11791,7 +11791,7 @@
         <v>605</v>
       </c>
       <c r="AN53" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="AO53">
         <v>0.99739127962445018</v>
@@ -11862,16 +11862,16 @@
         <v>396</v>
       </c>
       <c r="Y54" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="Z54" t="s">
         <v>457</v>
       </c>
       <c r="AA54">
-        <v>0.99874893763362849</v>
+        <v>0.99713671217394562</v>
       </c>
       <c r="AB54">
-        <v>27.496123184453968</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AD54" t="s">
         <v>307</v>
@@ -11901,7 +11901,7 @@
         <v>606</v>
       </c>
       <c r="AN54" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="AO54">
         <v>0.99818574894902312</v>
@@ -11972,16 +11972,16 @@
         <v>398</v>
       </c>
       <c r="Y55" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="Z55" t="s">
         <v>458</v>
       </c>
       <c r="AA55">
-        <v>0.99751567592854107</v>
+        <v>0.99774884372261763</v>
       </c>
       <c r="AB55">
-        <v>46.334800039670455</v>
+        <v>84.621736519387298</v>
       </c>
       <c r="AD55" t="s">
         <v>307</v>
@@ -12011,7 +12011,7 @@
         <v>607</v>
       </c>
       <c r="AN55" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="AO55">
         <v>0.99853353101054187</v>
@@ -12082,16 +12082,16 @@
         <v>400</v>
       </c>
       <c r="Y56" t="s">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="Z56" t="s">
         <v>459</v>
       </c>
       <c r="AA56">
-        <v>0.99834689519829145</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AB56">
-        <v>32.749623583141812</v>
+        <v>23.861203412894469</v>
       </c>
       <c r="AD56" t="s">
         <v>307</v>
@@ -12121,7 +12121,7 @@
         <v>608</v>
       </c>
       <c r="AN56" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="AO56">
         <v>0.99747843498043831</v>
@@ -12192,16 +12192,16 @@
         <v>402</v>
       </c>
       <c r="Y57" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="Z57" t="s">
         <v>460</v>
       </c>
       <c r="AA57">
-        <v>0.99853303004525662</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AB57">
-        <v>18.693183403514499</v>
+        <v>40.332510468654611</v>
       </c>
       <c r="AD57" t="s">
         <v>307</v>
@@ -12231,7 +12231,7 @@
         <v>609</v>
       </c>
       <c r="AN57" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="AO57">
         <v>0.99466341005350978</v>
@@ -12341,7 +12341,7 @@
         <v>610</v>
       </c>
       <c r="AN58" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AO58">
         <v>0.9977732948939011</v>
@@ -12451,7 +12451,7 @@
         <v>611</v>
       </c>
       <c r="AN59" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="AO59">
         <v>0.99872758388674931</v>
@@ -12614,7 +12614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F18D53C-086C-4BFA-B8F2-7D759E1D358F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89391065-8A20-4809-A3AC-CC937121CD20}">
   <dimension ref="B9:Z59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12726,7 +12726,7 @@
         <v>642</v>
       </c>
       <c r="K11" t="s">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="L11">
         <v>0.64021427611097514</v>
@@ -12759,7 +12759,7 @@
         <v>740</v>
       </c>
       <c r="X11" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Y11">
         <v>17.603249999999999</v>
@@ -12794,7 +12794,7 @@
         <v>644</v>
       </c>
       <c r="K12" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="L12">
         <v>3.683157674608327</v>
@@ -12827,7 +12827,7 @@
         <v>742</v>
       </c>
       <c r="X12" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="Y12">
         <v>11.58525</v>
@@ -12862,7 +12862,7 @@
         <v>646</v>
       </c>
       <c r="K13" t="s">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="L13">
         <v>1.1133782162108721</v>
@@ -12895,7 +12895,7 @@
         <v>744</v>
       </c>
       <c r="X13" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="Y13">
         <v>5.7000000000000002E-2</v>
@@ -12930,7 +12930,7 @@
         <v>648</v>
       </c>
       <c r="K14" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="L14">
         <v>2.5290705136145335</v>
@@ -12963,7 +12963,7 @@
         <v>746</v>
       </c>
       <c r="X14" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="Y14">
         <v>11.2965</v>
@@ -12998,7 +12998,7 @@
         <v>650</v>
       </c>
       <c r="K15" t="s">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="L15">
         <v>2.1620342624302693</v>
@@ -13031,7 +13031,7 @@
         <v>748</v>
       </c>
       <c r="X15" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="Y15">
         <v>0.83925000000000005</v>
@@ -13066,7 +13066,7 @@
         <v>652</v>
       </c>
       <c r="K16" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="L16">
         <v>0.10228431008717309</v>
@@ -13134,7 +13134,7 @@
         <v>654</v>
       </c>
       <c r="K17" t="s">
-        <v>579</v>
+        <v>602</v>
       </c>
       <c r="L17">
         <v>0.26374115795515951</v>
@@ -13167,7 +13167,7 @@
         <v>752</v>
       </c>
       <c r="X17" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="Y17">
         <v>5.8237500000000004</v>
@@ -13202,7 +13202,7 @@
         <v>656</v>
       </c>
       <c r="K18" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L18">
         <v>1.0775690479395925</v>
@@ -13235,7 +13235,7 @@
         <v>754</v>
       </c>
       <c r="X18" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="Y18">
         <v>16.887</v>
@@ -13303,7 +13303,7 @@
         <v>756</v>
       </c>
       <c r="X19" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="Y19">
         <v>17.089500000000001</v>
@@ -13338,7 +13338,7 @@
         <v>660</v>
       </c>
       <c r="K20" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="L20">
         <v>4.1793335626386838</v>
@@ -13371,7 +13371,7 @@
         <v>758</v>
       </c>
       <c r="X20" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="Y20">
         <v>5.4255000000000004</v>
@@ -13406,7 +13406,7 @@
         <v>662</v>
       </c>
       <c r="K21" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="L21">
         <v>0.10220883742433164</v>
@@ -13441,7 +13441,7 @@
         <v>664</v>
       </c>
       <c r="K22" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="L22">
         <v>3.2456117052218421</v>
@@ -13511,7 +13511,7 @@
         <v>668</v>
       </c>
       <c r="K24" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="L24">
         <v>0.18120178223038519</v>
@@ -13616,7 +13616,7 @@
         <v>674</v>
       </c>
       <c r="K27" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="L27">
         <v>4.0346953063254611</v>
@@ -13686,7 +13686,7 @@
         <v>678</v>
       </c>
       <c r="K29" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="L29">
         <v>0.19671799304243257</v>
@@ -13721,7 +13721,7 @@
         <v>680</v>
       </c>
       <c r="K30" t="s">
-        <v>564</v>
+        <v>601</v>
       </c>
       <c r="L30">
         <v>0.46906534608342149</v>
@@ -13756,7 +13756,7 @@
         <v>682</v>
       </c>
       <c r="K31" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="L31">
         <v>0.70432433684539619</v>
@@ -13791,7 +13791,7 @@
         <v>684</v>
       </c>
       <c r="K32" t="s">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="L32">
         <v>0.14326997649193718</v>
@@ -13826,7 +13826,7 @@
         <v>686</v>
       </c>
       <c r="K33" t="s">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="L33">
         <v>2.5135228824118248E-2</v>
@@ -13861,7 +13861,7 @@
         <v>688</v>
       </c>
       <c r="K34" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="L34">
         <v>0.60333316217563482</v>
@@ -13931,7 +13931,7 @@
         <v>692</v>
       </c>
       <c r="K36" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="L36">
         <v>5.5124889677616896E-2</v>
@@ -14036,7 +14036,7 @@
         <v>698</v>
       </c>
       <c r="K39" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L39">
         <v>2.9266524214395733</v>
@@ -14071,7 +14071,7 @@
         <v>700</v>
       </c>
       <c r="K40" t="s">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="L40">
         <v>0.46102512715199689</v>
@@ -14106,7 +14106,7 @@
         <v>702</v>
       </c>
       <c r="K41" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -14176,7 +14176,7 @@
         <v>706</v>
       </c>
       <c r="K43" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="L43">
         <v>0.80689812107944159</v>
@@ -14211,7 +14211,7 @@
         <v>708</v>
       </c>
       <c r="K44" t="s">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="L44">
         <v>0.1886799653533156</v>
@@ -14246,7 +14246,7 @@
         <v>710</v>
       </c>
       <c r="K45" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="L45">
         <v>2.577065692017253</v>
@@ -14281,7 +14281,7 @@
         <v>712</v>
       </c>
       <c r="K46" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L46">
         <v>0.32349873740765611</v>
@@ -14316,7 +14316,7 @@
         <v>714</v>
       </c>
       <c r="K47" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -14386,7 +14386,7 @@
         <v>718</v>
       </c>
       <c r="K49" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="L49">
         <v>1.4641560353950904</v>
@@ -14456,7 +14456,7 @@
         <v>722</v>
       </c>
       <c r="K51" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="L51">
         <v>2.3327457542865271</v>
@@ -14491,7 +14491,7 @@
         <v>724</v>
       </c>
       <c r="K52" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="L52">
         <v>0.64220735366408732</v>
@@ -14526,7 +14526,7 @@
         <v>726</v>
       </c>
       <c r="K53" t="s">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="L53">
         <v>0.20805219904440039</v>
@@ -14561,7 +14561,7 @@
         <v>728</v>
       </c>
       <c r="K54" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="L54">
         <v>1.3018026354345156</v>
@@ -14596,7 +14596,7 @@
         <v>730</v>
       </c>
       <c r="K55" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="L55">
         <v>3.0871018425456893</v>
@@ -14701,7 +14701,7 @@
         <v>736</v>
       </c>
       <c r="K58" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L58">
         <v>0.28717016660662842</v>
@@ -14736,7 +14736,7 @@
         <v>738</v>
       </c>
       <c r="K59" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L59">
         <v>0.93964202108728523</v>
@@ -14751,7 +14751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC1595FB-6545-4ACA-86F6-F4D97F7510B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70005A63-AA23-48BE-8AAC-94C83D7E3160}">
   <dimension ref="B9:Y159"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19812,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89708DF2-013E-4029-A1C6-D0847F91082E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0468FF53-33CB-42A6-9FE3-749851BF26C6}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACD74A6-C852-4DA5-BFA8-4B93D0619E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8B76BE-58A3-42E4-A6FE-92D680529156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -990,18 +990,204 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_025</t>
   </si>
   <si>
@@ -1014,84 +1200,6 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_036</t>
   </si>
   <si>
@@ -1110,52 +1218,10 @@
     <t>connecting solar to buses in cluster 48</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
+    <t>distr_solelc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_028</t>
@@ -1164,24 +1230,6 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_POL_002</t>
   </si>
   <si>
@@ -1194,52 +1242,28 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_003</t>
@@ -1278,36 +1302,105 @@
     <t>connecting solar to buses in cluster 51</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD22</t>
   </si>
   <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>e_Kalisz_POL</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Lukow_POL</t>
+  </si>
+  <si>
+    <t>e_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>e_Radom_POL</t>
+  </si>
+  <si>
+    <t>e_Lodz_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>e_Lublin_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>e_Pila_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
     <t>e_Skawina_POL</t>
   </si>
   <si>
@@ -1317,45 +1410,6 @@
     <t>e_Mielec_POL</t>
   </si>
   <si>
-    <t>e_Konin_POL</t>
-  </si>
-  <si>
-    <t>e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>e_Pila_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>e_Lukow_POL</t>
-  </si>
-  <si>
-    <t>e_Swidnica_POL</t>
-  </si>
-  <si>
-    <t>e_Radom_POL</t>
-  </si>
-  <si>
-    <t>e_Lodz_POL</t>
-  </si>
-  <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Grudziadz_POL</t>
-  </si>
-  <si>
     <t>e_Warsaw_POL</t>
   </si>
   <si>
@@ -1365,70 +1419,28 @@
     <t>e_Wloclawek_POL</t>
   </si>
   <si>
-    <t>e_Lubin_POL</t>
-  </si>
-  <si>
-    <t>e_OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>e_Opole_POL</t>
-  </si>
-  <si>
-    <t>e_Kalisz_POL</t>
-  </si>
-  <si>
-    <t>e_Poznan_POL</t>
-  </si>
-  <si>
-    <t>e_Wroclaw_POL</t>
-  </si>
-  <si>
-    <t>e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>e_Szczecin_POL</t>
+    <t>e_Elk_POL</t>
   </si>
   <si>
     <t>e_Rzeszow_POL</t>
   </si>
   <si>
-    <t>e_Elk_POL</t>
-  </si>
-  <si>
-    <t>e_Boleslawiec_POL</t>
-  </si>
-  <si>
-    <t>e_Czestochowa_POL</t>
-  </si>
-  <si>
     <t>e_Bialystok_POL</t>
   </si>
   <si>
     <t>e_Grajewo_POL</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL</t>
-  </si>
-  <si>
-    <t>e_Lublin_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL</t>
+    <t>e_Siedlce_POL</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>e_Belchatow_POL</t>
+  </si>
+  <si>
+    <t>e_Zabrze_POL</t>
   </si>
   <si>
     <t>e_GorzowWielkopolski_POL</t>
@@ -1449,16 +1461,268 @@
     <t>e_Pulawy_POL</t>
   </si>
   <si>
-    <t>e_Siedlce_POL</t>
-  </si>
-  <si>
-    <t>e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>e_Belchatow_POL</t>
-  </si>
-  <si>
-    <t>e_Zabrze_POL</t>
+    <t>distr_wonelc_won_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_030</t>
@@ -1467,12 +1731,6 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_012</t>
   </si>
   <si>
@@ -1491,276 +1749,147 @@
     <t>connecting wind onshore to buses in cluster 45</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_POL_042</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 42</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
+    <t>elc_won_POL_002</t>
+  </si>
+  <si>
+    <t>elc_won_POL_004</t>
+  </si>
+  <si>
+    <t>elc_won_POL_010</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>elc_won_POL_011</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
+  </si>
+  <si>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_049</t>
   </si>
   <si>
     <t>elc_won_POL_030</t>
   </si>
   <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
@@ -1770,136 +1899,19 @@
     <t>elc_won_POL_045</t>
   </si>
   <si>
-    <t>elc_won_POL_011</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>elc_won_POL_023</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
-  </si>
-  <si>
-    <t>elc_won_POL_002</t>
-  </si>
-  <si>
-    <t>elc_won_POL_004</t>
-  </si>
-  <si>
-    <t>elc_won_POL_010</t>
-  </si>
-  <si>
-    <t>elc_won_POL_037</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>elc_won_POL_049</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>elc_won_POL_032</t>
-  </si>
-  <si>
     <t>elc_won_POL_042</t>
   </si>
   <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
-  </si>
-  <si>
-    <t>elc_won_POL_026</t>
-  </si>
-  <si>
-    <t>elc_won_POL_048</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>elc_won_POL_034</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>elc_won_POL_025</t>
-  </si>
-  <si>
-    <t>elc_won_POL_027</t>
-  </si>
-  <si>
-    <t>elc_won_POL_028</t>
-  </si>
-  <si>
-    <t>elc_won_POL_038</t>
-  </si>
-  <si>
-    <t>elc_won_POL_040</t>
-  </si>
-  <si>
-    <t>elc_won_POL_046</t>
-  </si>
-  <si>
-    <t>elc_won_POL_047</t>
+    <t>distr_wofelc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_002</t>
@@ -1908,10 +1920,10 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
+    <t>distr_wofelc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_003</t>
@@ -1920,76 +1932,64 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_POL_008</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_001</t>
   </si>
   <si>
     <t>elc_wof_POL_002</t>
   </si>
   <si>
-    <t>elc_wof_POL_001</t>
+    <t>elc_wof_POL_005</t>
   </si>
   <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
     <t>elc_wof_POL_008</t>
   </si>
   <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
     <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -6534,7 +6534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E9CA94-CC50-4553-97C2-3590B0A62FA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871E5877-F2BA-4FF8-A813-A03A995EDC18}">
   <dimension ref="B9:BD61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6772,16 +6772,16 @@
         <v>308</v>
       </c>
       <c r="Y11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Z11" t="s">
         <v>414</v>
       </c>
       <c r="AA11">
-        <v>0.99751836673919181</v>
+        <v>0.99818636444109388</v>
       </c>
       <c r="AB11">
-        <v>50.515025114296037</v>
+        <v>45.221154662357485</v>
       </c>
       <c r="AD11" t="s">
         <v>307</v>
@@ -6811,13 +6811,13 @@
         <v>563</v>
       </c>
       <c r="AN11" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="AO11">
-        <v>0.99828876210676587</v>
+        <v>0.99751816641322844</v>
       </c>
       <c r="AP11">
-        <v>28.334088028040785</v>
+        <v>45.1502695224383</v>
       </c>
       <c r="AR11" t="s">
         <v>307</v>
@@ -6847,13 +6847,13 @@
         <v>632</v>
       </c>
       <c r="BB11" t="s">
-        <v>418</v>
+        <v>463</v>
       </c>
       <c r="BC11">
-        <v>0.99478860441526007</v>
+        <v>0.99378504174620896</v>
       </c>
       <c r="BD11">
-        <v>610.20976015093845</v>
+        <v>761.13276667340403</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6918,16 +6918,16 @@
         <v>312</v>
       </c>
       <c r="Y12" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="Z12" t="s">
         <v>415</v>
       </c>
       <c r="AA12">
-        <v>0.99774808836727491</v>
+        <v>0.99843994478948561</v>
       </c>
       <c r="AB12">
-        <v>41.186340097586395</v>
+        <v>28.334088028040785</v>
       </c>
       <c r="AD12" t="s">
         <v>307</v>
@@ -6957,13 +6957,13 @@
         <v>564</v>
       </c>
       <c r="AN12" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="AO12">
-        <v>0.99777778253795524</v>
+        <v>0.99754431624006568</v>
       </c>
       <c r="AP12">
-        <v>36.020821886415746</v>
+        <v>32.256845956342154</v>
       </c>
       <c r="AR12" t="s">
         <v>307</v>
@@ -6993,7 +6993,7 @@
         <v>633</v>
       </c>
       <c r="BB12" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="BC12">
         <v>0.99436455351944619</v>
@@ -7064,16 +7064,16 @@
         <v>314</v>
       </c>
       <c r="Y13" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Z13" t="s">
         <v>416</v>
       </c>
       <c r="AA13">
-        <v>0.99828790514523624</v>
+        <v>0.9983322364125492</v>
       </c>
       <c r="AB13">
-        <v>28.428965886446147</v>
+        <v>27.248239083262582</v>
       </c>
       <c r="AD13" t="s">
         <v>307</v>
@@ -7103,13 +7103,13 @@
         <v>565</v>
       </c>
       <c r="AN13" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="AO13">
-        <v>0.9967210177786987</v>
+        <v>0.99755521694544447</v>
       </c>
       <c r="AP13">
-        <v>34.34566125862937</v>
+        <v>50.682816539915542</v>
       </c>
       <c r="AR13" t="s">
         <v>307</v>
@@ -7139,13 +7139,13 @@
         <v>634</v>
       </c>
       <c r="BB13" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="BC13">
-        <v>0.99635015248973569</v>
+        <v>0.99478860441526007</v>
       </c>
       <c r="BD13">
-        <v>366.10125775280716</v>
+        <v>610.20976015093845</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7210,16 +7210,16 @@
         <v>316</v>
       </c>
       <c r="Y14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z14" t="s">
         <v>417</v>
       </c>
       <c r="AA14">
-        <v>0.99815889366481214</v>
+        <v>0.99795611274367535</v>
       </c>
       <c r="AB14">
-        <v>34.892661212818595</v>
+        <v>29.909469717927731</v>
       </c>
       <c r="AD14" t="s">
         <v>307</v>
@@ -7249,13 +7249,13 @@
         <v>566</v>
       </c>
       <c r="AN14" t="s">
-        <v>425</v>
+        <v>458</v>
       </c>
       <c r="AO14">
-        <v>0.99777922331243873</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AP14">
-        <v>61.086483632538339</v>
+        <v>2.9143415731308986</v>
       </c>
       <c r="AR14" t="s">
         <v>307</v>
@@ -7285,13 +7285,13 @@
         <v>635</v>
       </c>
       <c r="BB14" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="BC14">
-        <v>0.99503061728845632</v>
+        <v>0.99784666475123052</v>
       </c>
       <c r="BD14">
-        <v>669.38461499965297</v>
+        <v>434.14794560012712</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7356,16 +7356,16 @@
         <v>318</v>
       </c>
       <c r="Y15" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="Z15" t="s">
         <v>418</v>
       </c>
       <c r="AA15">
-        <v>0.99679205626668776</v>
+        <v>0.99756835894174822</v>
       </c>
       <c r="AB15">
-        <v>28.983218493781202</v>
+        <v>36.020821886415746</v>
       </c>
       <c r="AD15" t="s">
         <v>307</v>
@@ -7395,13 +7395,13 @@
         <v>567</v>
       </c>
       <c r="AN15" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="AO15">
-        <v>0.99777988747037838</v>
+        <v>0.9980121476893673</v>
       </c>
       <c r="AP15">
-        <v>36.605495131795273</v>
+        <v>30.863466083156009</v>
       </c>
       <c r="AR15" t="s">
         <v>307</v>
@@ -7431,13 +7431,13 @@
         <v>636</v>
       </c>
       <c r="BB15" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="BC15">
-        <v>0.99784666475123052</v>
+        <v>0.99635015248973569</v>
       </c>
       <c r="BD15">
-        <v>434.14794560012712</v>
+        <v>366.10125775280716</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7502,16 +7502,16 @@
         <v>320</v>
       </c>
       <c r="Y16" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="Z16" t="s">
         <v>419</v>
       </c>
       <c r="AA16">
-        <v>0.99713110094318969</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AB16">
-        <v>34.34566125862937</v>
+        <v>23.31941562731657</v>
       </c>
       <c r="AD16" t="s">
         <v>307</v>
@@ -7541,13 +7541,13 @@
         <v>568</v>
       </c>
       <c r="AN16" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AO16">
-        <v>0.9980121476893673</v>
+        <v>0.99811519908104196</v>
       </c>
       <c r="AP16">
-        <v>30.863466083156009</v>
+        <v>41.186340097586395</v>
       </c>
       <c r="AR16" t="s">
         <v>307</v>
@@ -7577,7 +7577,7 @@
         <v>637</v>
       </c>
       <c r="BB16" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="BC16">
         <v>0.99671396210736585</v>
@@ -7648,16 +7648,16 @@
         <v>322</v>
       </c>
       <c r="Y17" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="Z17" t="s">
         <v>420</v>
       </c>
       <c r="AA17">
-        <v>0.99749963479302273</v>
+        <v>0.99834689519829145</v>
       </c>
       <c r="AB17">
-        <v>49.14481327115881</v>
+        <v>32.749623583141812</v>
       </c>
       <c r="AD17" t="s">
         <v>307</v>
@@ -7687,13 +7687,13 @@
         <v>569</v>
       </c>
       <c r="AN17" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="AO17">
-        <v>0.99811519908104196</v>
+        <v>0.99837593922723478</v>
       </c>
       <c r="AP17">
-        <v>41.186340097586395</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AR17" t="s">
         <v>307</v>
@@ -7723,7 +7723,7 @@
         <v>638</v>
       </c>
       <c r="BB17" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="BC17">
         <v>0.99498581429447941</v>
@@ -7794,16 +7794,16 @@
         <v>324</v>
       </c>
       <c r="Y18" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="Z18" t="s">
         <v>421</v>
       </c>
       <c r="AA18">
-        <v>0.9985687661763365</v>
+        <v>0.99853303004525662</v>
       </c>
       <c r="AB18">
-        <v>50.93040927578344</v>
+        <v>18.693183403514499</v>
       </c>
       <c r="AD18" t="s">
         <v>307</v>
@@ -7833,13 +7833,13 @@
         <v>570</v>
       </c>
       <c r="AN18" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="AO18">
-        <v>0.99837593922723478</v>
+        <v>0.99757815671697558</v>
       </c>
       <c r="AP18">
-        <v>25.205687076233477</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AR18" t="s">
         <v>307</v>
@@ -7869,7 +7869,7 @@
         <v>639</v>
       </c>
       <c r="BB18" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="BC18">
         <v>0.99705787611047647</v>
@@ -7940,16 +7940,16 @@
         <v>326</v>
       </c>
       <c r="Y19" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Z19" t="s">
         <v>422</v>
       </c>
       <c r="AA19">
-        <v>0.99814724525850784</v>
+        <v>0.99871805281197423</v>
       </c>
       <c r="AB19">
-        <v>47.820994144128512</v>
+        <v>25.256759506353582</v>
       </c>
       <c r="AD19" t="s">
         <v>307</v>
@@ -7979,13 +7979,13 @@
         <v>571</v>
       </c>
       <c r="AN19" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AO19">
-        <v>0.99757815671697558</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AP19">
-        <v>51.990142494672078</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AR19" t="s">
         <v>307</v>
@@ -8015,13 +8015,13 @@
         <v>640</v>
       </c>
       <c r="BB19" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="BC19">
-        <v>0.99249606766869936</v>
+        <v>0.99503061728845632</v>
       </c>
       <c r="BD19">
-        <v>661.89204677750558</v>
+        <v>669.38461499965297</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8086,16 +8086,16 @@
         <v>328</v>
       </c>
       <c r="Y20" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="Z20" t="s">
         <v>423</v>
       </c>
       <c r="AA20">
-        <v>0.99848201234520018</v>
+        <v>0.99637763901827192</v>
       </c>
       <c r="AB20">
-        <v>72.463654284142635</v>
+        <v>48.031259731727893</v>
       </c>
       <c r="AD20" t="s">
         <v>307</v>
@@ -8125,13 +8125,13 @@
         <v>572</v>
       </c>
       <c r="AN20" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="AO20">
-        <v>0.99916488913437129</v>
+        <v>0.99729296780855581</v>
       </c>
       <c r="AP20">
-        <v>15.260625790927634</v>
+        <v>49.14481327115881</v>
       </c>
       <c r="AR20" t="s">
         <v>307</v>
@@ -8161,13 +8161,13 @@
         <v>641</v>
       </c>
       <c r="BB20" t="s">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="BC20">
-        <v>0.99378504174620896</v>
+        <v>0.99249606766869936</v>
       </c>
       <c r="BD20">
-        <v>761.13276667340403</v>
+        <v>661.89204677750558</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8232,16 +8232,16 @@
         <v>330</v>
       </c>
       <c r="Y21" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Z21" t="s">
         <v>424</v>
       </c>
       <c r="AA21">
-        <v>0.99886290297361824</v>
+        <v>0.99873544632009026</v>
       </c>
       <c r="AB21">
-        <v>26.622770797002293</v>
+        <v>34.387878972174441</v>
       </c>
       <c r="AD21" t="s">
         <v>307</v>
@@ -8271,13 +8271,13 @@
         <v>573</v>
       </c>
       <c r="AN21" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="AO21">
-        <v>0.99729296780855581</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AP21">
-        <v>49.14481327115881</v>
+        <v>12.729766626457181</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8342,16 +8342,16 @@
         <v>332</v>
       </c>
       <c r="Y22" t="s">
-        <v>296</v>
+        <v>259</v>
       </c>
       <c r="Z22" t="s">
         <v>425</v>
       </c>
       <c r="AA22">
-        <v>0.99779181951287421</v>
+        <v>0.99814724525850784</v>
       </c>
       <c r="AB22">
-        <v>61.086483632538339</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AD22" t="s">
         <v>307</v>
@@ -8381,13 +8381,13 @@
         <v>574</v>
       </c>
       <c r="AN22" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="AO22">
-        <v>0.99921633401208909</v>
+        <v>0.99871472031655018</v>
       </c>
       <c r="AP22">
-        <v>12.729766626457181</v>
+        <v>28.428965886446147</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>334</v>
       </c>
       <c r="Y23" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s">
         <v>426</v>
       </c>
       <c r="AA23">
-        <v>0.99762279320259084</v>
+        <v>0.99848201234520018</v>
       </c>
       <c r="AB23">
-        <v>50.682816539915542</v>
+        <v>72.463654284142635</v>
       </c>
       <c r="AD23" t="s">
         <v>307</v>
@@ -8491,13 +8491,13 @@
         <v>575</v>
       </c>
       <c r="AN23" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="AO23">
-        <v>0.99885698485202501</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AP23">
-        <v>25.256759506353582</v>
+        <v>23.861203412894469</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8562,16 +8562,16 @@
         <v>336</v>
       </c>
       <c r="Y24" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="Z24" t="s">
         <v>427</v>
       </c>
       <c r="AA24">
-        <v>0.99782727135381688</v>
+        <v>0.99886290297361824</v>
       </c>
       <c r="AB24">
-        <v>30.875049982999808</v>
+        <v>26.622770797002293</v>
       </c>
       <c r="AD24" t="s">
         <v>307</v>
@@ -8601,13 +8601,13 @@
         <v>576</v>
       </c>
       <c r="AN24" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AO24">
-        <v>0.99709581552680626</v>
+        <v>0.99777778253795524</v>
       </c>
       <c r="AP24">
-        <v>53.231766754458491</v>
+        <v>36.020821886415746</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>338</v>
       </c>
       <c r="Y25" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="Z25" t="s">
         <v>428</v>
       </c>
       <c r="AA25">
-        <v>0.99795655945864681</v>
+        <v>0.99779181951287421</v>
       </c>
       <c r="AB25">
-        <v>75.277133913292474</v>
+        <v>61.086483632538339</v>
       </c>
       <c r="AD25" t="s">
         <v>307</v>
@@ -8711,13 +8711,13 @@
         <v>577</v>
       </c>
       <c r="AN25" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="AO25">
-        <v>0.99863950725251116</v>
+        <v>0.99845480529905328</v>
       </c>
       <c r="AP25">
-        <v>34.387878972174441</v>
+        <v>47.820994144128512</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8782,16 +8782,16 @@
         <v>340</v>
       </c>
       <c r="Y26" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="Z26" t="s">
         <v>429</v>
       </c>
       <c r="AA26">
-        <v>0.99874893763362849</v>
+        <v>0.99815889366481214</v>
       </c>
       <c r="AB26">
-        <v>27.496123184453968</v>
+        <v>34.892661212818595</v>
       </c>
       <c r="AD26" t="s">
         <v>307</v>
@@ -8821,13 +8821,13 @@
         <v>578</v>
       </c>
       <c r="AN26" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AO26">
-        <v>0.99837520457423046</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AP26">
-        <v>29.909469717927731</v>
+        <v>12.019055461720432</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8892,16 +8892,16 @@
         <v>342</v>
       </c>
       <c r="Y27" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="Z27" t="s">
         <v>430</v>
       </c>
       <c r="AA27">
-        <v>0.9978643471647114</v>
+        <v>0.99762279320259084</v>
       </c>
       <c r="AB27">
-        <v>31.560996462068374</v>
+        <v>50.682816539915542</v>
       </c>
       <c r="AD27" t="s">
         <v>307</v>
@@ -8931,13 +8931,13 @@
         <v>579</v>
       </c>
       <c r="AN27" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="AO27">
-        <v>0.99751816641322844</v>
+        <v>0.99850473493624492</v>
       </c>
       <c r="AP27">
-        <v>45.1502695224383</v>
+        <v>27.496123184453968</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9002,16 +9002,16 @@
         <v>344</v>
       </c>
       <c r="Y28" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="Z28" t="s">
         <v>431</v>
       </c>
       <c r="AA28">
-        <v>0.99789011269484895</v>
+        <v>0.99782727135381688</v>
       </c>
       <c r="AB28">
-        <v>36.605495131795273</v>
+        <v>30.875049982999808</v>
       </c>
       <c r="AD28" t="s">
         <v>307</v>
@@ -9041,13 +9041,13 @@
         <v>580</v>
       </c>
       <c r="AN28" t="s">
-        <v>461</v>
+        <v>422</v>
       </c>
       <c r="AO28">
-        <v>0.99754431624006568</v>
+        <v>0.99885698485202501</v>
       </c>
       <c r="AP28">
-        <v>32.256845956342154</v>
+        <v>25.256759506353582</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9112,16 +9112,16 @@
         <v>346</v>
       </c>
       <c r="Y29" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="Z29" t="s">
         <v>432</v>
       </c>
       <c r="AA29">
-        <v>0.99783121031362565</v>
+        <v>0.99795655945864681</v>
       </c>
       <c r="AB29">
-        <v>51.165698000691506</v>
+        <v>75.277133913292474</v>
       </c>
       <c r="AD29" t="s">
         <v>307</v>
@@ -9151,13 +9151,13 @@
         <v>581</v>
       </c>
       <c r="AN29" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="AO29">
-        <v>0.99755521694544447</v>
+        <v>0.99709581552680626</v>
       </c>
       <c r="AP29">
-        <v>50.682816539915542</v>
+        <v>53.231766754458491</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9222,16 +9222,16 @@
         <v>348</v>
       </c>
       <c r="Y30" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="Z30" t="s">
         <v>433</v>
       </c>
       <c r="AA30">
-        <v>0.99818636444109388</v>
+        <v>0.99874893763362849</v>
       </c>
       <c r="AB30">
-        <v>45.221154662357485</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AD30" t="s">
         <v>307</v>
@@ -9261,13 +9261,13 @@
         <v>582</v>
       </c>
       <c r="AN30" t="s">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="AO30">
-        <v>0.99984169097848852</v>
+        <v>0.99863950725251116</v>
       </c>
       <c r="AP30">
-        <v>2.9143415731308986</v>
+        <v>34.387878972174441</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9332,16 +9332,16 @@
         <v>350</v>
       </c>
       <c r="Y31" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="Z31" t="s">
         <v>434</v>
       </c>
       <c r="AA31">
-        <v>0.99843994478948561</v>
+        <v>0.9976031883518911</v>
       </c>
       <c r="AB31">
-        <v>28.334088028040785</v>
+        <v>58.963512461864056</v>
       </c>
       <c r="AD31" t="s">
         <v>307</v>
@@ -9371,13 +9371,13 @@
         <v>583</v>
       </c>
       <c r="AN31" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="AO31">
-        <v>0.99839049347738307</v>
+        <v>0.99837520457423046</v>
       </c>
       <c r="AP31">
-        <v>75.277133913292474</v>
+        <v>29.909469717927731</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9442,16 +9442,16 @@
         <v>352</v>
       </c>
       <c r="Y32" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="Z32" t="s">
         <v>435</v>
       </c>
       <c r="AA32">
-        <v>0.9983322364125492</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AB32">
-        <v>27.248239083262582</v>
+        <v>23.107973955380711</v>
       </c>
       <c r="AD32" t="s">
         <v>307</v>
@@ -9481,13 +9481,13 @@
         <v>584</v>
       </c>
       <c r="AN32" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="AO32">
-        <v>0.99697913305259955</v>
+        <v>0.99863161241655762</v>
       </c>
       <c r="AP32">
-        <v>58.519281729791345</v>
+        <v>48.306707937232645</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9552,16 +9552,16 @@
         <v>354</v>
       </c>
       <c r="Y33" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="Z33" t="s">
         <v>436</v>
       </c>
       <c r="AA33">
-        <v>0.99795611274367535</v>
+        <v>0.99755900053893942</v>
       </c>
       <c r="AB33">
-        <v>29.909469717927731</v>
+        <v>42.327567967950763</v>
       </c>
       <c r="AD33" t="s">
         <v>307</v>
@@ -9591,13 +9591,13 @@
         <v>585</v>
       </c>
       <c r="AN33" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="AO33">
-        <v>0.99757778563357669</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AP33">
-        <v>45.221154662357485</v>
+        <v>24.883658184919245</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9662,16 +9662,16 @@
         <v>356</v>
       </c>
       <c r="Y34" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="Z34" t="s">
         <v>437</v>
       </c>
       <c r="AA34">
-        <v>0.99756835894174822</v>
+        <v>0.99776786767941794</v>
       </c>
       <c r="AB34">
-        <v>36.020821886415746</v>
+        <v>27.059822883365296</v>
       </c>
       <c r="AD34" t="s">
         <v>307</v>
@@ -9701,13 +9701,13 @@
         <v>586</v>
       </c>
       <c r="AN34" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="AO34">
-        <v>0.99896573022887158</v>
+        <v>0.9975765595050764</v>
       </c>
       <c r="AP34">
-        <v>18.936001260254645</v>
+        <v>31.560996462068374</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9772,16 +9772,16 @@
         <v>358</v>
       </c>
       <c r="Y35" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="Z35" t="s">
         <v>438</v>
       </c>
       <c r="AA35">
-        <v>0.99872758388674931</v>
+        <v>0.99789789449716026</v>
       </c>
       <c r="AB35">
-        <v>23.31941562731657</v>
+        <v>39.831307398714806</v>
       </c>
       <c r="AD35" t="s">
         <v>307</v>
@@ -9811,13 +9811,13 @@
         <v>587</v>
       </c>
       <c r="AN35" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="AO35">
-        <v>0.99813022065694434</v>
+        <v>0.99632737337312927</v>
       </c>
       <c r="AP35">
-        <v>40.332510468654611</v>
+        <v>48.031259731727893</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9882,16 +9882,16 @@
         <v>360</v>
       </c>
       <c r="Y36" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="Z36" t="s">
         <v>439</v>
       </c>
       <c r="AA36">
-        <v>0.9976031883518911</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AB36">
-        <v>58.963512461864056</v>
+        <v>45.737867404715672</v>
       </c>
       <c r="AD36" t="s">
         <v>307</v>
@@ -9921,13 +9921,13 @@
         <v>588</v>
       </c>
       <c r="AN36" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="AO36">
-        <v>0.9975765595050764</v>
+        <v>0.99739127962445018</v>
       </c>
       <c r="AP36">
-        <v>31.560996462068374</v>
+        <v>39.831307398714806</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9992,16 +9992,16 @@
         <v>362</v>
       </c>
       <c r="Y37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z37" t="s">
         <v>440</v>
       </c>
       <c r="AA37">
-        <v>0.99870289970840342</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AB37">
-        <v>23.107973955380711</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AD37" t="s">
         <v>307</v>
@@ -10031,13 +10031,13 @@
         <v>589</v>
       </c>
       <c r="AN37" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="AO37">
-        <v>0.99649252363612195</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AP37">
-        <v>28.983218493781202</v>
+        <v>33.253084498654445</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10102,16 +10102,16 @@
         <v>364</v>
       </c>
       <c r="Y38" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="Z38" t="s">
         <v>441</v>
       </c>
       <c r="AA38">
-        <v>0.99818574894902312</v>
+        <v>0.99679205626668776</v>
       </c>
       <c r="AB38">
-        <v>33.253084498654445</v>
+        <v>28.983218493781202</v>
       </c>
       <c r="AD38" t="s">
         <v>307</v>
@@ -10141,13 +10141,13 @@
         <v>590</v>
       </c>
       <c r="AN38" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AO38">
-        <v>0.99767811393002859</v>
+        <v>0.99853353101054187</v>
       </c>
       <c r="AP38">
-        <v>30.875049982999808</v>
+        <v>18.693183403514499</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10212,16 +10212,16 @@
         <v>366</v>
       </c>
       <c r="Y39" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="Z39" t="s">
         <v>442</v>
       </c>
       <c r="AA39">
-        <v>0.99751567592854107</v>
+        <v>0.99713110094318969</v>
       </c>
       <c r="AB39">
-        <v>46.334800039670455</v>
+        <v>34.34566125862937</v>
       </c>
       <c r="AD39" t="s">
         <v>307</v>
@@ -10251,13 +10251,13 @@
         <v>591</v>
       </c>
       <c r="AN39" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO39">
-        <v>0.99764304373832691</v>
+        <v>0.99747843498043831</v>
       </c>
       <c r="AP39">
-        <v>42.327567967950763</v>
+        <v>46.334800039670455</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10322,16 +10322,16 @@
         <v>368</v>
       </c>
       <c r="Y40" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="Z40" t="s">
         <v>443</v>
       </c>
       <c r="AA40">
-        <v>0.99834689519829145</v>
+        <v>0.99749963479302273</v>
       </c>
       <c r="AB40">
-        <v>32.749623583141812</v>
+        <v>49.14481327115881</v>
       </c>
       <c r="AD40" t="s">
         <v>307</v>
@@ -10361,13 +10361,13 @@
         <v>592</v>
       </c>
       <c r="AN40" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="AO40">
-        <v>0.99790384243262886</v>
+        <v>0.99466341005350978</v>
       </c>
       <c r="AP40">
-        <v>72.461220387375079</v>
+        <v>58.229467192272445</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10432,16 +10432,16 @@
         <v>370</v>
       </c>
       <c r="Y41" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="Z41" t="s">
         <v>444</v>
       </c>
       <c r="AA41">
-        <v>0.99853303004525662</v>
+        <v>0.9985687661763365</v>
       </c>
       <c r="AB41">
-        <v>18.693183403514499</v>
+        <v>50.93040927578344</v>
       </c>
       <c r="AD41" t="s">
         <v>307</v>
@@ -10471,13 +10471,13 @@
         <v>593</v>
       </c>
       <c r="AN41" t="s">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="AO41">
-        <v>0.99797028609854399</v>
+        <v>0.9977732948939011</v>
       </c>
       <c r="AP41">
-        <v>34.892661212818595</v>
+        <v>51.165698000691506</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10542,16 +10542,16 @@
         <v>372</v>
       </c>
       <c r="Y42" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="Z42" t="s">
         <v>445</v>
       </c>
       <c r="AA42">
-        <v>0.99754569173664964</v>
+        <v>0.99751836673919181</v>
       </c>
       <c r="AB42">
-        <v>45.1502695224383</v>
+        <v>50.515025114296037</v>
       </c>
       <c r="AD42" t="s">
         <v>307</v>
@@ -10581,13 +10581,13 @@
         <v>594</v>
       </c>
       <c r="AN42" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="AO42">
-        <v>0.99870289970840342</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AP42">
-        <v>23.107973955380711</v>
+        <v>23.31941562731657</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10652,16 +10652,16 @@
         <v>374</v>
       </c>
       <c r="Y43" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="Z43" t="s">
         <v>446</v>
       </c>
       <c r="AA43">
-        <v>0.99697644816659792</v>
+        <v>0.99774808836727491</v>
       </c>
       <c r="AB43">
-        <v>58.519281729791345</v>
+        <v>41.186340097586395</v>
       </c>
       <c r="AD43" t="s">
         <v>307</v>
@@ -10691,13 +10691,13 @@
         <v>595</v>
       </c>
       <c r="AN43" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
       <c r="AO43">
-        <v>0.99845480529905328</v>
+        <v>0.99790284855194045</v>
       </c>
       <c r="AP43">
-        <v>47.820994144128512</v>
+        <v>35.874797800938026</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10762,16 +10762,16 @@
         <v>376</v>
       </c>
       <c r="Y44" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="Z44" t="s">
         <v>447</v>
       </c>
       <c r="AA44">
-        <v>0.99871805281197423</v>
+        <v>0.99828790514523624</v>
       </c>
       <c r="AB44">
-        <v>25.256759506353582</v>
+        <v>28.428965886446147</v>
       </c>
       <c r="AD44" t="s">
         <v>307</v>
@@ -10801,13 +10801,13 @@
         <v>596</v>
       </c>
       <c r="AN44" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="AO44">
-        <v>0.9991052659747558</v>
+        <v>0.99856107979091546</v>
       </c>
       <c r="AP44">
-        <v>12.019055461720432</v>
+        <v>26.622770797002293</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10872,16 +10872,16 @@
         <v>378</v>
       </c>
       <c r="Y45" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="Z45" t="s">
         <v>448</v>
       </c>
       <c r="AA45">
-        <v>0.99637763901827192</v>
+        <v>0.9978643471647114</v>
       </c>
       <c r="AB45">
-        <v>48.031259731727893</v>
+        <v>31.560996462068374</v>
       </c>
       <c r="AD45" t="s">
         <v>307</v>
@@ -10911,13 +10911,13 @@
         <v>597</v>
       </c>
       <c r="AN45" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="AO45">
-        <v>0.99850473493624492</v>
+        <v>0.99649252363612195</v>
       </c>
       <c r="AP45">
-        <v>27.496123184453968</v>
+        <v>28.983218493781202</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10982,16 +10982,16 @@
         <v>380</v>
       </c>
       <c r="Y46" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="Z46" t="s">
         <v>449</v>
       </c>
       <c r="AA46">
-        <v>0.99873544632009026</v>
+        <v>0.99789011269484895</v>
       </c>
       <c r="AB46">
-        <v>34.387878972174441</v>
+        <v>36.605495131795273</v>
       </c>
       <c r="AD46" t="s">
         <v>307</v>
@@ -11021,13 +11021,13 @@
         <v>598</v>
       </c>
       <c r="AN46" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="AO46">
-        <v>0.99871472031655018</v>
+        <v>0.99767811393002859</v>
       </c>
       <c r="AP46">
-        <v>28.428965886446147</v>
+        <v>30.875049982999808</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -11092,16 +11092,16 @@
         <v>382</v>
       </c>
       <c r="Y47" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="Z47" t="s">
         <v>450</v>
       </c>
       <c r="AA47">
-        <v>0.99755900053893942</v>
+        <v>0.99783121031362565</v>
       </c>
       <c r="AB47">
-        <v>42.327567967950763</v>
+        <v>51.165698000691506</v>
       </c>
       <c r="AD47" t="s">
         <v>307</v>
@@ -11131,13 +11131,13 @@
         <v>599</v>
       </c>
       <c r="AN47" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="AO47">
-        <v>0.99782029353787438</v>
+        <v>0.99764304373832691</v>
       </c>
       <c r="AP47">
-        <v>23.861203412894469</v>
+        <v>42.327567967950763</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -11202,16 +11202,16 @@
         <v>384</v>
       </c>
       <c r="Y48" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="Z48" t="s">
         <v>451</v>
       </c>
       <c r="AA48">
-        <v>0.99776786767941794</v>
+        <v>0.99751567592854107</v>
       </c>
       <c r="AB48">
-        <v>27.059822883365296</v>
+        <v>46.334800039670455</v>
       </c>
       <c r="AD48" t="s">
         <v>307</v>
@@ -11241,13 +11241,13 @@
         <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AO48">
-        <v>0.99790284855194045</v>
+        <v>0.99790384243262886</v>
       </c>
       <c r="AP48">
-        <v>35.874797800938026</v>
+        <v>72.461220387375079</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -11312,16 +11312,16 @@
         <v>386</v>
       </c>
       <c r="Y49" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Z49" t="s">
         <v>452</v>
       </c>
       <c r="AA49">
-        <v>0.99789789449716026</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AB49">
-        <v>39.831307398714806</v>
+        <v>33.253084498654445</v>
       </c>
       <c r="AD49" t="s">
         <v>307</v>
@@ -11351,13 +11351,13 @@
         <v>601</v>
       </c>
       <c r="AN49" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="AO49">
-        <v>0.99856107979091546</v>
+        <v>0.99797028609854399</v>
       </c>
       <c r="AP49">
-        <v>26.622770797002293</v>
+        <v>34.892661212818595</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -11422,16 +11422,16 @@
         <v>388</v>
       </c>
       <c r="Y50" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="Z50" t="s">
         <v>453</v>
       </c>
       <c r="AA50">
-        <v>0.99864365615724771</v>
+        <v>0.99754569173664964</v>
       </c>
       <c r="AB50">
-        <v>45.737867404715672</v>
+        <v>45.1502695224383</v>
       </c>
       <c r="AD50" t="s">
         <v>307</v>
@@ -11461,13 +11461,13 @@
         <v>602</v>
       </c>
       <c r="AN50" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="AO50">
-        <v>0.99863161241655762</v>
+        <v>0.99839049347738307</v>
       </c>
       <c r="AP50">
-        <v>48.306707937232645</v>
+        <v>75.277133913292474</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -11532,16 +11532,16 @@
         <v>390</v>
       </c>
       <c r="Y51" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="Z51" t="s">
         <v>454</v>
       </c>
       <c r="AA51">
-        <v>0.9991052659747558</v>
+        <v>0.99697644816659792</v>
       </c>
       <c r="AB51">
-        <v>12.019055461720432</v>
+        <v>58.519281729791345</v>
       </c>
       <c r="AD51" t="s">
         <v>307</v>
@@ -11571,13 +11571,13 @@
         <v>603</v>
       </c>
       <c r="AN51" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO51">
-        <v>0.99864365615724771</v>
+        <v>0.99697913305259955</v>
       </c>
       <c r="AP51">
-        <v>24.883658184919245</v>
+        <v>58.519281729791345</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -11642,16 +11642,16 @@
         <v>392</v>
       </c>
       <c r="Y52" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z52" t="s">
         <v>455</v>
       </c>
       <c r="AA52">
-        <v>0.99811506665856298</v>
+        <v>0.99761913939972058</v>
       </c>
       <c r="AB52">
-        <v>35.874797800938026</v>
+        <v>32.256845956342154</v>
       </c>
       <c r="AD52" t="s">
         <v>307</v>
@@ -11681,13 +11681,13 @@
         <v>604</v>
       </c>
       <c r="AN52" t="s">
-        <v>448</v>
+        <v>414</v>
       </c>
       <c r="AO52">
-        <v>0.99632737337312927</v>
+        <v>0.99757778563357669</v>
       </c>
       <c r="AP52">
-        <v>48.031259731727893</v>
+        <v>45.221154662357485</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -11752,16 +11752,16 @@
         <v>394</v>
       </c>
       <c r="Y53" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="Z53" t="s">
         <v>456</v>
       </c>
       <c r="AA53">
-        <v>0.99852418793335518</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AB53">
-        <v>25.205687076233477</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AD53" t="s">
         <v>307</v>
@@ -11791,13 +11791,13 @@
         <v>605</v>
       </c>
       <c r="AN53" t="s">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="AO53">
-        <v>0.99739127962445018</v>
+        <v>0.99896573022887158</v>
       </c>
       <c r="AP53">
-        <v>39.831307398714806</v>
+        <v>18.936001260254645</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -11862,16 +11862,16 @@
         <v>396</v>
       </c>
       <c r="Y54" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="Z54" t="s">
         <v>457</v>
       </c>
       <c r="AA54">
-        <v>0.99713671217394562</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AB54">
-        <v>51.990142494672078</v>
+        <v>12.729766626457181</v>
       </c>
       <c r="AD54" t="s">
         <v>307</v>
@@ -11901,13 +11901,13 @@
         <v>606</v>
       </c>
       <c r="AN54" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="AO54">
-        <v>0.99818574894902312</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AP54">
-        <v>33.253084498654445</v>
+        <v>40.332510468654611</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -11972,16 +11972,16 @@
         <v>398</v>
       </c>
       <c r="Y55" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="Z55" t="s">
         <v>458</v>
       </c>
       <c r="AA55">
-        <v>0.99774884372261763</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AB55">
-        <v>84.621736519387298</v>
+        <v>2.9143415731308986</v>
       </c>
       <c r="AD55" t="s">
         <v>307</v>
@@ -12011,13 +12011,13 @@
         <v>607</v>
       </c>
       <c r="AN55" t="s">
-        <v>444</v>
+        <v>415</v>
       </c>
       <c r="AO55">
-        <v>0.99853353101054187</v>
+        <v>0.99828876210676587</v>
       </c>
       <c r="AP55">
-        <v>18.693183403514499</v>
+        <v>28.334088028040785</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -12082,16 +12082,16 @@
         <v>400</v>
       </c>
       <c r="Y56" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="Z56" t="s">
         <v>459</v>
       </c>
       <c r="AA56">
-        <v>0.99782029353787438</v>
+        <v>0.99811506665856298</v>
       </c>
       <c r="AB56">
-        <v>23.861203412894469</v>
+        <v>35.874797800938026</v>
       </c>
       <c r="AD56" t="s">
         <v>307</v>
@@ -12124,10 +12124,10 @@
         <v>442</v>
       </c>
       <c r="AO56">
-        <v>0.99747843498043831</v>
+        <v>0.9967210177786987</v>
       </c>
       <c r="AP56">
-        <v>46.334800039670455</v>
+        <v>34.34566125862937</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -12192,16 +12192,16 @@
         <v>402</v>
       </c>
       <c r="Y57" t="s">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="Z57" t="s">
         <v>460</v>
       </c>
       <c r="AA57">
-        <v>0.99813022065694434</v>
+        <v>0.99852418793335518</v>
       </c>
       <c r="AB57">
-        <v>40.332510468654611</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AD57" t="s">
         <v>307</v>
@@ -12231,13 +12231,13 @@
         <v>609</v>
       </c>
       <c r="AN57" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="AO57">
-        <v>0.99466341005350978</v>
+        <v>0.99777922331243873</v>
       </c>
       <c r="AP57">
-        <v>58.229467192272445</v>
+        <v>61.086483632538339</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -12302,16 +12302,16 @@
         <v>404</v>
       </c>
       <c r="Y58" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Z58" t="s">
         <v>461</v>
       </c>
       <c r="AA58">
-        <v>0.99761913939972058</v>
+        <v>0.99713671217394562</v>
       </c>
       <c r="AB58">
-        <v>32.256845956342154</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AD58" t="s">
         <v>307</v>
@@ -12341,13 +12341,13 @@
         <v>610</v>
       </c>
       <c r="AN58" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="AO58">
-        <v>0.9977732948939011</v>
+        <v>0.99777988747037838</v>
       </c>
       <c r="AP58">
-        <v>51.165698000691506</v>
+        <v>36.605495131795273</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -12412,16 +12412,16 @@
         <v>406</v>
       </c>
       <c r="Y59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z59" t="s">
         <v>462</v>
       </c>
       <c r="AA59">
-        <v>0.99916488913437129</v>
+        <v>0.99774884372261763</v>
       </c>
       <c r="AB59">
-        <v>15.260625790927634</v>
+        <v>84.621736519387298</v>
       </c>
       <c r="AD59" t="s">
         <v>307</v>
@@ -12451,13 +12451,13 @@
         <v>611</v>
       </c>
       <c r="AN59" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AO59">
-        <v>0.99872758388674931</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AP59">
-        <v>23.31941562731657</v>
+        <v>23.107973955380711</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -12522,16 +12522,16 @@
         <v>408</v>
       </c>
       <c r="Y60" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="Z60" t="s">
         <v>463</v>
       </c>
       <c r="AA60">
-        <v>0.99921633401208909</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AB60">
-        <v>12.729766626457181</v>
+        <v>23.861203412894469</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -12596,16 +12596,16 @@
         <v>410</v>
       </c>
       <c r="Y61" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="Z61" t="s">
         <v>464</v>
       </c>
       <c r="AA61">
-        <v>0.99984169097848852</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AB61">
-        <v>2.9143415731308986</v>
+        <v>40.332510468654611</v>
       </c>
     </row>
   </sheetData>
@@ -12614,7 +12614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89391065-8A20-4809-A3AC-CC937121CD20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C17EE5F-34F1-4EA4-9744-5858F7FC092D}">
   <dimension ref="B9:Z59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12726,7 +12726,7 @@
         <v>642</v>
       </c>
       <c r="K11" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="L11">
         <v>0.64021427611097514</v>
@@ -12794,7 +12794,7 @@
         <v>644</v>
       </c>
       <c r="K12" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="L12">
         <v>3.683157674608327</v>
@@ -12827,7 +12827,7 @@
         <v>742</v>
       </c>
       <c r="X12" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="Y12">
         <v>11.58525</v>
@@ -12862,7 +12862,7 @@
         <v>646</v>
       </c>
       <c r="K13" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="L13">
         <v>1.1133782162108721</v>
@@ -12895,7 +12895,7 @@
         <v>744</v>
       </c>
       <c r="X13" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="Y13">
         <v>5.7000000000000002E-2</v>
@@ -12930,7 +12930,7 @@
         <v>648</v>
       </c>
       <c r="K14" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="L14">
         <v>2.5290705136145335</v>
@@ -12998,7 +12998,7 @@
         <v>650</v>
       </c>
       <c r="K15" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="L15">
         <v>2.1620342624302693</v>
@@ -13031,7 +13031,7 @@
         <v>748</v>
       </c>
       <c r="X15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="Y15">
         <v>0.83925000000000005</v>
@@ -13066,7 +13066,7 @@
         <v>652</v>
       </c>
       <c r="K16" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="L16">
         <v>0.10228431008717309</v>
@@ -13099,7 +13099,7 @@
         <v>750</v>
       </c>
       <c r="X16" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Y16">
         <v>2.0332499999999998</v>
@@ -13134,7 +13134,7 @@
         <v>654</v>
       </c>
       <c r="K17" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="L17">
         <v>0.26374115795515951</v>
@@ -13202,7 +13202,7 @@
         <v>656</v>
       </c>
       <c r="K18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="L18">
         <v>1.0775690479395925</v>
@@ -13235,7 +13235,7 @@
         <v>754</v>
       </c>
       <c r="X18" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="Y18">
         <v>16.887</v>
@@ -13270,7 +13270,7 @@
         <v>658</v>
       </c>
       <c r="K19" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="L19">
         <v>1.644864133979123</v>
@@ -13303,7 +13303,7 @@
         <v>756</v>
       </c>
       <c r="X19" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="Y19">
         <v>17.089500000000001</v>
@@ -13338,7 +13338,7 @@
         <v>660</v>
       </c>
       <c r="K20" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="L20">
         <v>4.1793335626386838</v>
@@ -13406,7 +13406,7 @@
         <v>662</v>
       </c>
       <c r="K21" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L21">
         <v>0.10220883742433164</v>
@@ -13441,7 +13441,7 @@
         <v>664</v>
       </c>
       <c r="K22" t="s">
-        <v>565</v>
+        <v>608</v>
       </c>
       <c r="L22">
         <v>3.2456117052218421</v>
@@ -13476,7 +13476,7 @@
         <v>666</v>
       </c>
       <c r="K23" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="L23">
         <v>3.822617103272679</v>
@@ -13511,7 +13511,7 @@
         <v>668</v>
       </c>
       <c r="K24" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="L24">
         <v>0.18120178223038519</v>
@@ -13546,7 +13546,7 @@
         <v>670</v>
       </c>
       <c r="K25" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="L25">
         <v>1.2636771265917695</v>
@@ -13581,7 +13581,7 @@
         <v>672</v>
       </c>
       <c r="K26" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="L26">
         <v>2.5500240416298969</v>
@@ -13616,7 +13616,7 @@
         <v>674</v>
       </c>
       <c r="K27" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="L27">
         <v>4.0346953063254611</v>
@@ -13651,7 +13651,7 @@
         <v>676</v>
       </c>
       <c r="K28" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="L28">
         <v>2.4674795572908166</v>
@@ -13686,7 +13686,7 @@
         <v>678</v>
       </c>
       <c r="K29" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L29">
         <v>0.19671799304243257</v>
@@ -13721,7 +13721,7 @@
         <v>680</v>
       </c>
       <c r="K30" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="L30">
         <v>0.46906534608342149</v>
@@ -13756,7 +13756,7 @@
         <v>682</v>
       </c>
       <c r="K31" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="L31">
         <v>0.70432433684539619</v>
@@ -13791,7 +13791,7 @@
         <v>684</v>
       </c>
       <c r="K32" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="L32">
         <v>0.14326997649193718</v>
@@ -13826,7 +13826,7 @@
         <v>686</v>
       </c>
       <c r="K33" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="L33">
         <v>2.5135228824118248E-2</v>
@@ -13861,7 +13861,7 @@
         <v>688</v>
       </c>
       <c r="K34" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L34">
         <v>0.60333316217563482</v>
@@ -13896,7 +13896,7 @@
         <v>690</v>
       </c>
       <c r="K35" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="L35">
         <v>0.61002023046213527</v>
@@ -13931,7 +13931,7 @@
         <v>692</v>
       </c>
       <c r="K36" t="s">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="L36">
         <v>5.5124889677616896E-2</v>
@@ -13966,7 +13966,7 @@
         <v>694</v>
       </c>
       <c r="K37" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="L37">
         <v>0.19696072330654418</v>
@@ -14001,7 +14001,7 @@
         <v>696</v>
       </c>
       <c r="K38" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="L38">
         <v>0.37453679972687481</v>
@@ -14036,7 +14036,7 @@
         <v>698</v>
       </c>
       <c r="K39" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L39">
         <v>2.9266524214395733</v>
@@ -14071,7 +14071,7 @@
         <v>700</v>
       </c>
       <c r="K40" t="s">
-        <v>563</v>
+        <v>607</v>
       </c>
       <c r="L40">
         <v>0.46102512715199689</v>
@@ -14106,7 +14106,7 @@
         <v>702</v>
       </c>
       <c r="K41" t="s">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -14141,7 +14141,7 @@
         <v>704</v>
       </c>
       <c r="K42" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="L42">
         <v>1.9780607647145438</v>
@@ -14176,7 +14176,7 @@
         <v>706</v>
       </c>
       <c r="K43" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="L43">
         <v>0.80689812107944159</v>
@@ -14211,7 +14211,7 @@
         <v>708</v>
       </c>
       <c r="K44" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="L44">
         <v>0.1886799653533156</v>
@@ -14246,7 +14246,7 @@
         <v>710</v>
       </c>
       <c r="K45" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="L45">
         <v>2.577065692017253</v>
@@ -14281,7 +14281,7 @@
         <v>712</v>
       </c>
       <c r="K46" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L46">
         <v>0.32349873740765611</v>
@@ -14316,7 +14316,7 @@
         <v>714</v>
       </c>
       <c r="K47" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -14351,7 +14351,7 @@
         <v>716</v>
       </c>
       <c r="K48" t="s">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="L48">
         <v>2.3210450729876548</v>
@@ -14386,7 +14386,7 @@
         <v>718</v>
       </c>
       <c r="K49" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="L49">
         <v>1.4641560353950904</v>
@@ -14421,7 +14421,7 @@
         <v>720</v>
       </c>
       <c r="K50" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="L50">
         <v>4.3172734082397007E-3</v>
@@ -14456,7 +14456,7 @@
         <v>722</v>
       </c>
       <c r="K51" t="s">
-        <v>566</v>
+        <v>609</v>
       </c>
       <c r="L51">
         <v>2.3327457542865271</v>
@@ -14491,7 +14491,7 @@
         <v>724</v>
       </c>
       <c r="K52" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="L52">
         <v>0.64220735366408732</v>
@@ -14526,7 +14526,7 @@
         <v>726</v>
       </c>
       <c r="K53" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="L53">
         <v>0.20805219904440039</v>
@@ -14561,7 +14561,7 @@
         <v>728</v>
       </c>
       <c r="K54" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="L54">
         <v>1.3018026354345156</v>
@@ -14596,7 +14596,7 @@
         <v>730</v>
       </c>
       <c r="K55" t="s">
-        <v>567</v>
+        <v>610</v>
       </c>
       <c r="L55">
         <v>3.0871018425456893</v>
@@ -14631,7 +14631,7 @@
         <v>732</v>
       </c>
       <c r="K56" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="L56">
         <v>3.1635610249840389</v>
@@ -14666,7 +14666,7 @@
         <v>734</v>
       </c>
       <c r="K57" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="L57">
         <v>9.3245940212150449E-2</v>
@@ -14701,7 +14701,7 @@
         <v>736</v>
       </c>
       <c r="K58" t="s">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="L58">
         <v>0.28717016660662842</v>
@@ -14736,7 +14736,7 @@
         <v>738</v>
       </c>
       <c r="K59" t="s">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="L59">
         <v>0.93964202108728523</v>
@@ -14751,7 +14751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70005A63-AA23-48BE-8AAC-94C83D7E3160}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67DCE07-CC5C-45E3-B0D1-E9E85C783236}">
   <dimension ref="B9:Y159"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19812,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0468FF53-33CB-42A6-9FE3-749851BF26C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E92D2EE-D333-4ED5-A269-9D9F119618C0}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8B76BE-58A3-42E4-A6FE-92D680529156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8D8698-5D48-40CC-8B75-0C3FF9D2ADE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1032,6 +1032,144 @@
     <t>connecting solar to buses in cluster 49</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_011</t>
   </si>
   <si>
@@ -1044,22 +1182,70 @@
     <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
+    <t>distr_solelc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
   </si>
   <si>
     <t>distr_solelc_spv_POL_005</t>
@@ -1086,222 +1272,36 @@
     <t>connecting solar to buses in cluster 42</t>
   </si>
   <si>
+    <t>distr_solelc_spv_POL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_POL_033</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_solelc_spv_POL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_POL_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1326,19 +1326,112 @@
     <t>e_Wroclaw_POL</t>
   </si>
   <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>e_Pila_POL</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>e_Skawina_POL</t>
+  </si>
+  <si>
+    <t>e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>e_Mielec_POL</t>
+  </si>
+  <si>
     <t>e_Boleslawiec_POL</t>
   </si>
   <si>
     <t>e_Czestochowa_POL</t>
   </si>
   <si>
-    <t>e_Bydgoszcz_POL</t>
-  </si>
-  <si>
-    <t>e_Police_POL</t>
-  </si>
-  <si>
-    <t>e_Tarnow_POL</t>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>e_Lublin_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Walbrzych_POL</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
   </si>
   <si>
     <t>e_Lukow_POL</t>
@@ -1353,112 +1446,187 @@
     <t>e_Lodz_POL</t>
   </si>
   <si>
+    <t>e_Siedlce_POL</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>e_Belchatow_POL</t>
+  </si>
+  <si>
+    <t>e_Zabrze_POL</t>
+  </si>
+  <si>
     <t>e_Konin_POL</t>
   </si>
   <si>
-    <t>e_Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>e_Lomza_POL</t>
-  </si>
-  <si>
-    <t>e_ZielonaGora_POL</t>
-  </si>
-  <si>
-    <t>e_Grudziadz_POL</t>
-  </si>
-  <si>
-    <t>e_KedzierzynKozle_POL</t>
-  </si>
-  <si>
-    <t>e_Szczecin_POL</t>
-  </si>
-  <si>
-    <t>e_Lublin_POL</t>
-  </si>
-  <si>
-    <t>e_Sosnowiec_POL</t>
-  </si>
-  <si>
-    <t>e_Kielce_POL</t>
-  </si>
-  <si>
-    <t>e_Walbrzych_POL</t>
-  </si>
-  <si>
-    <t>e_Katowice_POL</t>
-  </si>
-  <si>
-    <t>e_Slupsk_POL</t>
-  </si>
-  <si>
-    <t>e_Gdansk_POL</t>
-  </si>
-  <si>
-    <t>e_Pila_POL</t>
-  </si>
-  <si>
-    <t>e_BielskoBiala_POL</t>
-  </si>
-  <si>
-    <t>e_Skawina_POL</t>
-  </si>
-  <si>
-    <t>e_Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_Mielec_POL</t>
-  </si>
-  <si>
-    <t>e_Warsaw_POL</t>
-  </si>
-  <si>
-    <t>e_Plock_POL</t>
-  </si>
-  <si>
-    <t>e_Wloclawek_POL</t>
-  </si>
-  <si>
-    <t>e_Elk_POL</t>
-  </si>
-  <si>
-    <t>e_Rzeszow_POL</t>
-  </si>
-  <si>
-    <t>e_Bialystok_POL</t>
-  </si>
-  <si>
-    <t>e_Grajewo_POL</t>
-  </si>
-  <si>
-    <t>e_Siedlce_POL</t>
-  </si>
-  <si>
-    <t>e_Radomsko_POL</t>
-  </si>
-  <si>
-    <t>e_Belchatow_POL</t>
-  </si>
-  <si>
-    <t>e_Zabrze_POL</t>
-  </si>
-  <si>
-    <t>e_GorzowWielkopolski_POL</t>
-  </si>
-  <si>
-    <t>e_Legnica_POL</t>
-  </si>
-  <si>
-    <t>e_Krosno_POL</t>
-  </si>
-  <si>
-    <t>e_Zamosc_POL</t>
-  </si>
-  <si>
-    <t>e_Gdynia_POL</t>
-  </si>
-  <si>
-    <t>e_Pulawy_POL</t>
+    <t>distr_wonelc_won_POL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_002</t>
@@ -1497,34 +1665,82 @@
     <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
+    <t>distr_wonelc_won_POL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_POL_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
   </si>
   <si>
     <t>distr_wonelc_won_POL_026</t>
@@ -1539,220 +1755,88 @@
     <t>connecting wind onshore to buses in cluster 48</t>
   </si>
   <si>
-    <t>distr_wonelc_won_POL_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_POL_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
+    <t>elc_won_POL_003</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_005</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_001</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_014</t>
+  </si>
+  <si>
+    <t>elc_won_POL_017</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_049</t>
+  </si>
+  <si>
+    <t>elc_won_POL_012</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_006</t>
+  </si>
+  <si>
+    <t>elc_won_POL_008</t>
+  </si>
+  <si>
+    <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_007</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
   </si>
   <si>
     <t>elc_won_POL_002</t>
@@ -1773,19 +1857,43 @@
     <t>elc_won_POL_024</t>
   </si>
   <si>
-    <t>elc_won_POL_006</t>
-  </si>
-  <si>
-    <t>elc_won_POL_008</t>
-  </si>
-  <si>
-    <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
+    <t>elc_won_POL_015</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
+  </si>
+  <si>
+    <t>elc_won_POL_009</t>
+  </si>
+  <si>
+    <t>elc_won_POL_013</t>
+  </si>
+  <si>
+    <t>elc_won_POL_016</t>
+  </si>
+  <si>
+    <t>elc_won_POL_018</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
   </si>
   <si>
     <t>elc_won_POL_026</t>
@@ -1794,112 +1902,46 @@
     <t>elc_won_POL_048</t>
   </si>
   <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
-    <t>elc_won_POL_005</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
-  </si>
-  <si>
-    <t>elc_won_POL_001</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>elc_won_POL_023</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
-  </si>
-  <si>
-    <t>elc_won_POL_007</t>
-  </si>
-  <si>
-    <t>elc_won_POL_034</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>elc_won_POL_015</t>
-  </si>
-  <si>
-    <t>elc_won_POL_025</t>
-  </si>
-  <si>
-    <t>elc_won_POL_027</t>
-  </si>
-  <si>
-    <t>elc_won_POL_028</t>
-  </si>
-  <si>
-    <t>elc_won_POL_038</t>
-  </si>
-  <si>
-    <t>elc_won_POL_040</t>
-  </si>
-  <si>
-    <t>elc_won_POL_046</t>
-  </si>
-  <si>
-    <t>elc_won_POL_047</t>
-  </si>
-  <si>
-    <t>elc_won_POL_003</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>elc_won_POL_009</t>
-  </si>
-  <si>
-    <t>elc_won_POL_013</t>
-  </si>
-  <si>
-    <t>elc_won_POL_016</t>
-  </si>
-  <si>
-    <t>elc_won_POL_018</t>
-  </si>
-  <si>
-    <t>elc_won_POL_032</t>
-  </si>
-  <si>
-    <t>elc_won_POL_014</t>
-  </si>
-  <si>
-    <t>elc_won_POL_017</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>elc_won_POL_049</t>
-  </si>
-  <si>
-    <t>elc_won_POL_030</t>
-  </si>
-  <si>
-    <t>elc_won_POL_012</t>
-  </si>
-  <si>
-    <t>elc_won_POL_041</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>elc_won_POL_042</t>
+    <t>distr_wofelc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_POL_009</t>
@@ -1908,18 +1950,6 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_POL_005</t>
   </si>
   <si>
@@ -1932,64 +1962,34 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
+    <t>elc_wof_POL_001</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_002</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
   </si>
   <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
-    <t>elc_wof_POL_001</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_002</t>
-  </si>
-  <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
     <t>elc_wof_POL_003</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
   </si>
   <si>
     <t>e_won_POL_001</t>
@@ -6534,7 +6534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871E5877-F2BA-4FF8-A813-A03A995EDC18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364B1A6A-8A18-436E-ACEC-087107AD08A3}">
   <dimension ref="B9:BD61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6811,13 +6811,13 @@
         <v>563</v>
       </c>
       <c r="AN11" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="AO11">
-        <v>0.99751816641322844</v>
+        <v>0.99790284855194045</v>
       </c>
       <c r="AP11">
-        <v>45.1502695224383</v>
+        <v>35.874797800938026</v>
       </c>
       <c r="AR11" t="s">
         <v>307</v>
@@ -6847,13 +6847,13 @@
         <v>632</v>
       </c>
       <c r="BB11" t="s">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="BC11">
-        <v>0.99378504174620896</v>
+        <v>0.99436455351944619</v>
       </c>
       <c r="BD11">
-        <v>761.13276667340403</v>
+        <v>728.41730490967211</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6957,13 +6957,13 @@
         <v>564</v>
       </c>
       <c r="AN12" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AO12">
-        <v>0.99754431624006568</v>
+        <v>0.99856107979091546</v>
       </c>
       <c r="AP12">
-        <v>32.256845956342154</v>
+        <v>26.622770797002293</v>
       </c>
       <c r="AR12" t="s">
         <v>307</v>
@@ -6993,13 +6993,13 @@
         <v>633</v>
       </c>
       <c r="BB12" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BC12">
-        <v>0.99436455351944619</v>
+        <v>0.99503061728845632</v>
       </c>
       <c r="BD12">
-        <v>728.41730490967211</v>
+        <v>669.38461499965297</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7103,13 +7103,13 @@
         <v>565</v>
       </c>
       <c r="AN13" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="AO13">
-        <v>0.99755521694544447</v>
+        <v>0.9975765595050764</v>
       </c>
       <c r="AP13">
-        <v>50.682816539915542</v>
+        <v>31.560996462068374</v>
       </c>
       <c r="AR13" t="s">
         <v>307</v>
@@ -7139,13 +7139,13 @@
         <v>634</v>
       </c>
       <c r="BB13" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="BC13">
-        <v>0.99478860441526007</v>
+        <v>0.99671396210736585</v>
       </c>
       <c r="BD13">
-        <v>610.20976015093845</v>
+        <v>535.75153841730867</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7249,13 +7249,13 @@
         <v>566</v>
       </c>
       <c r="AN14" t="s">
-        <v>458</v>
+        <v>415</v>
       </c>
       <c r="AO14">
-        <v>0.99984169097848852</v>
+        <v>0.99828876210676587</v>
       </c>
       <c r="AP14">
-        <v>2.9143415731308986</v>
+        <v>28.334088028040785</v>
       </c>
       <c r="AR14" t="s">
         <v>307</v>
@@ -7285,13 +7285,13 @@
         <v>635</v>
       </c>
       <c r="BB14" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="BC14">
-        <v>0.99784666475123052</v>
+        <v>0.99498581429447941</v>
       </c>
       <c r="BD14">
-        <v>434.14794560012712</v>
+        <v>682.74537814765154</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7395,13 +7395,13 @@
         <v>567</v>
       </c>
       <c r="AN15" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="AO15">
-        <v>0.9980121476893673</v>
+        <v>0.99845480529905328</v>
       </c>
       <c r="AP15">
-        <v>30.863466083156009</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AR15" t="s">
         <v>307</v>
@@ -7431,13 +7431,13 @@
         <v>636</v>
       </c>
       <c r="BB15" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BC15">
-        <v>0.99635015248973569</v>
+        <v>0.99705787611047647</v>
       </c>
       <c r="BD15">
-        <v>366.10125775280716</v>
+        <v>516.05305554711185</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7541,13 +7541,13 @@
         <v>568</v>
       </c>
       <c r="AN16" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="AO16">
-        <v>0.99811519908104196</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AP16">
-        <v>41.186340097586395</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AR16" t="s">
         <v>307</v>
@@ -7577,13 +7577,13 @@
         <v>637</v>
       </c>
       <c r="BB16" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="BC16">
-        <v>0.99671396210736585</v>
+        <v>0.99478860441526007</v>
       </c>
       <c r="BD16">
-        <v>535.75153841730867</v>
+        <v>610.20976015093845</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7648,16 +7648,16 @@
         <v>322</v>
       </c>
       <c r="Y17" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="Z17" t="s">
         <v>420</v>
       </c>
       <c r="AA17">
-        <v>0.99834689519829145</v>
+        <v>0.9976031883518911</v>
       </c>
       <c r="AB17">
-        <v>32.749623583141812</v>
+        <v>58.963512461864056</v>
       </c>
       <c r="AD17" t="s">
         <v>307</v>
@@ -7687,13 +7687,13 @@
         <v>569</v>
       </c>
       <c r="AN17" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="AO17">
-        <v>0.99837593922723478</v>
+        <v>0.99850473493624492</v>
       </c>
       <c r="AP17">
-        <v>25.205687076233477</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AR17" t="s">
         <v>307</v>
@@ -7723,13 +7723,13 @@
         <v>638</v>
       </c>
       <c r="BB17" t="s">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="BC17">
-        <v>0.99498581429447941</v>
+        <v>0.99249606766869936</v>
       </c>
       <c r="BD17">
-        <v>682.74537814765154</v>
+        <v>661.89204677750558</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7794,16 +7794,16 @@
         <v>324</v>
       </c>
       <c r="Y18" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="Z18" t="s">
         <v>421</v>
       </c>
       <c r="AA18">
-        <v>0.99853303004525662</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AB18">
-        <v>18.693183403514499</v>
+        <v>23.107973955380711</v>
       </c>
       <c r="AD18" t="s">
         <v>307</v>
@@ -7833,13 +7833,13 @@
         <v>570</v>
       </c>
       <c r="AN18" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="AO18">
-        <v>0.99757815671697558</v>
+        <v>0.99885698485202501</v>
       </c>
       <c r="AP18">
-        <v>51.990142494672078</v>
+        <v>25.256759506353582</v>
       </c>
       <c r="AR18" t="s">
         <v>307</v>
@@ -7869,13 +7869,13 @@
         <v>639</v>
       </c>
       <c r="BB18" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="BC18">
-        <v>0.99705787611047647</v>
+        <v>0.99378504174620896</v>
       </c>
       <c r="BD18">
-        <v>516.05305554711185</v>
+        <v>761.13276667340403</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7940,16 +7940,16 @@
         <v>326</v>
       </c>
       <c r="Y19" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Z19" t="s">
         <v>422</v>
       </c>
       <c r="AA19">
-        <v>0.99871805281197423</v>
+        <v>0.99679205626668776</v>
       </c>
       <c r="AB19">
-        <v>25.256759506353582</v>
+        <v>28.983218493781202</v>
       </c>
       <c r="AD19" t="s">
         <v>307</v>
@@ -7979,13 +7979,13 @@
         <v>571</v>
       </c>
       <c r="AN19" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="AO19">
-        <v>0.99916488913437129</v>
+        <v>0.99709581552680626</v>
       </c>
       <c r="AP19">
-        <v>15.260625790927634</v>
+        <v>53.231766754458491</v>
       </c>
       <c r="AR19" t="s">
         <v>307</v>
@@ -8015,13 +8015,13 @@
         <v>640</v>
       </c>
       <c r="BB19" t="s">
-        <v>463</v>
+        <v>423</v>
       </c>
       <c r="BC19">
-        <v>0.99503061728845632</v>
+        <v>0.99784666475123052</v>
       </c>
       <c r="BD19">
-        <v>669.38461499965297</v>
+        <v>434.14794560012712</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8086,16 +8086,16 @@
         <v>328</v>
       </c>
       <c r="Y20" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Z20" t="s">
         <v>423</v>
       </c>
       <c r="AA20">
-        <v>0.99637763901827192</v>
+        <v>0.99713110094318969</v>
       </c>
       <c r="AB20">
-        <v>48.031259731727893</v>
+        <v>34.34566125862937</v>
       </c>
       <c r="AD20" t="s">
         <v>307</v>
@@ -8125,13 +8125,13 @@
         <v>572</v>
       </c>
       <c r="AN20" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="AO20">
-        <v>0.99729296780855581</v>
+        <v>0.99863950725251116</v>
       </c>
       <c r="AP20">
-        <v>49.14481327115881</v>
+        <v>34.387878972174441</v>
       </c>
       <c r="AR20" t="s">
         <v>307</v>
@@ -8161,13 +8161,13 @@
         <v>641</v>
       </c>
       <c r="BB20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="BC20">
-        <v>0.99249606766869936</v>
+        <v>0.99635015248973569</v>
       </c>
       <c r="BD20">
-        <v>661.89204677750558</v>
+        <v>366.10125775280716</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8232,16 +8232,16 @@
         <v>330</v>
       </c>
       <c r="Y21" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="Z21" t="s">
         <v>424</v>
       </c>
       <c r="AA21">
-        <v>0.99873544632009026</v>
+        <v>0.99749963479302273</v>
       </c>
       <c r="AB21">
-        <v>34.387878972174441</v>
+        <v>49.14481327115881</v>
       </c>
       <c r="AD21" t="s">
         <v>307</v>
@@ -8271,13 +8271,13 @@
         <v>573</v>
       </c>
       <c r="AN21" t="s">
-        <v>457</v>
+        <v>417</v>
       </c>
       <c r="AO21">
-        <v>0.99921633401208909</v>
+        <v>0.99837520457423046</v>
       </c>
       <c r="AP21">
-        <v>12.729766626457181</v>
+        <v>29.909469717927731</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8342,16 +8342,16 @@
         <v>332</v>
       </c>
       <c r="Y22" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="Z22" t="s">
         <v>425</v>
       </c>
       <c r="AA22">
-        <v>0.99814724525850784</v>
+        <v>0.9985687661763365</v>
       </c>
       <c r="AB22">
-        <v>47.820994144128512</v>
+        <v>50.93040927578344</v>
       </c>
       <c r="AD22" t="s">
         <v>307</v>
@@ -8381,13 +8381,13 @@
         <v>574</v>
       </c>
       <c r="AN22" t="s">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="AO22">
-        <v>0.99871472031655018</v>
+        <v>0.99777778253795524</v>
       </c>
       <c r="AP22">
-        <v>28.428965886446147</v>
+        <v>36.020821886415746</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>334</v>
       </c>
       <c r="Y23" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s">
         <v>426</v>
       </c>
       <c r="AA23">
-        <v>0.99848201234520018</v>
+        <v>0.99762279320259084</v>
       </c>
       <c r="AB23">
-        <v>72.463654284142635</v>
+        <v>50.682816539915542</v>
       </c>
       <c r="AD23" t="s">
         <v>307</v>
@@ -8491,13 +8491,13 @@
         <v>575</v>
       </c>
       <c r="AN23" t="s">
-        <v>463</v>
+        <v>428</v>
       </c>
       <c r="AO23">
-        <v>0.99782029353787438</v>
+        <v>0.99839049347738307</v>
       </c>
       <c r="AP23">
-        <v>23.861203412894469</v>
+        <v>75.277133913292474</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8562,16 +8562,16 @@
         <v>336</v>
       </c>
       <c r="Y24" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s">
         <v>427</v>
       </c>
       <c r="AA24">
-        <v>0.99886290297361824</v>
+        <v>0.99782727135381688</v>
       </c>
       <c r="AB24">
-        <v>26.622770797002293</v>
+        <v>30.875049982999808</v>
       </c>
       <c r="AD24" t="s">
         <v>307</v>
@@ -8601,13 +8601,13 @@
         <v>576</v>
       </c>
       <c r="AN24" t="s">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="AO24">
-        <v>0.99777778253795524</v>
+        <v>0.99697913305259955</v>
       </c>
       <c r="AP24">
-        <v>36.020821886415746</v>
+        <v>58.519281729791345</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>338</v>
       </c>
       <c r="Y25" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="Z25" t="s">
         <v>428</v>
       </c>
       <c r="AA25">
-        <v>0.99779181951287421</v>
+        <v>0.99795655945864681</v>
       </c>
       <c r="AB25">
-        <v>61.086483632538339</v>
+        <v>75.277133913292474</v>
       </c>
       <c r="AD25" t="s">
         <v>307</v>
@@ -8711,13 +8711,13 @@
         <v>577</v>
       </c>
       <c r="AN25" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="AO25">
-        <v>0.99845480529905328</v>
+        <v>0.99757778563357669</v>
       </c>
       <c r="AP25">
-        <v>47.820994144128512</v>
+        <v>45.221154662357485</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8782,16 +8782,16 @@
         <v>340</v>
       </c>
       <c r="Y26" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="Z26" t="s">
         <v>429</v>
       </c>
       <c r="AA26">
-        <v>0.99815889366481214</v>
+        <v>0.99874893763362849</v>
       </c>
       <c r="AB26">
-        <v>34.892661212818595</v>
+        <v>27.496123184453968</v>
       </c>
       <c r="AD26" t="s">
         <v>307</v>
@@ -8821,13 +8821,13 @@
         <v>578</v>
       </c>
       <c r="AN26" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="AO26">
-        <v>0.9991052659747558</v>
+        <v>0.99896573022887158</v>
       </c>
       <c r="AP26">
-        <v>12.019055461720432</v>
+        <v>18.936001260254645</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8892,16 +8892,16 @@
         <v>342</v>
       </c>
       <c r="Y27" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="Z27" t="s">
         <v>430</v>
       </c>
       <c r="AA27">
-        <v>0.99762279320259084</v>
+        <v>0.99871805281197423</v>
       </c>
       <c r="AB27">
-        <v>50.682816539915542</v>
+        <v>25.256759506353582</v>
       </c>
       <c r="AD27" t="s">
         <v>307</v>
@@ -8931,13 +8931,13 @@
         <v>579</v>
       </c>
       <c r="AN27" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="AO27">
-        <v>0.99850473493624492</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AP27">
-        <v>27.496123184453968</v>
+        <v>40.332510468654611</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9002,16 +9002,16 @@
         <v>344</v>
       </c>
       <c r="Y28" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Z28" t="s">
         <v>431</v>
       </c>
       <c r="AA28">
-        <v>0.99782727135381688</v>
+        <v>0.99637763901827192</v>
       </c>
       <c r="AB28">
-        <v>30.875049982999808</v>
+        <v>48.031259731727893</v>
       </c>
       <c r="AD28" t="s">
         <v>307</v>
@@ -9041,13 +9041,13 @@
         <v>580</v>
       </c>
       <c r="AN28" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO28">
-        <v>0.99885698485202501</v>
+        <v>0.9967210177786987</v>
       </c>
       <c r="AP28">
-        <v>25.256759506353582</v>
+        <v>34.34566125862937</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9112,16 +9112,16 @@
         <v>346</v>
       </c>
       <c r="Y29" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="Z29" t="s">
         <v>432</v>
       </c>
       <c r="AA29">
-        <v>0.99795655945864681</v>
+        <v>0.99873544632009026</v>
       </c>
       <c r="AB29">
-        <v>75.277133913292474</v>
+        <v>34.387878972174441</v>
       </c>
       <c r="AD29" t="s">
         <v>307</v>
@@ -9151,13 +9151,13 @@
         <v>581</v>
       </c>
       <c r="AN29" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="AO29">
-        <v>0.99709581552680626</v>
+        <v>0.99777922331243873</v>
       </c>
       <c r="AP29">
-        <v>53.231766754458491</v>
+        <v>61.086483632538339</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9222,16 +9222,16 @@
         <v>348</v>
       </c>
       <c r="Y30" t="s">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="Z30" t="s">
         <v>433</v>
       </c>
       <c r="AA30">
-        <v>0.99874893763362849</v>
+        <v>0.99811506665856298</v>
       </c>
       <c r="AB30">
-        <v>27.496123184453968</v>
+        <v>35.874797800938026</v>
       </c>
       <c r="AD30" t="s">
         <v>307</v>
@@ -9261,13 +9261,13 @@
         <v>582</v>
       </c>
       <c r="AN30" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="AO30">
-        <v>0.99863950725251116</v>
+        <v>0.99777988747037838</v>
       </c>
       <c r="AP30">
-        <v>34.387878972174441</v>
+        <v>36.605495131795273</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9332,16 +9332,16 @@
         <v>350</v>
       </c>
       <c r="Y31" t="s">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="Z31" t="s">
         <v>434</v>
       </c>
       <c r="AA31">
-        <v>0.9976031883518911</v>
+        <v>0.99852418793335518</v>
       </c>
       <c r="AB31">
-        <v>58.963512461864056</v>
+        <v>25.205687076233477</v>
       </c>
       <c r="AD31" t="s">
         <v>307</v>
@@ -9371,13 +9371,13 @@
         <v>583</v>
       </c>
       <c r="AN31" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="AO31">
-        <v>0.99837520457423046</v>
+        <v>0.99837593922723478</v>
       </c>
       <c r="AP31">
-        <v>29.909469717927731</v>
+        <v>25.205687076233477</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9442,16 +9442,16 @@
         <v>352</v>
       </c>
       <c r="Y32" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="Z32" t="s">
         <v>435</v>
       </c>
       <c r="AA32">
-        <v>0.99870289970840342</v>
+        <v>0.99713671217394562</v>
       </c>
       <c r="AB32">
-        <v>23.107973955380711</v>
+        <v>51.990142494672078</v>
       </c>
       <c r="AD32" t="s">
         <v>307</v>
@@ -9481,13 +9481,13 @@
         <v>584</v>
       </c>
       <c r="AN32" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="AO32">
-        <v>0.99863161241655762</v>
+        <v>0.99757815671697558</v>
       </c>
       <c r="AP32">
-        <v>48.306707937232645</v>
+        <v>51.990142494672078</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9552,16 +9552,16 @@
         <v>354</v>
       </c>
       <c r="Y33" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Z33" t="s">
         <v>436</v>
       </c>
       <c r="AA33">
-        <v>0.99755900053893942</v>
+        <v>0.99774884372261763</v>
       </c>
       <c r="AB33">
-        <v>42.327567967950763</v>
+        <v>84.621736519387298</v>
       </c>
       <c r="AD33" t="s">
         <v>307</v>
@@ -9591,13 +9591,13 @@
         <v>585</v>
       </c>
       <c r="AN33" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="AO33">
-        <v>0.99864365615724771</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AP33">
-        <v>24.883658184919245</v>
+        <v>15.260625790927634</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9662,16 +9662,16 @@
         <v>356</v>
       </c>
       <c r="Y34" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="Z34" t="s">
         <v>437</v>
       </c>
       <c r="AA34">
-        <v>0.99776786767941794</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AB34">
-        <v>27.059822883365296</v>
+        <v>23.861203412894469</v>
       </c>
       <c r="AD34" t="s">
         <v>307</v>
@@ -9701,13 +9701,13 @@
         <v>586</v>
       </c>
       <c r="AN34" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="AO34">
-        <v>0.9975765595050764</v>
+        <v>0.99729296780855581</v>
       </c>
       <c r="AP34">
-        <v>31.560996462068374</v>
+        <v>49.14481327115881</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9772,16 +9772,16 @@
         <v>358</v>
       </c>
       <c r="Y35" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="Z35" t="s">
         <v>438</v>
       </c>
       <c r="AA35">
-        <v>0.99789789449716026</v>
+        <v>0.99813022065694434</v>
       </c>
       <c r="AB35">
-        <v>39.831307398714806</v>
+        <v>40.332510468654611</v>
       </c>
       <c r="AD35" t="s">
         <v>307</v>
@@ -9811,13 +9811,13 @@
         <v>587</v>
       </c>
       <c r="AN35" t="s">
-        <v>423</v>
+        <v>462</v>
       </c>
       <c r="AO35">
-        <v>0.99632737337312927</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AP35">
-        <v>48.031259731727893</v>
+        <v>12.729766626457181</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9882,16 +9882,16 @@
         <v>360</v>
       </c>
       <c r="Y36" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="Z36" t="s">
         <v>439</v>
       </c>
       <c r="AA36">
-        <v>0.99864365615724771</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AB36">
-        <v>45.737867404715672</v>
+        <v>33.253084498654445</v>
       </c>
       <c r="AD36" t="s">
         <v>307</v>
@@ -9921,13 +9921,13 @@
         <v>588</v>
       </c>
       <c r="AN36" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="AO36">
-        <v>0.99739127962445018</v>
+        <v>0.99863161241655762</v>
       </c>
       <c r="AP36">
-        <v>39.831307398714806</v>
+        <v>48.306707937232645</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9992,16 +9992,16 @@
         <v>362</v>
       </c>
       <c r="Y37" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="Z37" t="s">
         <v>440</v>
       </c>
       <c r="AA37">
-        <v>0.9991052659747558</v>
+        <v>0.99751836673919181</v>
       </c>
       <c r="AB37">
-        <v>12.019055461720432</v>
+        <v>50.515025114296037</v>
       </c>
       <c r="AD37" t="s">
         <v>307</v>
@@ -10031,13 +10031,13 @@
         <v>589</v>
       </c>
       <c r="AN37" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO37">
-        <v>0.99818574894902312</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AP37">
-        <v>33.253084498654445</v>
+        <v>24.883658184919245</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10102,16 +10102,16 @@
         <v>364</v>
       </c>
       <c r="Y38" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="Z38" t="s">
         <v>441</v>
       </c>
       <c r="AA38">
-        <v>0.99679205626668776</v>
+        <v>0.99774808836727491</v>
       </c>
       <c r="AB38">
-        <v>28.983218493781202</v>
+        <v>41.186340097586395</v>
       </c>
       <c r="AD38" t="s">
         <v>307</v>
@@ -10144,10 +10144,10 @@
         <v>421</v>
       </c>
       <c r="AO38">
-        <v>0.99853353101054187</v>
+        <v>0.99870289970840342</v>
       </c>
       <c r="AP38">
-        <v>18.693183403514499</v>
+        <v>23.107973955380711</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10212,16 +10212,16 @@
         <v>366</v>
       </c>
       <c r="Y39" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="Z39" t="s">
         <v>442</v>
       </c>
       <c r="AA39">
-        <v>0.99713110094318969</v>
+        <v>0.99828790514523624</v>
       </c>
       <c r="AB39">
-        <v>34.34566125862937</v>
+        <v>28.428965886446147</v>
       </c>
       <c r="AD39" t="s">
         <v>307</v>
@@ -10251,13 +10251,13 @@
         <v>591</v>
       </c>
       <c r="AN39" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AO39">
-        <v>0.99747843498043831</v>
+        <v>0.99751816641322844</v>
       </c>
       <c r="AP39">
-        <v>46.334800039670455</v>
+        <v>45.1502695224383</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10322,16 +10322,16 @@
         <v>368</v>
       </c>
       <c r="Y40" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="Z40" t="s">
         <v>443</v>
       </c>
       <c r="AA40">
-        <v>0.99749963479302273</v>
+        <v>0.99834689519829145</v>
       </c>
       <c r="AB40">
-        <v>49.14481327115881</v>
+        <v>32.749623583141812</v>
       </c>
       <c r="AD40" t="s">
         <v>307</v>
@@ -10361,13 +10361,13 @@
         <v>592</v>
       </c>
       <c r="AN40" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="AO40">
-        <v>0.99466341005350978</v>
+        <v>0.99754431624006568</v>
       </c>
       <c r="AP40">
-        <v>58.229467192272445</v>
+        <v>32.256845956342154</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10432,16 +10432,16 @@
         <v>370</v>
       </c>
       <c r="Y41" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="Z41" t="s">
         <v>444</v>
       </c>
       <c r="AA41">
-        <v>0.9985687661763365</v>
+        <v>0.99853303004525662</v>
       </c>
       <c r="AB41">
-        <v>50.93040927578344</v>
+        <v>18.693183403514499</v>
       </c>
       <c r="AD41" t="s">
         <v>307</v>
@@ -10471,13 +10471,13 @@
         <v>593</v>
       </c>
       <c r="AN41" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="AO41">
-        <v>0.9977732948939011</v>
+        <v>0.99755521694544447</v>
       </c>
       <c r="AP41">
-        <v>51.165698000691506</v>
+        <v>50.682816539915542</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10542,16 +10542,16 @@
         <v>372</v>
       </c>
       <c r="Y42" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="Z42" t="s">
         <v>445</v>
       </c>
       <c r="AA42">
-        <v>0.99751836673919181</v>
+        <v>0.99751567592854107</v>
       </c>
       <c r="AB42">
-        <v>50.515025114296037</v>
+        <v>46.334800039670455</v>
       </c>
       <c r="AD42" t="s">
         <v>307</v>
@@ -10581,13 +10581,13 @@
         <v>594</v>
       </c>
       <c r="AN42" t="s">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="AO42">
-        <v>0.99872758388674931</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AP42">
-        <v>23.31941562731657</v>
+        <v>2.9143415731308986</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10652,16 +10652,16 @@
         <v>374</v>
       </c>
       <c r="Y43" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="Z43" t="s">
         <v>446</v>
       </c>
       <c r="AA43">
-        <v>0.99774808836727491</v>
+        <v>0.9978643471647114</v>
       </c>
       <c r="AB43">
-        <v>41.186340097586395</v>
+        <v>31.560996462068374</v>
       </c>
       <c r="AD43" t="s">
         <v>307</v>
@@ -10691,13 +10691,13 @@
         <v>595</v>
       </c>
       <c r="AN43" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="AO43">
-        <v>0.99790284855194045</v>
+        <v>0.9980121476893673</v>
       </c>
       <c r="AP43">
-        <v>35.874797800938026</v>
+        <v>30.863466083156009</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10762,16 +10762,16 @@
         <v>376</v>
       </c>
       <c r="Y44" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="Z44" t="s">
         <v>447</v>
       </c>
       <c r="AA44">
-        <v>0.99828790514523624</v>
+        <v>0.99789011269484895</v>
       </c>
       <c r="AB44">
-        <v>28.428965886446147</v>
+        <v>36.605495131795273</v>
       </c>
       <c r="AD44" t="s">
         <v>307</v>
@@ -10801,13 +10801,13 @@
         <v>596</v>
       </c>
       <c r="AN44" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="AO44">
-        <v>0.99856107979091546</v>
+        <v>0.99811519908104196</v>
       </c>
       <c r="AP44">
-        <v>26.622770797002293</v>
+        <v>41.186340097586395</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10872,16 +10872,16 @@
         <v>378</v>
       </c>
       <c r="Y45" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="Z45" t="s">
         <v>448</v>
       </c>
       <c r="AA45">
-        <v>0.9978643471647114</v>
+        <v>0.99783121031362565</v>
       </c>
       <c r="AB45">
-        <v>31.560996462068374</v>
+        <v>51.165698000691506</v>
       </c>
       <c r="AD45" t="s">
         <v>307</v>
@@ -10911,13 +10911,13 @@
         <v>597</v>
       </c>
       <c r="AN45" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="AO45">
-        <v>0.99649252363612195</v>
+        <v>0.99632737337312927</v>
       </c>
       <c r="AP45">
-        <v>28.983218493781202</v>
+        <v>48.031259731727893</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10982,16 +10982,16 @@
         <v>380</v>
       </c>
       <c r="Y46" t="s">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="Z46" t="s">
         <v>449</v>
       </c>
       <c r="AA46">
-        <v>0.99789011269484895</v>
+        <v>0.99754569173664964</v>
       </c>
       <c r="AB46">
-        <v>36.605495131795273</v>
+        <v>45.1502695224383</v>
       </c>
       <c r="AD46" t="s">
         <v>307</v>
@@ -11021,13 +11021,13 @@
         <v>598</v>
       </c>
       <c r="AN46" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="AO46">
-        <v>0.99767811393002859</v>
+        <v>0.99739127962445018</v>
       </c>
       <c r="AP46">
-        <v>30.875049982999808</v>
+        <v>39.831307398714806</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -11092,16 +11092,16 @@
         <v>382</v>
       </c>
       <c r="Y47" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="Z47" t="s">
         <v>450</v>
       </c>
       <c r="AA47">
-        <v>0.99783121031362565</v>
+        <v>0.99697644816659792</v>
       </c>
       <c r="AB47">
-        <v>51.165698000691506</v>
+        <v>58.519281729791345</v>
       </c>
       <c r="AD47" t="s">
         <v>307</v>
@@ -11131,13 +11131,13 @@
         <v>599</v>
       </c>
       <c r="AN47" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AO47">
-        <v>0.99764304373832691</v>
+        <v>0.99818574894902312</v>
       </c>
       <c r="AP47">
-        <v>42.327567967950763</v>
+        <v>33.253084498654445</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -11202,16 +11202,16 @@
         <v>384</v>
       </c>
       <c r="Y48" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="Z48" t="s">
         <v>451</v>
       </c>
       <c r="AA48">
-        <v>0.99751567592854107</v>
+        <v>0.99755900053893942</v>
       </c>
       <c r="AB48">
-        <v>46.334800039670455</v>
+        <v>42.327567967950763</v>
       </c>
       <c r="AD48" t="s">
         <v>307</v>
@@ -11241,13 +11241,13 @@
         <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="AO48">
-        <v>0.99790384243262886</v>
+        <v>0.99853353101054187</v>
       </c>
       <c r="AP48">
-        <v>72.461220387375079</v>
+        <v>18.693183403514499</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -11312,16 +11312,16 @@
         <v>386</v>
       </c>
       <c r="Y49" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="Z49" t="s">
         <v>452</v>
       </c>
       <c r="AA49">
-        <v>0.99818574894902312</v>
+        <v>0.99776786767941794</v>
       </c>
       <c r="AB49">
-        <v>33.253084498654445</v>
+        <v>27.059822883365296</v>
       </c>
       <c r="AD49" t="s">
         <v>307</v>
@@ -11351,13 +11351,13 @@
         <v>601</v>
       </c>
       <c r="AN49" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="AO49">
-        <v>0.99797028609854399</v>
+        <v>0.99747843498043831</v>
       </c>
       <c r="AP49">
-        <v>34.892661212818595</v>
+        <v>46.334800039670455</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -11422,16 +11422,16 @@
         <v>388</v>
       </c>
       <c r="Y50" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="Z50" t="s">
         <v>453</v>
       </c>
       <c r="AA50">
-        <v>0.99754569173664964</v>
+        <v>0.99789789449716026</v>
       </c>
       <c r="AB50">
-        <v>45.1502695224383</v>
+        <v>39.831307398714806</v>
       </c>
       <c r="AD50" t="s">
         <v>307</v>
@@ -11461,13 +11461,13 @@
         <v>602</v>
       </c>
       <c r="AN50" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="AO50">
-        <v>0.99839049347738307</v>
+        <v>0.99466341005350978</v>
       </c>
       <c r="AP50">
-        <v>75.277133913292474</v>
+        <v>58.229467192272445</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -11532,16 +11532,16 @@
         <v>390</v>
       </c>
       <c r="Y51" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="Z51" t="s">
         <v>454</v>
       </c>
       <c r="AA51">
-        <v>0.99697644816659792</v>
+        <v>0.99864365615724771</v>
       </c>
       <c r="AB51">
-        <v>58.519281729791345</v>
+        <v>45.737867404715672</v>
       </c>
       <c r="AD51" t="s">
         <v>307</v>
@@ -11571,13 +11571,13 @@
         <v>603</v>
       </c>
       <c r="AN51" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="AO51">
-        <v>0.99697913305259955</v>
+        <v>0.9977732948939011</v>
       </c>
       <c r="AP51">
-        <v>58.519281729791345</v>
+        <v>51.165698000691506</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -11642,16 +11642,16 @@
         <v>392</v>
       </c>
       <c r="Y52" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="Z52" t="s">
         <v>455</v>
       </c>
       <c r="AA52">
-        <v>0.99761913939972058</v>
+        <v>0.9991052659747558</v>
       </c>
       <c r="AB52">
-        <v>32.256845956342154</v>
+        <v>12.019055461720432</v>
       </c>
       <c r="AD52" t="s">
         <v>307</v>
@@ -11681,13 +11681,13 @@
         <v>604</v>
       </c>
       <c r="AN52" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AO52">
-        <v>0.99757778563357669</v>
+        <v>0.99872758388674931</v>
       </c>
       <c r="AP52">
-        <v>45.221154662357485</v>
+        <v>23.31941562731657</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -11752,16 +11752,16 @@
         <v>394</v>
       </c>
       <c r="Y53" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="Z53" t="s">
         <v>456</v>
       </c>
       <c r="AA53">
-        <v>0.99916488913437129</v>
+        <v>0.99814724525850784</v>
       </c>
       <c r="AB53">
-        <v>15.260625790927634</v>
+        <v>47.820994144128512</v>
       </c>
       <c r="AD53" t="s">
         <v>307</v>
@@ -11791,13 +11791,13 @@
         <v>605</v>
       </c>
       <c r="AN53" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AO53">
-        <v>0.99896573022887158</v>
+        <v>0.99649252363612195</v>
       </c>
       <c r="AP53">
-        <v>18.936001260254645</v>
+        <v>28.983218493781202</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -11862,16 +11862,16 @@
         <v>396</v>
       </c>
       <c r="Y54" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="Z54" t="s">
         <v>457</v>
       </c>
       <c r="AA54">
-        <v>0.99921633401208909</v>
+        <v>0.99848201234520018</v>
       </c>
       <c r="AB54">
-        <v>12.729766626457181</v>
+        <v>72.463654284142635</v>
       </c>
       <c r="AD54" t="s">
         <v>307</v>
@@ -11901,13 +11901,13 @@
         <v>606</v>
       </c>
       <c r="AN54" t="s">
-        <v>464</v>
+        <v>427</v>
       </c>
       <c r="AO54">
-        <v>0.99813022065694434</v>
+        <v>0.99767811393002859</v>
       </c>
       <c r="AP54">
-        <v>40.332510468654611</v>
+        <v>30.875049982999808</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -11972,16 +11972,16 @@
         <v>398</v>
       </c>
       <c r="Y55" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="Z55" t="s">
         <v>458</v>
       </c>
       <c r="AA55">
-        <v>0.99984169097848852</v>
+        <v>0.99886290297361824</v>
       </c>
       <c r="AB55">
-        <v>2.9143415731308986</v>
+        <v>26.622770797002293</v>
       </c>
       <c r="AD55" t="s">
         <v>307</v>
@@ -12011,13 +12011,13 @@
         <v>607</v>
       </c>
       <c r="AN55" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="AO55">
-        <v>0.99828876210676587</v>
+        <v>0.99764304373832691</v>
       </c>
       <c r="AP55">
-        <v>28.334088028040785</v>
+        <v>42.327567967950763</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -12082,16 +12082,16 @@
         <v>400</v>
       </c>
       <c r="Y56" t="s">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="Z56" t="s">
         <v>459</v>
       </c>
       <c r="AA56">
-        <v>0.99811506665856298</v>
+        <v>0.99779181951287421</v>
       </c>
       <c r="AB56">
-        <v>35.874797800938026</v>
+        <v>61.086483632538339</v>
       </c>
       <c r="AD56" t="s">
         <v>307</v>
@@ -12121,13 +12121,13 @@
         <v>608</v>
       </c>
       <c r="AN56" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="AO56">
-        <v>0.9967210177786987</v>
+        <v>0.99790384243262886</v>
       </c>
       <c r="AP56">
-        <v>34.34566125862937</v>
+        <v>72.461220387375079</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -12192,16 +12192,16 @@
         <v>402</v>
       </c>
       <c r="Y57" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Z57" t="s">
         <v>460</v>
       </c>
       <c r="AA57">
-        <v>0.99852418793335518</v>
+        <v>0.99761913939972058</v>
       </c>
       <c r="AB57">
-        <v>25.205687076233477</v>
+        <v>32.256845956342154</v>
       </c>
       <c r="AD57" t="s">
         <v>307</v>
@@ -12231,13 +12231,13 @@
         <v>609</v>
       </c>
       <c r="AN57" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="AO57">
-        <v>0.99777922331243873</v>
+        <v>0.99797028609854399</v>
       </c>
       <c r="AP57">
-        <v>61.086483632538339</v>
+        <v>34.892661212818595</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -12302,16 +12302,16 @@
         <v>404</v>
       </c>
       <c r="Y58" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="Z58" t="s">
         <v>461</v>
       </c>
       <c r="AA58">
-        <v>0.99713671217394562</v>
+        <v>0.99916488913437129</v>
       </c>
       <c r="AB58">
-        <v>51.990142494672078</v>
+        <v>15.260625790927634</v>
       </c>
       <c r="AD58" t="s">
         <v>307</v>
@@ -12341,13 +12341,13 @@
         <v>610</v>
       </c>
       <c r="AN58" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="AO58">
-        <v>0.99777988747037838</v>
+        <v>0.99871472031655018</v>
       </c>
       <c r="AP58">
-        <v>36.605495131795273</v>
+        <v>28.428965886446147</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -12412,16 +12412,16 @@
         <v>406</v>
       </c>
       <c r="Y59" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="Z59" t="s">
         <v>462</v>
       </c>
       <c r="AA59">
-        <v>0.99774884372261763</v>
+        <v>0.99921633401208909</v>
       </c>
       <c r="AB59">
-        <v>84.621736519387298</v>
+        <v>12.729766626457181</v>
       </c>
       <c r="AD59" t="s">
         <v>307</v>
@@ -12451,13 +12451,13 @@
         <v>611</v>
       </c>
       <c r="AN59" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AO59">
-        <v>0.99870289970840342</v>
+        <v>0.99782029353787438</v>
       </c>
       <c r="AP59">
-        <v>23.107973955380711</v>
+        <v>23.861203412894469</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -12522,16 +12522,16 @@
         <v>408</v>
       </c>
       <c r="Y60" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="Z60" t="s">
         <v>463</v>
       </c>
       <c r="AA60">
-        <v>0.99782029353787438</v>
+        <v>0.99984169097848852</v>
       </c>
       <c r="AB60">
-        <v>23.861203412894469</v>
+        <v>2.9143415731308986</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -12596,16 +12596,16 @@
         <v>410</v>
       </c>
       <c r="Y61" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="Z61" t="s">
         <v>464</v>
       </c>
       <c r="AA61">
-        <v>0.99813022065694434</v>
+        <v>0.99815889366481214</v>
       </c>
       <c r="AB61">
-        <v>40.332510468654611</v>
+        <v>34.892661212818595</v>
       </c>
     </row>
   </sheetData>
@@ -12614,7 +12614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C17EE5F-34F1-4EA4-9744-5858F7FC092D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CCBE04-5A81-4C08-90A5-199C982A9E6E}">
   <dimension ref="B9:Z59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12726,7 +12726,7 @@
         <v>642</v>
       </c>
       <c r="K11" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="L11">
         <v>0.64021427611097514</v>
@@ -12759,7 +12759,7 @@
         <v>740</v>
       </c>
       <c r="X11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Y11">
         <v>17.603249999999999</v>
@@ -12794,7 +12794,7 @@
         <v>644</v>
       </c>
       <c r="K12" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="L12">
         <v>3.683157674608327</v>
@@ -12827,7 +12827,7 @@
         <v>742</v>
       </c>
       <c r="X12" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="Y12">
         <v>11.58525</v>
@@ -12862,7 +12862,7 @@
         <v>646</v>
       </c>
       <c r="K13" t="s">
-        <v>595</v>
+        <v>563</v>
       </c>
       <c r="L13">
         <v>1.1133782162108721</v>
@@ -12895,7 +12895,7 @@
         <v>744</v>
       </c>
       <c r="X13" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="Y13">
         <v>5.7000000000000002E-2</v>
@@ -12930,7 +12930,7 @@
         <v>648</v>
       </c>
       <c r="K14" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="L14">
         <v>2.5290705136145335</v>
@@ -12963,7 +12963,7 @@
         <v>746</v>
       </c>
       <c r="X14" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="Y14">
         <v>11.2965</v>
@@ -12998,7 +12998,7 @@
         <v>650</v>
       </c>
       <c r="K15" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="L15">
         <v>2.1620342624302693</v>
@@ -13031,7 +13031,7 @@
         <v>748</v>
       </c>
       <c r="X15" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="Y15">
         <v>0.83925000000000005</v>
@@ -13066,7 +13066,7 @@
         <v>652</v>
       </c>
       <c r="K16" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="L16">
         <v>0.10228431008717309</v>
@@ -13099,7 +13099,7 @@
         <v>750</v>
       </c>
       <c r="X16" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="Y16">
         <v>2.0332499999999998</v>
@@ -13134,7 +13134,7 @@
         <v>654</v>
       </c>
       <c r="K17" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L17">
         <v>0.26374115795515951</v>
@@ -13167,7 +13167,7 @@
         <v>752</v>
       </c>
       <c r="X17" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="Y17">
         <v>5.8237500000000004</v>
@@ -13202,7 +13202,7 @@
         <v>656</v>
       </c>
       <c r="K18" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="L18">
         <v>1.0775690479395925</v>
@@ -13235,7 +13235,7 @@
         <v>754</v>
       </c>
       <c r="X18" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="Y18">
         <v>16.887</v>
@@ -13270,7 +13270,7 @@
         <v>658</v>
       </c>
       <c r="K19" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="L19">
         <v>1.644864133979123</v>
@@ -13303,7 +13303,7 @@
         <v>756</v>
       </c>
       <c r="X19" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="Y19">
         <v>17.089500000000001</v>
@@ -13338,7 +13338,7 @@
         <v>660</v>
       </c>
       <c r="K20" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="L20">
         <v>4.1793335626386838</v>
@@ -13371,7 +13371,7 @@
         <v>758</v>
       </c>
       <c r="X20" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="Y20">
         <v>5.4255000000000004</v>
@@ -13406,7 +13406,7 @@
         <v>662</v>
       </c>
       <c r="K21" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="L21">
         <v>0.10220883742433164</v>
@@ -13441,7 +13441,7 @@
         <v>664</v>
       </c>
       <c r="K22" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="L22">
         <v>3.2456117052218421</v>
@@ -13476,7 +13476,7 @@
         <v>666</v>
       </c>
       <c r="K23" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="L23">
         <v>3.822617103272679</v>
@@ -13511,7 +13511,7 @@
         <v>668</v>
       </c>
       <c r="K24" t="s">
-        <v>602</v>
+        <v>575</v>
       </c>
       <c r="L24">
         <v>0.18120178223038519</v>
@@ -13546,7 +13546,7 @@
         <v>670</v>
       </c>
       <c r="K25" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="L25">
         <v>1.2636771265917695</v>
@@ -13581,7 +13581,7 @@
         <v>672</v>
       </c>
       <c r="K26" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="L26">
         <v>2.5500240416298969</v>
@@ -13616,7 +13616,7 @@
         <v>674</v>
       </c>
       <c r="K27" t="s">
-        <v>603</v>
+        <v>576</v>
       </c>
       <c r="L27">
         <v>4.0346953063254611</v>
@@ -13651,7 +13651,7 @@
         <v>676</v>
       </c>
       <c r="K28" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="L28">
         <v>2.4674795572908166</v>
@@ -13686,7 +13686,7 @@
         <v>678</v>
       </c>
       <c r="K29" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="L29">
         <v>0.19671799304243257</v>
@@ -13721,7 +13721,7 @@
         <v>680</v>
       </c>
       <c r="K30" t="s">
-        <v>596</v>
+        <v>564</v>
       </c>
       <c r="L30">
         <v>0.46906534608342149</v>
@@ -13756,7 +13756,7 @@
         <v>682</v>
       </c>
       <c r="K31" t="s">
-        <v>604</v>
+        <v>577</v>
       </c>
       <c r="L31">
         <v>0.70432433684539619</v>
@@ -13791,7 +13791,7 @@
         <v>684</v>
       </c>
       <c r="K32" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="L32">
         <v>0.14326997649193718</v>
@@ -13826,7 +13826,7 @@
         <v>686</v>
       </c>
       <c r="K33" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="L33">
         <v>2.5135228824118248E-2</v>
@@ -13861,7 +13861,7 @@
         <v>688</v>
       </c>
       <c r="K34" t="s">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="L34">
         <v>0.60333316217563482</v>
@@ -13896,7 +13896,7 @@
         <v>690</v>
       </c>
       <c r="K35" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="L35">
         <v>0.61002023046213527</v>
@@ -13931,7 +13931,7 @@
         <v>692</v>
       </c>
       <c r="K36" t="s">
-        <v>574</v>
+        <v>610</v>
       </c>
       <c r="L36">
         <v>5.5124889677616896E-2</v>
@@ -13966,7 +13966,7 @@
         <v>694</v>
       </c>
       <c r="K37" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="L37">
         <v>0.19696072330654418</v>
@@ -14001,7 +14001,7 @@
         <v>696</v>
       </c>
       <c r="K38" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="L38">
         <v>0.37453679972687481</v>
@@ -14036,7 +14036,7 @@
         <v>698</v>
       </c>
       <c r="K39" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="L39">
         <v>2.9266524214395733</v>
@@ -14071,7 +14071,7 @@
         <v>700</v>
       </c>
       <c r="K40" t="s">
-        <v>607</v>
+        <v>566</v>
       </c>
       <c r="L40">
         <v>0.46102512715199689</v>
@@ -14106,7 +14106,7 @@
         <v>702</v>
       </c>
       <c r="K41" t="s">
-        <v>605</v>
+        <v>578</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -14141,7 +14141,7 @@
         <v>704</v>
       </c>
       <c r="K42" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="L42">
         <v>1.9780607647145438</v>
@@ -14176,7 +14176,7 @@
         <v>706</v>
       </c>
       <c r="K43" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="L43">
         <v>0.80689812107944159</v>
@@ -14211,7 +14211,7 @@
         <v>708</v>
       </c>
       <c r="K44" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L44">
         <v>0.1886799653533156</v>
@@ -14246,7 +14246,7 @@
         <v>710</v>
       </c>
       <c r="K45" t="s">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="L45">
         <v>2.577065692017253</v>
@@ -14281,7 +14281,7 @@
         <v>712</v>
       </c>
       <c r="K46" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="L46">
         <v>0.32349873740765611</v>
@@ -14316,7 +14316,7 @@
         <v>714</v>
       </c>
       <c r="K47" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -14351,7 +14351,7 @@
         <v>716</v>
       </c>
       <c r="K48" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="L48">
         <v>2.3210450729876548</v>
@@ -14386,7 +14386,7 @@
         <v>718</v>
       </c>
       <c r="K49" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="L49">
         <v>1.4641560353950904</v>
@@ -14421,7 +14421,7 @@
         <v>720</v>
       </c>
       <c r="K50" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="L50">
         <v>4.3172734082397007E-3</v>
@@ -14456,7 +14456,7 @@
         <v>722</v>
       </c>
       <c r="K51" t="s">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="L51">
         <v>2.3327457542865271</v>
@@ -14491,7 +14491,7 @@
         <v>724</v>
       </c>
       <c r="K52" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="L52">
         <v>0.64220735366408732</v>
@@ -14526,7 +14526,7 @@
         <v>726</v>
       </c>
       <c r="K53" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="L53">
         <v>0.20805219904440039</v>
@@ -14561,7 +14561,7 @@
         <v>728</v>
       </c>
       <c r="K54" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="L54">
         <v>1.3018026354345156</v>
@@ -14596,7 +14596,7 @@
         <v>730</v>
       </c>
       <c r="K55" t="s">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="L55">
         <v>3.0871018425456893</v>
@@ -14631,7 +14631,7 @@
         <v>732</v>
       </c>
       <c r="K56" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="L56">
         <v>3.1635610249840389</v>
@@ -14666,7 +14666,7 @@
         <v>734</v>
       </c>
       <c r="K57" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="L57">
         <v>9.3245940212150449E-2</v>
@@ -14701,7 +14701,7 @@
         <v>736</v>
       </c>
       <c r="K58" t="s">
-        <v>575</v>
+        <v>611</v>
       </c>
       <c r="L58">
         <v>0.28717016660662842</v>
@@ -14736,7 +14736,7 @@
         <v>738</v>
       </c>
       <c r="K59" t="s">
-        <v>606</v>
+        <v>579</v>
       </c>
       <c r="L59">
         <v>0.93964202108728523</v>
@@ -14751,7 +14751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67DCE07-CC5C-45E3-B0D1-E9E85C783236}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B19108C-1C77-43BF-8B7F-5605FB0345AD}">
   <dimension ref="B9:Y159"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19812,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E92D2EE-D333-4ED5-A269-9D9F119618C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94E0241-1D8C-498A-9753-71E596C1D5B5}">
   <dimension ref="B9:T60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
